--- a/doc/ETS_EPP_Profil_Positionen.xlsx
+++ b/doc/ETS_EPP_Profil_Positionen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Matthias\OpenKNX\OAM-EnoceanNEU\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD4867D3-216E-4E1B-8A85-F0FF430EC35B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB578F8-C48F-48B0-80D5-5FD469588E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="20016" windowHeight="9960" firstSheet="2" activeTab="2" xr2:uid="{569ECD57-C369-4D5C-ADA5-279ADE310DDC}"/>
+    <workbookView xWindow="1236" yWindow="2508" windowWidth="21624" windowHeight="12336" firstSheet="3" activeTab="3" xr2:uid="{569ECD57-C369-4D5C-ADA5-279ADE310DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="EEP-Profile" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2467" uniqueCount="1018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="1022">
   <si>
     <t>F6-02-01</t>
   </si>
@@ -3339,6 +3339,18 @@
   </si>
   <si>
     <t>F3</t>
+  </si>
+  <si>
+    <t>CO2 / VOC</t>
+  </si>
+  <si>
+    <t>VOC_Identification</t>
+  </si>
+  <si>
+    <t>DPT9.030</t>
+  </si>
+  <si>
+    <t>Werte in µg/m3</t>
   </si>
 </sst>
 </file>
@@ -4004,35 +4016,23 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4043,31 +4043,31 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4079,16 +4079,28 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4492,13 +4504,13 @@
       <c r="B3" s="9">
         <v>1</v>
       </c>
-      <c r="C3" s="111" t="s">
+      <c r="C3" s="110" t="s">
         <v>220</v>
       </c>
-      <c r="D3" s="111" t="s">
+      <c r="D3" s="110" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="111">
+      <c r="E3" s="110">
         <v>2</v>
       </c>
       <c r="F3" s="9" t="s">
@@ -4512,9 +4524,9 @@
       <c r="B4" s="9">
         <v>2</v>
       </c>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
       <c r="F4" s="9" t="s">
         <v>15</v>
       </c>
@@ -4526,9 +4538,9 @@
       <c r="B5" s="9">
         <v>3</v>
       </c>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
       <c r="F5" s="9" t="s">
         <v>16</v>
       </c>
@@ -4540,9 +4552,9 @@
       <c r="B6" s="9">
         <v>4</v>
       </c>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
       <c r="F6" s="9" t="s">
         <v>17</v>
       </c>
@@ -4554,9 +4566,9 @@
       <c r="B7" s="9">
         <v>5</v>
       </c>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
-      <c r="E7" s="111"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
       <c r="F7" s="9" t="s">
         <v>18</v>
       </c>
@@ -4568,9 +4580,9 @@
       <c r="B8" s="9">
         <v>6</v>
       </c>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="111"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="110"/>
       <c r="F8" s="9" t="s">
         <v>19</v>
       </c>
@@ -4582,9 +4594,9 @@
       <c r="B9" s="9">
         <v>7</v>
       </c>
-      <c r="C9" s="111"/>
-      <c r="D9" s="111"/>
-      <c r="E9" s="111"/>
+      <c r="C9" s="110"/>
+      <c r="D9" s="110"/>
+      <c r="E9" s="110"/>
       <c r="F9" s="9" t="s">
         <v>20</v>
       </c>
@@ -4596,9 +4608,9 @@
       <c r="B10" s="9">
         <v>8</v>
       </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="111"/>
-      <c r="E10" s="111"/>
+      <c r="C10" s="110"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="110"/>
       <c r="F10" s="9" t="s">
         <v>21</v>
       </c>
@@ -4610,9 +4622,9 @@
       <c r="B11" s="9">
         <v>9</v>
       </c>
-      <c r="C11" s="111"/>
-      <c r="D11" s="111"/>
-      <c r="E11" s="111"/>
+      <c r="C11" s="110"/>
+      <c r="D11" s="110"/>
+      <c r="E11" s="110"/>
       <c r="F11" s="9" t="s">
         <v>22</v>
       </c>
@@ -4624,9 +4636,9 @@
       <c r="B12" s="9">
         <v>10</v>
       </c>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
+      <c r="C12" s="110"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="110"/>
       <c r="F12" s="9" t="s">
         <v>33</v>
       </c>
@@ -4638,9 +4650,9 @@
       <c r="B13" s="9">
         <v>11</v>
       </c>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
+      <c r="C13" s="110"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="110"/>
       <c r="F13" s="9" t="s">
         <v>34</v>
       </c>
@@ -4652,9 +4664,9 @@
       <c r="B14" s="9">
         <v>12</v>
       </c>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
+      <c r="C14" s="110"/>
+      <c r="D14" s="110"/>
+      <c r="E14" s="110"/>
       <c r="F14" s="9" t="s">
         <v>23</v>
       </c>
@@ -4666,9 +4678,9 @@
       <c r="B15" s="9">
         <v>13</v>
       </c>
-      <c r="C15" s="111"/>
-      <c r="D15" s="111"/>
-      <c r="E15" s="111"/>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="110"/>
       <c r="F15" s="9" t="s">
         <v>24</v>
       </c>
@@ -4680,9 +4692,9 @@
       <c r="B16" s="9">
         <v>14</v>
       </c>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
+      <c r="C16" s="110"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="110"/>
       <c r="F16" s="9" t="s">
         <v>25</v>
       </c>
@@ -4694,9 +4706,9 @@
       <c r="B17" s="9">
         <v>15</v>
       </c>
-      <c r="C17" s="111"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="111"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="110"/>
       <c r="F17" s="9" t="s">
         <v>26</v>
       </c>
@@ -4708,9 +4720,9 @@
       <c r="B18" s="9">
         <v>16</v>
       </c>
-      <c r="C18" s="111"/>
-      <c r="D18" s="111"/>
-      <c r="E18" s="111"/>
+      <c r="C18" s="110"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="110"/>
       <c r="F18" s="9" t="s">
         <v>27</v>
       </c>
@@ -4722,9 +4734,9 @@
       <c r="B19" s="9">
         <v>17</v>
       </c>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
+      <c r="C19" s="110"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="110"/>
       <c r="F19" s="9" t="s">
         <v>28</v>
       </c>
@@ -4736,9 +4748,9 @@
       <c r="B20" s="9">
         <v>18</v>
       </c>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="110"/>
       <c r="F20" s="9" t="s">
         <v>29</v>
       </c>
@@ -4750,9 +4762,9 @@
       <c r="B21" s="9">
         <v>19</v>
       </c>
-      <c r="C21" s="111"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
+      <c r="C21" s="110"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="110"/>
       <c r="F21" s="9" t="s">
         <v>30</v>
       </c>
@@ -4764,9 +4776,9 @@
       <c r="B22" s="9">
         <v>20</v>
       </c>
-      <c r="C22" s="111"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="111"/>
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="110"/>
       <c r="F22" s="9" t="s">
         <v>31</v>
       </c>
@@ -4778,9 +4790,9 @@
       <c r="B23" s="9">
         <v>21</v>
       </c>
-      <c r="C23" s="111"/>
-      <c r="D23" s="111"/>
-      <c r="E23" s="111"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="110"/>
       <c r="F23" s="9" t="s">
         <v>32</v>
       </c>
@@ -4792,9 +4804,9 @@
       <c r="B24" s="9">
         <v>22</v>
       </c>
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
+      <c r="C24" s="110"/>
+      <c r="D24" s="110"/>
+      <c r="E24" s="110"/>
       <c r="F24" s="9" t="s">
         <v>35</v>
       </c>
@@ -4806,9 +4818,9 @@
       <c r="B25" s="9">
         <v>23</v>
       </c>
-      <c r="C25" s="111"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
       <c r="F25" s="9" t="s">
         <v>36</v>
       </c>
@@ -4820,9 +4832,9 @@
       <c r="B26" s="9">
         <v>24</v>
       </c>
-      <c r="C26" s="111"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="111"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
       <c r="F26" s="9" t="s">
         <v>37</v>
       </c>
@@ -4834,9 +4846,9 @@
       <c r="B27" s="9">
         <v>25</v>
       </c>
-      <c r="C27" s="111"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="111"/>
+      <c r="C27" s="110"/>
+      <c r="D27" s="110"/>
+      <c r="E27" s="110"/>
       <c r="F27" s="9" t="s">
         <v>38</v>
       </c>
@@ -4848,9 +4860,9 @@
       <c r="B28" s="9">
         <v>26</v>
       </c>
-      <c r="C28" s="111"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="111">
+      <c r="C28" s="110"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="110">
         <v>4</v>
       </c>
       <c r="F28" s="9" t="s">
@@ -4864,9 +4876,9 @@
       <c r="B29" s="9">
         <v>27</v>
       </c>
-      <c r="C29" s="111"/>
-      <c r="D29" s="111"/>
-      <c r="E29" s="111"/>
+      <c r="C29" s="110"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="110"/>
       <c r="F29" s="9" t="s">
         <v>40</v>
       </c>
@@ -4878,9 +4890,9 @@
       <c r="B30" s="9">
         <v>28</v>
       </c>
-      <c r="C30" s="111"/>
-      <c r="D30" s="111"/>
-      <c r="E30" s="111"/>
+      <c r="C30" s="110"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="110"/>
       <c r="F30" s="9" t="s">
         <v>41</v>
       </c>
@@ -4892,9 +4904,9 @@
       <c r="B31" s="9">
         <v>29</v>
       </c>
-      <c r="C31" s="111"/>
-      <c r="D31" s="111"/>
-      <c r="E31" s="111"/>
+      <c r="C31" s="110"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="110"/>
       <c r="F31" s="9" t="s">
         <v>464</v>
       </c>
@@ -4903,8 +4915,8 @@
       <c r="B32" s="9">
         <v>30</v>
       </c>
-      <c r="C32" s="111"/>
-      <c r="D32" s="111"/>
+      <c r="C32" s="110"/>
+      <c r="D32" s="110"/>
       <c r="E32" s="26">
         <v>5</v>
       </c>
@@ -4919,9 +4931,9 @@
       <c r="B33" s="9">
         <v>31</v>
       </c>
-      <c r="C33" s="111"/>
-      <c r="D33" s="111"/>
-      <c r="E33" s="111">
+      <c r="C33" s="110"/>
+      <c r="D33" s="110"/>
+      <c r="E33" s="110">
         <v>6</v>
       </c>
       <c r="F33" s="9" t="s">
@@ -4935,9 +4947,9 @@
       <c r="B34" s="9">
         <v>32</v>
       </c>
-      <c r="C34" s="111"/>
-      <c r="D34" s="111"/>
-      <c r="E34" s="111"/>
+      <c r="C34" s="110"/>
+      <c r="D34" s="110"/>
+      <c r="E34" s="110"/>
       <c r="F34" s="9" t="s">
         <v>44</v>
       </c>
@@ -4949,9 +4961,9 @@
       <c r="B35" s="9">
         <v>33</v>
       </c>
-      <c r="C35" s="111"/>
-      <c r="D35" s="111"/>
-      <c r="E35" s="111"/>
+      <c r="C35" s="110"/>
+      <c r="D35" s="110"/>
+      <c r="E35" s="110"/>
       <c r="F35" s="9" t="s">
         <v>45</v>
       </c>
@@ -4963,9 +4975,9 @@
       <c r="B36" s="9">
         <v>34</v>
       </c>
-      <c r="C36" s="111"/>
-      <c r="D36" s="111"/>
-      <c r="E36" s="111"/>
+      <c r="C36" s="110"/>
+      <c r="D36" s="110"/>
+      <c r="E36" s="110"/>
       <c r="F36" s="9" t="s">
         <v>465</v>
       </c>
@@ -4977,9 +4989,9 @@
       <c r="B37" s="9">
         <v>35</v>
       </c>
-      <c r="C37" s="111"/>
-      <c r="D37" s="111"/>
-      <c r="E37" s="111"/>
+      <c r="C37" s="110"/>
+      <c r="D37" s="110"/>
+      <c r="E37" s="110"/>
       <c r="F37" s="9" t="s">
         <v>466</v>
       </c>
@@ -4991,9 +5003,9 @@
       <c r="B38" s="9">
         <v>36</v>
       </c>
-      <c r="C38" s="111"/>
-      <c r="D38" s="111"/>
-      <c r="E38" s="111">
+      <c r="C38" s="110"/>
+      <c r="D38" s="110"/>
+      <c r="E38" s="110">
         <v>7</v>
       </c>
       <c r="F38" s="9" t="s">
@@ -5010,9 +5022,9 @@
       <c r="B39" s="9">
         <v>37</v>
       </c>
-      <c r="C39" s="111"/>
-      <c r="D39" s="111"/>
-      <c r="E39" s="111"/>
+      <c r="C39" s="110"/>
+      <c r="D39" s="110"/>
+      <c r="E39" s="110"/>
       <c r="F39" s="9" t="s">
         <v>47</v>
       </c>
@@ -5027,9 +5039,9 @@
       <c r="B40" s="9">
         <v>38</v>
       </c>
-      <c r="C40" s="111"/>
-      <c r="D40" s="111"/>
-      <c r="E40" s="111"/>
+      <c r="C40" s="110"/>
+      <c r="D40" s="110"/>
+      <c r="E40" s="110"/>
       <c r="F40" s="9" t="s">
         <v>48</v>
       </c>
@@ -5047,9 +5059,9 @@
       <c r="B41" s="9">
         <v>39</v>
       </c>
-      <c r="C41" s="111"/>
-      <c r="D41" s="111"/>
-      <c r="E41" s="111">
+      <c r="C41" s="110"/>
+      <c r="D41" s="110"/>
+      <c r="E41" s="110">
         <v>8</v>
       </c>
       <c r="F41" s="9" t="s">
@@ -5060,9 +5072,9 @@
       <c r="B42" s="9">
         <v>40</v>
       </c>
-      <c r="C42" s="111"/>
-      <c r="D42" s="111"/>
-      <c r="E42" s="111"/>
+      <c r="C42" s="110"/>
+      <c r="D42" s="110"/>
+      <c r="E42" s="110"/>
       <c r="F42" s="9" t="s">
         <v>50</v>
       </c>
@@ -5071,9 +5083,9 @@
       <c r="B43" s="9">
         <v>41</v>
       </c>
-      <c r="C43" s="111"/>
-      <c r="D43" s="111"/>
-      <c r="E43" s="111"/>
+      <c r="C43" s="110"/>
+      <c r="D43" s="110"/>
+      <c r="E43" s="110"/>
       <c r="F43" s="9" t="s">
         <v>51</v>
       </c>
@@ -5082,9 +5094,9 @@
       <c r="B44" s="9">
         <v>42</v>
       </c>
-      <c r="C44" s="111"/>
-      <c r="D44" s="111"/>
-      <c r="E44" s="111">
+      <c r="C44" s="110"/>
+      <c r="D44" s="110"/>
+      <c r="E44" s="110">
         <v>9</v>
       </c>
       <c r="F44" s="9" t="s">
@@ -5095,9 +5107,9 @@
       <c r="B45" s="9">
         <v>43</v>
       </c>
-      <c r="C45" s="111"/>
-      <c r="D45" s="111"/>
-      <c r="E45" s="111"/>
+      <c r="C45" s="110"/>
+      <c r="D45" s="110"/>
+      <c r="E45" s="110"/>
       <c r="F45" s="9" t="s">
         <v>54</v>
       </c>
@@ -5106,9 +5118,9 @@
       <c r="B46" s="9">
         <v>44</v>
       </c>
-      <c r="C46" s="111"/>
-      <c r="D46" s="111"/>
-      <c r="E46" s="111"/>
+      <c r="C46" s="110"/>
+      <c r="D46" s="110"/>
+      <c r="E46" s="110"/>
       <c r="F46" s="9" t="s">
         <v>55</v>
       </c>
@@ -5117,9 +5129,9 @@
       <c r="B47" s="9">
         <v>45</v>
       </c>
-      <c r="C47" s="111"/>
-      <c r="D47" s="111"/>
-      <c r="E47" s="111"/>
+      <c r="C47" s="110"/>
+      <c r="D47" s="110"/>
+      <c r="E47" s="110"/>
       <c r="F47" s="9" t="s">
         <v>56</v>
       </c>
@@ -5128,9 +5140,9 @@
       <c r="B48" s="9">
         <v>46</v>
       </c>
-      <c r="C48" s="111"/>
-      <c r="D48" s="111"/>
-      <c r="E48" s="111"/>
+      <c r="C48" s="110"/>
+      <c r="D48" s="110"/>
+      <c r="E48" s="110"/>
       <c r="F48" s="9" t="s">
         <v>57</v>
       </c>
@@ -5139,9 +5151,9 @@
       <c r="B49" s="9">
         <v>47</v>
       </c>
-      <c r="C49" s="111"/>
-      <c r="D49" s="111"/>
-      <c r="E49" s="111"/>
+      <c r="C49" s="110"/>
+      <c r="D49" s="110"/>
+      <c r="E49" s="110"/>
       <c r="F49" s="9" t="s">
         <v>58</v>
       </c>
@@ -5150,9 +5162,9 @@
       <c r="B50" s="9">
         <v>48</v>
       </c>
-      <c r="C50" s="111"/>
-      <c r="D50" s="111"/>
-      <c r="E50" s="111"/>
+      <c r="C50" s="110"/>
+      <c r="D50" s="110"/>
+      <c r="E50" s="110"/>
       <c r="F50" s="9" t="s">
         <v>59</v>
       </c>
@@ -5161,9 +5173,9 @@
       <c r="B51" s="9">
         <v>49</v>
       </c>
-      <c r="C51" s="111"/>
-      <c r="D51" s="111"/>
-      <c r="E51" s="111"/>
+      <c r="C51" s="110"/>
+      <c r="D51" s="110"/>
+      <c r="E51" s="110"/>
       <c r="F51" s="9" t="s">
         <v>60</v>
       </c>
@@ -5172,9 +5184,9 @@
       <c r="B52" s="9">
         <v>50</v>
       </c>
-      <c r="C52" s="111"/>
-      <c r="D52" s="111"/>
-      <c r="E52" s="111"/>
+      <c r="C52" s="110"/>
+      <c r="D52" s="110"/>
+      <c r="E52" s="110"/>
       <c r="F52" s="9" t="s">
         <v>61</v>
       </c>
@@ -5183,9 +5195,9 @@
       <c r="B53" s="9">
         <v>51</v>
       </c>
-      <c r="C53" s="111"/>
-      <c r="D53" s="111"/>
-      <c r="E53" s="111"/>
+      <c r="C53" s="110"/>
+      <c r="D53" s="110"/>
+      <c r="E53" s="110"/>
       <c r="F53" s="9" t="s">
         <v>467</v>
       </c>
@@ -5194,9 +5206,9 @@
       <c r="B54" s="9">
         <v>52</v>
       </c>
-      <c r="C54" s="111"/>
-      <c r="D54" s="111"/>
-      <c r="E54" s="111">
+      <c r="C54" s="110"/>
+      <c r="D54" s="110"/>
+      <c r="E54" s="110">
         <v>10</v>
       </c>
       <c r="F54" s="9" t="s">
@@ -5207,9 +5219,9 @@
       <c r="B55" s="9">
         <v>53</v>
       </c>
-      <c r="C55" s="111"/>
-      <c r="D55" s="111"/>
-      <c r="E55" s="111"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="110"/>
+      <c r="E55" s="110"/>
       <c r="F55" s="9" t="s">
         <v>63</v>
       </c>
@@ -5218,9 +5230,9 @@
       <c r="B56" s="9">
         <v>54</v>
       </c>
-      <c r="C56" s="111"/>
-      <c r="D56" s="111"/>
-      <c r="E56" s="111"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="110"/>
+      <c r="E56" s="110"/>
       <c r="F56" s="9" t="s">
         <v>64</v>
       </c>
@@ -5229,9 +5241,9 @@
       <c r="B57" s="9">
         <v>55</v>
       </c>
-      <c r="C57" s="111"/>
-      <c r="D57" s="111"/>
-      <c r="E57" s="111"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="110"/>
+      <c r="E57" s="110"/>
       <c r="F57" s="9" t="s">
         <v>65</v>
       </c>
@@ -5240,9 +5252,9 @@
       <c r="B58" s="9">
         <v>56</v>
       </c>
-      <c r="C58" s="111"/>
-      <c r="D58" s="111"/>
-      <c r="E58" s="111"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="110"/>
+      <c r="E58" s="110"/>
       <c r="F58" s="9" t="s">
         <v>66</v>
       </c>
@@ -5251,9 +5263,9 @@
       <c r="B59" s="9">
         <v>57</v>
       </c>
-      <c r="C59" s="111"/>
-      <c r="D59" s="111"/>
-      <c r="E59" s="111"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="110"/>
+      <c r="E59" s="110"/>
       <c r="F59" s="9" t="s">
         <v>67</v>
       </c>
@@ -5262,9 +5274,9 @@
       <c r="B60" s="9">
         <v>58</v>
       </c>
-      <c r="C60" s="111"/>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
+      <c r="C60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
       <c r="F60" s="9" t="s">
         <v>68</v>
       </c>
@@ -5273,9 +5285,9 @@
       <c r="B61" s="9">
         <v>59</v>
       </c>
-      <c r="C61" s="111"/>
-      <c r="D61" s="111"/>
-      <c r="E61" s="111"/>
+      <c r="C61" s="110"/>
+      <c r="D61" s="110"/>
+      <c r="E61" s="110"/>
       <c r="F61" s="9" t="s">
         <v>69</v>
       </c>
@@ -5284,9 +5296,9 @@
       <c r="B62" s="9">
         <v>60</v>
       </c>
-      <c r="C62" s="111"/>
-      <c r="D62" s="111"/>
-      <c r="E62" s="111"/>
+      <c r="C62" s="110"/>
+      <c r="D62" s="110"/>
+      <c r="E62" s="110"/>
       <c r="F62" s="9" t="s">
         <v>70</v>
       </c>
@@ -5295,9 +5307,9 @@
       <c r="B63" s="9">
         <v>61</v>
       </c>
-      <c r="C63" s="111"/>
-      <c r="D63" s="111"/>
-      <c r="E63" s="111"/>
+      <c r="C63" s="110"/>
+      <c r="D63" s="110"/>
+      <c r="E63" s="110"/>
       <c r="F63" s="9" t="s">
         <v>80</v>
       </c>
@@ -5306,9 +5318,9 @@
       <c r="B64" s="9">
         <v>62</v>
       </c>
-      <c r="C64" s="111"/>
-      <c r="D64" s="111"/>
-      <c r="E64" s="111"/>
+      <c r="C64" s="110"/>
+      <c r="D64" s="110"/>
+      <c r="E64" s="110"/>
       <c r="F64" s="9" t="s">
         <v>81</v>
       </c>
@@ -5317,9 +5329,9 @@
       <c r="B65" s="9">
         <v>63</v>
       </c>
-      <c r="C65" s="111"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="111"/>
+      <c r="C65" s="110"/>
+      <c r="D65" s="110"/>
+      <c r="E65" s="110"/>
       <c r="F65" s="9" t="s">
         <v>82</v>
       </c>
@@ -5328,9 +5340,9 @@
       <c r="B66" s="9">
         <v>64</v>
       </c>
-      <c r="C66" s="111"/>
-      <c r="D66" s="111"/>
-      <c r="E66" s="111"/>
+      <c r="C66" s="110"/>
+      <c r="D66" s="110"/>
+      <c r="E66" s="110"/>
       <c r="F66" s="9" t="s">
         <v>83</v>
       </c>
@@ -5339,9 +5351,9 @@
       <c r="B67" s="9">
         <v>65</v>
       </c>
-      <c r="C67" s="111"/>
-      <c r="D67" s="111"/>
-      <c r="E67" s="111"/>
+      <c r="C67" s="110"/>
+      <c r="D67" s="110"/>
+      <c r="E67" s="110"/>
       <c r="F67" s="9" t="s">
         <v>71</v>
       </c>
@@ -5350,9 +5362,9 @@
       <c r="B68" s="9">
         <v>66</v>
       </c>
-      <c r="C68" s="111"/>
-      <c r="D68" s="111"/>
-      <c r="E68" s="111"/>
+      <c r="C68" s="110"/>
+      <c r="D68" s="110"/>
+      <c r="E68" s="110"/>
       <c r="F68" s="9" t="s">
         <v>72</v>
       </c>
@@ -5361,9 +5373,9 @@
       <c r="B69" s="9">
         <v>67</v>
       </c>
-      <c r="C69" s="111"/>
-      <c r="D69" s="111"/>
-      <c r="E69" s="111"/>
+      <c r="C69" s="110"/>
+      <c r="D69" s="110"/>
+      <c r="E69" s="110"/>
       <c r="F69" s="9" t="s">
         <v>73</v>
       </c>
@@ -5372,9 +5384,9 @@
       <c r="B70" s="9">
         <v>68</v>
       </c>
-      <c r="C70" s="111"/>
-      <c r="D70" s="111"/>
-      <c r="E70" s="111"/>
+      <c r="C70" s="110"/>
+      <c r="D70" s="110"/>
+      <c r="E70" s="110"/>
       <c r="F70" s="9" t="s">
         <v>74</v>
       </c>
@@ -5383,9 +5395,9 @@
       <c r="B71" s="9">
         <v>69</v>
       </c>
-      <c r="C71" s="111"/>
-      <c r="D71" s="111"/>
-      <c r="E71" s="111"/>
+      <c r="C71" s="110"/>
+      <c r="D71" s="110"/>
+      <c r="E71" s="110"/>
       <c r="F71" s="9" t="s">
         <v>75</v>
       </c>
@@ -5394,9 +5406,9 @@
       <c r="B72" s="9">
         <v>70</v>
       </c>
-      <c r="C72" s="111"/>
-      <c r="D72" s="111"/>
-      <c r="E72" s="111"/>
+      <c r="C72" s="110"/>
+      <c r="D72" s="110"/>
+      <c r="E72" s="110"/>
       <c r="F72" s="9" t="s">
         <v>76</v>
       </c>
@@ -5405,9 +5417,9 @@
       <c r="B73" s="9">
         <v>71</v>
       </c>
-      <c r="C73" s="111"/>
-      <c r="D73" s="111"/>
-      <c r="E73" s="111"/>
+      <c r="C73" s="110"/>
+      <c r="D73" s="110"/>
+      <c r="E73" s="110"/>
       <c r="F73" s="9" t="s">
         <v>77</v>
       </c>
@@ -5416,9 +5428,9 @@
       <c r="B74" s="9">
         <v>72</v>
       </c>
-      <c r="C74" s="111"/>
-      <c r="D74" s="111"/>
-      <c r="E74" s="111"/>
+      <c r="C74" s="110"/>
+      <c r="D74" s="110"/>
+      <c r="E74" s="110"/>
       <c r="F74" s="9" t="s">
         <v>78</v>
       </c>
@@ -5427,9 +5439,9 @@
       <c r="B75" s="9">
         <v>73</v>
       </c>
-      <c r="C75" s="111"/>
-      <c r="D75" s="111"/>
-      <c r="E75" s="111"/>
+      <c r="C75" s="110"/>
+      <c r="D75" s="110"/>
+      <c r="E75" s="110"/>
       <c r="F75" s="9" t="s">
         <v>79</v>
       </c>
@@ -5438,9 +5450,9 @@
       <c r="B76" s="9">
         <v>74</v>
       </c>
-      <c r="C76" s="111"/>
-      <c r="D76" s="111"/>
-      <c r="E76" s="111"/>
+      <c r="C76" s="110"/>
+      <c r="D76" s="110"/>
+      <c r="E76" s="110"/>
       <c r="F76" s="9" t="s">
         <v>84</v>
       </c>
@@ -5449,9 +5461,9 @@
       <c r="B77" s="9">
         <v>75</v>
       </c>
-      <c r="C77" s="111"/>
-      <c r="D77" s="111"/>
-      <c r="E77" s="111"/>
+      <c r="C77" s="110"/>
+      <c r="D77" s="110"/>
+      <c r="E77" s="110"/>
       <c r="F77" s="9" t="s">
         <v>87</v>
       </c>
@@ -5460,9 +5472,9 @@
       <c r="B78" s="9">
         <v>76</v>
       </c>
-      <c r="C78" s="111"/>
-      <c r="D78" s="111"/>
-      <c r="E78" s="111"/>
+      <c r="C78" s="110"/>
+      <c r="D78" s="110"/>
+      <c r="E78" s="110"/>
       <c r="F78" s="9" t="s">
         <v>88</v>
       </c>
@@ -5471,9 +5483,9 @@
       <c r="B79" s="9">
         <v>77</v>
       </c>
-      <c r="C79" s="111"/>
-      <c r="D79" s="111"/>
-      <c r="E79" s="111"/>
+      <c r="C79" s="110"/>
+      <c r="D79" s="110"/>
+      <c r="E79" s="110"/>
       <c r="F79" s="9" t="s">
         <v>89</v>
       </c>
@@ -5482,9 +5494,9 @@
       <c r="B80" s="9">
         <v>78</v>
       </c>
-      <c r="C80" s="111"/>
-      <c r="D80" s="111"/>
-      <c r="E80" s="111"/>
+      <c r="C80" s="110"/>
+      <c r="D80" s="110"/>
+      <c r="E80" s="110"/>
       <c r="F80" s="9" t="s">
         <v>90</v>
       </c>
@@ -5493,9 +5505,9 @@
       <c r="B81" s="9">
         <v>79</v>
       </c>
-      <c r="C81" s="111"/>
-      <c r="D81" s="111"/>
-      <c r="E81" s="111"/>
+      <c r="C81" s="110"/>
+      <c r="D81" s="110"/>
+      <c r="E81" s="110"/>
       <c r="F81" s="9" t="s">
         <v>91</v>
       </c>
@@ -5504,9 +5516,9 @@
       <c r="B82" s="9">
         <v>80</v>
       </c>
-      <c r="C82" s="111"/>
-      <c r="D82" s="111"/>
-      <c r="E82" s="111"/>
+      <c r="C82" s="110"/>
+      <c r="D82" s="110"/>
+      <c r="E82" s="110"/>
       <c r="F82" s="9" t="s">
         <v>92</v>
       </c>
@@ -5515,9 +5527,9 @@
       <c r="B83" s="9">
         <v>81</v>
       </c>
-      <c r="C83" s="111"/>
-      <c r="D83" s="111"/>
-      <c r="E83" s="111"/>
+      <c r="C83" s="110"/>
+      <c r="D83" s="110"/>
+      <c r="E83" s="110"/>
       <c r="F83" s="9" t="s">
         <v>85</v>
       </c>
@@ -5526,9 +5538,9 @@
       <c r="B84" s="9">
         <v>82</v>
       </c>
-      <c r="C84" s="111"/>
-      <c r="D84" s="111"/>
-      <c r="E84" s="111"/>
+      <c r="C84" s="110"/>
+      <c r="D84" s="110"/>
+      <c r="E84" s="110"/>
       <c r="F84" s="9" t="s">
         <v>86</v>
       </c>
@@ -5537,9 +5549,9 @@
       <c r="B85" s="9">
         <v>83</v>
       </c>
-      <c r="C85" s="111"/>
-      <c r="D85" s="111"/>
-      <c r="E85" s="111"/>
+      <c r="C85" s="110"/>
+      <c r="D85" s="110"/>
+      <c r="E85" s="110"/>
       <c r="F85" s="9" t="s">
         <v>468</v>
       </c>
@@ -5548,9 +5560,9 @@
       <c r="B86" s="9">
         <v>84</v>
       </c>
-      <c r="C86" s="111"/>
-      <c r="D86" s="111"/>
-      <c r="E86" s="111"/>
+      <c r="C86" s="110"/>
+      <c r="D86" s="110"/>
+      <c r="E86" s="110"/>
       <c r="F86" s="9" t="s">
         <v>469</v>
       </c>
@@ -5559,9 +5571,9 @@
       <c r="B87" s="9">
         <v>85</v>
       </c>
-      <c r="C87" s="111"/>
-      <c r="D87" s="111"/>
-      <c r="E87" s="111">
+      <c r="C87" s="110"/>
+      <c r="D87" s="110"/>
+      <c r="E87" s="110">
         <v>11</v>
       </c>
       <c r="F87" s="9" t="s">
@@ -5572,9 +5584,9 @@
       <c r="B88" s="9">
         <v>86</v>
       </c>
-      <c r="C88" s="111"/>
-      <c r="D88" s="111"/>
-      <c r="E88" s="111"/>
+      <c r="C88" s="110"/>
+      <c r="D88" s="110"/>
+      <c r="E88" s="110"/>
       <c r="F88" s="9" t="s">
         <v>94</v>
       </c>
@@ -5583,9 +5595,9 @@
       <c r="B89" s="9">
         <v>87</v>
       </c>
-      <c r="C89" s="111"/>
-      <c r="D89" s="111"/>
-      <c r="E89" s="111"/>
+      <c r="C89" s="110"/>
+      <c r="D89" s="110"/>
+      <c r="E89" s="110"/>
       <c r="F89" s="9" t="s">
         <v>95</v>
       </c>
@@ -5594,9 +5606,9 @@
       <c r="B90" s="9">
         <v>88</v>
       </c>
-      <c r="C90" s="111"/>
-      <c r="D90" s="111"/>
-      <c r="E90" s="111"/>
+      <c r="C90" s="110"/>
+      <c r="D90" s="110"/>
+      <c r="E90" s="110"/>
       <c r="F90" s="9" t="s">
         <v>96</v>
       </c>
@@ -5605,9 +5617,9 @@
       <c r="B91" s="9">
         <v>89</v>
       </c>
-      <c r="C91" s="111"/>
-      <c r="D91" s="111"/>
-      <c r="E91" s="111"/>
+      <c r="C91" s="110"/>
+      <c r="D91" s="110"/>
+      <c r="E91" s="110"/>
       <c r="F91" s="9" t="s">
         <v>470</v>
       </c>
@@ -5616,9 +5628,9 @@
       <c r="B92" s="9">
         <v>90</v>
       </c>
-      <c r="C92" s="111"/>
-      <c r="D92" s="111"/>
-      <c r="E92" s="111">
+      <c r="C92" s="110"/>
+      <c r="D92" s="110"/>
+      <c r="E92" s="110">
         <v>12</v>
       </c>
       <c r="F92" s="9" t="s">
@@ -5629,9 +5641,9 @@
       <c r="B93" s="9">
         <v>91</v>
       </c>
-      <c r="C93" s="111"/>
-      <c r="D93" s="111"/>
-      <c r="E93" s="111"/>
+      <c r="C93" s="110"/>
+      <c r="D93" s="110"/>
+      <c r="E93" s="110"/>
       <c r="F93" s="9" t="s">
         <v>98</v>
       </c>
@@ -5643,9 +5655,9 @@
       <c r="B94" s="9">
         <v>92</v>
       </c>
-      <c r="C94" s="111"/>
-      <c r="D94" s="111"/>
-      <c r="E94" s="111"/>
+      <c r="C94" s="110"/>
+      <c r="D94" s="110"/>
+      <c r="E94" s="110"/>
       <c r="F94" s="9" t="s">
         <v>99</v>
       </c>
@@ -5654,9 +5666,9 @@
       <c r="B95" s="9">
         <v>93</v>
       </c>
-      <c r="C95" s="111"/>
-      <c r="D95" s="111"/>
-      <c r="E95" s="111"/>
+      <c r="C95" s="110"/>
+      <c r="D95" s="110"/>
+      <c r="E95" s="110"/>
       <c r="F95" s="9" t="s">
         <v>100</v>
       </c>
@@ -5665,9 +5677,9 @@
       <c r="B96" s="9">
         <v>94</v>
       </c>
-      <c r="C96" s="111"/>
-      <c r="D96" s="111"/>
-      <c r="E96" s="111"/>
+      <c r="C96" s="110"/>
+      <c r="D96" s="110"/>
+      <c r="E96" s="110"/>
       <c r="F96" s="9" t="s">
         <v>101</v>
       </c>
@@ -5676,9 +5688,9 @@
       <c r="B97" s="9">
         <v>95</v>
       </c>
-      <c r="C97" s="111"/>
-      <c r="D97" s="111"/>
-      <c r="E97" s="111"/>
+      <c r="C97" s="110"/>
+      <c r="D97" s="110"/>
+      <c r="E97" s="110"/>
       <c r="F97" s="9" t="s">
         <v>102</v>
       </c>
@@ -5687,9 +5699,9 @@
       <c r="B98" s="9">
         <v>96</v>
       </c>
-      <c r="C98" s="111"/>
-      <c r="D98" s="111"/>
-      <c r="E98" s="111"/>
+      <c r="C98" s="110"/>
+      <c r="D98" s="110"/>
+      <c r="E98" s="110"/>
       <c r="F98" s="9" t="s">
         <v>103</v>
       </c>
@@ -5698,9 +5710,9 @@
       <c r="B99" s="9">
         <v>97</v>
       </c>
-      <c r="C99" s="111"/>
-      <c r="D99" s="111"/>
-      <c r="E99" s="111">
+      <c r="C99" s="110"/>
+      <c r="D99" s="110"/>
+      <c r="E99" s="110">
         <v>13</v>
       </c>
       <c r="F99" s="9" t="s">
@@ -5711,9 +5723,9 @@
       <c r="B100" s="9">
         <v>98</v>
       </c>
-      <c r="C100" s="111"/>
-      <c r="D100" s="111"/>
-      <c r="E100" s="111"/>
+      <c r="C100" s="110"/>
+      <c r="D100" s="110"/>
+      <c r="E100" s="110"/>
       <c r="F100" s="9" t="s">
         <v>105</v>
       </c>
@@ -5722,9 +5734,9 @@
       <c r="B101" s="9">
         <v>99</v>
       </c>
-      <c r="C101" s="111"/>
-      <c r="D101" s="111"/>
-      <c r="E101" s="111"/>
+      <c r="C101" s="110"/>
+      <c r="D101" s="110"/>
+      <c r="E101" s="110"/>
       <c r="F101" s="9" t="s">
         <v>106</v>
       </c>
@@ -5733,9 +5745,9 @@
       <c r="B102" s="9">
         <v>100</v>
       </c>
-      <c r="C102" s="111"/>
-      <c r="D102" s="111"/>
-      <c r="E102" s="111"/>
+      <c r="C102" s="110"/>
+      <c r="D102" s="110"/>
+      <c r="E102" s="110"/>
       <c r="F102" s="9" t="s">
         <v>107</v>
       </c>
@@ -5744,9 +5756,9 @@
       <c r="B103" s="9">
         <v>101</v>
       </c>
-      <c r="C103" s="111"/>
-      <c r="D103" s="111"/>
-      <c r="E103" s="111"/>
+      <c r="C103" s="110"/>
+      <c r="D103" s="110"/>
+      <c r="E103" s="110"/>
       <c r="F103" s="9" t="s">
         <v>108</v>
       </c>
@@ -5755,9 +5767,9 @@
       <c r="B104" s="9">
         <v>102</v>
       </c>
-      <c r="C104" s="111"/>
-      <c r="D104" s="111"/>
-      <c r="E104" s="111"/>
+      <c r="C104" s="110"/>
+      <c r="D104" s="110"/>
+      <c r="E104" s="110"/>
       <c r="F104" s="9" t="s">
         <v>109</v>
       </c>
@@ -5766,9 +5778,9 @@
       <c r="B105" s="9">
         <v>103</v>
       </c>
-      <c r="C105" s="111"/>
-      <c r="D105" s="111"/>
-      <c r="E105" s="111"/>
+      <c r="C105" s="110"/>
+      <c r="D105" s="110"/>
+      <c r="E105" s="110"/>
       <c r="F105" s="9" t="s">
         <v>471</v>
       </c>
@@ -5777,9 +5789,9 @@
       <c r="B106" s="9">
         <v>104</v>
       </c>
-      <c r="C106" s="111"/>
-      <c r="D106" s="111"/>
-      <c r="E106" s="111"/>
+      <c r="C106" s="110"/>
+      <c r="D106" s="110"/>
+      <c r="E106" s="110"/>
       <c r="F106" s="9" t="s">
         <v>472</v>
       </c>
@@ -5788,9 +5800,9 @@
       <c r="B107" s="9">
         <v>105</v>
       </c>
-      <c r="C107" s="111"/>
-      <c r="D107" s="111"/>
-      <c r="E107" s="111"/>
+      <c r="C107" s="110"/>
+      <c r="D107" s="110"/>
+      <c r="E107" s="110"/>
       <c r="F107" s="9" t="s">
         <v>110</v>
       </c>
@@ -5799,9 +5811,9 @@
       <c r="B108" s="9">
         <v>106</v>
       </c>
-      <c r="C108" s="111"/>
-      <c r="D108" s="111"/>
-      <c r="E108" s="111">
+      <c r="C108" s="110"/>
+      <c r="D108" s="110"/>
+      <c r="E108" s="110">
         <v>14</v>
       </c>
       <c r="F108" s="9" t="s">
@@ -5815,9 +5827,9 @@
       <c r="B109" s="9">
         <v>107</v>
       </c>
-      <c r="C109" s="111"/>
-      <c r="D109" s="111"/>
-      <c r="E109" s="111"/>
+      <c r="C109" s="110"/>
+      <c r="D109" s="110"/>
+      <c r="E109" s="110"/>
       <c r="F109" s="9" t="s">
         <v>112</v>
       </c>
@@ -5829,9 +5841,9 @@
       <c r="B110" s="9">
         <v>108</v>
       </c>
-      <c r="C110" s="111"/>
-      <c r="D110" s="111"/>
-      <c r="E110" s="111"/>
+      <c r="C110" s="110"/>
+      <c r="D110" s="110"/>
+      <c r="E110" s="110"/>
       <c r="F110" s="9" t="s">
         <v>113</v>
       </c>
@@ -5843,9 +5855,9 @@
       <c r="B111" s="9">
         <v>109</v>
       </c>
-      <c r="C111" s="111"/>
-      <c r="D111" s="111"/>
-      <c r="E111" s="111"/>
+      <c r="C111" s="110"/>
+      <c r="D111" s="110"/>
+      <c r="E111" s="110"/>
       <c r="F111" s="9" t="s">
         <v>114</v>
       </c>
@@ -5857,9 +5869,9 @@
       <c r="B112" s="9">
         <v>110</v>
       </c>
-      <c r="C112" s="111"/>
-      <c r="D112" s="111"/>
-      <c r="E112" s="111"/>
+      <c r="C112" s="110"/>
+      <c r="D112" s="110"/>
+      <c r="E112" s="110"/>
       <c r="F112" s="9" t="s">
         <v>115</v>
       </c>
@@ -5871,9 +5883,9 @@
       <c r="B113" s="9">
         <v>111</v>
       </c>
-      <c r="C113" s="111"/>
-      <c r="D113" s="111"/>
-      <c r="E113" s="111"/>
+      <c r="C113" s="110"/>
+      <c r="D113" s="110"/>
+      <c r="E113" s="110"/>
       <c r="F113" s="9" t="s">
         <v>116</v>
       </c>
@@ -5885,9 +5897,9 @@
       <c r="B114" s="9">
         <v>112</v>
       </c>
-      <c r="C114" s="111"/>
-      <c r="D114" s="111"/>
-      <c r="E114" s="111"/>
+      <c r="C114" s="110"/>
+      <c r="D114" s="110"/>
+      <c r="E114" s="110"/>
       <c r="F114" s="9" t="s">
         <v>448</v>
       </c>
@@ -5902,9 +5914,9 @@
       <c r="B115" s="9">
         <v>113</v>
       </c>
-      <c r="C115" s="111"/>
-      <c r="D115" s="111"/>
-      <c r="E115" s="111"/>
+      <c r="C115" s="110"/>
+      <c r="D115" s="110"/>
+      <c r="E115" s="110"/>
       <c r="F115" s="9" t="s">
         <v>451</v>
       </c>
@@ -5916,9 +5928,9 @@
       <c r="B116" s="9">
         <v>114</v>
       </c>
-      <c r="C116" s="111"/>
-      <c r="D116" s="111"/>
-      <c r="E116" s="111"/>
+      <c r="C116" s="110"/>
+      <c r="D116" s="110"/>
+      <c r="E116" s="110"/>
       <c r="F116" s="9" t="s">
         <v>452</v>
       </c>
@@ -5930,9 +5942,9 @@
       <c r="B117" s="9">
         <v>115</v>
       </c>
-      <c r="C117" s="111"/>
-      <c r="D117" s="111"/>
-      <c r="E117" s="111"/>
+      <c r="C117" s="110"/>
+      <c r="D117" s="110"/>
+      <c r="E117" s="110"/>
       <c r="F117" s="9" t="s">
         <v>453</v>
       </c>
@@ -5944,9 +5956,9 @@
       <c r="B118" s="9">
         <v>116</v>
       </c>
-      <c r="C118" s="111"/>
-      <c r="D118" s="111"/>
-      <c r="E118" s="111">
+      <c r="C118" s="110"/>
+      <c r="D118" s="110"/>
+      <c r="E118" s="110">
         <v>20</v>
       </c>
       <c r="F118" s="9" t="s">
@@ -5957,9 +5969,9 @@
       <c r="B119" s="9">
         <v>117</v>
       </c>
-      <c r="C119" s="111"/>
-      <c r="D119" s="111"/>
-      <c r="E119" s="111"/>
+      <c r="C119" s="110"/>
+      <c r="D119" s="110"/>
+      <c r="E119" s="110"/>
       <c r="F119" s="9" t="s">
         <v>118</v>
       </c>
@@ -5968,9 +5980,9 @@
       <c r="B120" s="9">
         <v>118</v>
       </c>
-      <c r="C120" s="111"/>
-      <c r="D120" s="111"/>
-      <c r="E120" s="111"/>
+      <c r="C120" s="110"/>
+      <c r="D120" s="110"/>
+      <c r="E120" s="110"/>
       <c r="F120" s="9" t="s">
         <v>119</v>
       </c>
@@ -5979,9 +5991,9 @@
       <c r="B121" s="9">
         <v>119</v>
       </c>
-      <c r="C121" s="111"/>
-      <c r="D121" s="111"/>
-      <c r="E121" s="111"/>
+      <c r="C121" s="110"/>
+      <c r="D121" s="110"/>
+      <c r="E121" s="110"/>
       <c r="F121" s="9" t="s">
         <v>120</v>
       </c>
@@ -5990,9 +6002,9 @@
       <c r="B122" s="9">
         <v>120</v>
       </c>
-      <c r="C122" s="111"/>
-      <c r="D122" s="111"/>
-      <c r="E122" s="111"/>
+      <c r="C122" s="110"/>
+      <c r="D122" s="110"/>
+      <c r="E122" s="110"/>
       <c r="F122" s="9" t="s">
         <v>473</v>
       </c>
@@ -6001,9 +6013,9 @@
       <c r="B123" s="9">
         <v>121</v>
       </c>
-      <c r="C123" s="111"/>
-      <c r="D123" s="111"/>
-      <c r="E123" s="111"/>
+      <c r="C123" s="110"/>
+      <c r="D123" s="110"/>
+      <c r="E123" s="110"/>
       <c r="F123" s="9" t="s">
         <v>474</v>
       </c>
@@ -6021,9 +6033,9 @@
       <c r="B124" s="9">
         <v>122</v>
       </c>
-      <c r="C124" s="111"/>
-      <c r="D124" s="111"/>
-      <c r="E124" s="111"/>
+      <c r="C124" s="110"/>
+      <c r="D124" s="110"/>
+      <c r="E124" s="110"/>
       <c r="F124" s="9" t="s">
         <v>121</v>
       </c>
@@ -6032,9 +6044,9 @@
       <c r="B125" s="9">
         <v>123</v>
       </c>
-      <c r="C125" s="111"/>
-      <c r="D125" s="111"/>
-      <c r="E125" s="111"/>
+      <c r="C125" s="110"/>
+      <c r="D125" s="110"/>
+      <c r="E125" s="110"/>
       <c r="F125" s="9" t="s">
         <v>122</v>
       </c>
@@ -6043,9 +6055,9 @@
       <c r="B126" s="9">
         <v>124</v>
       </c>
-      <c r="C126" s="111"/>
-      <c r="D126" s="111"/>
-      <c r="E126" s="111"/>
+      <c r="C126" s="110"/>
+      <c r="D126" s="110"/>
+      <c r="E126" s="110"/>
       <c r="F126" s="9" t="s">
         <v>123</v>
       </c>
@@ -6054,9 +6066,9 @@
       <c r="B127" s="9">
         <v>125</v>
       </c>
-      <c r="C127" s="111"/>
-      <c r="D127" s="111"/>
-      <c r="E127" s="111">
+      <c r="C127" s="110"/>
+      <c r="D127" s="110"/>
+      <c r="E127" s="110">
         <v>30</v>
       </c>
       <c r="F127" s="9" t="s">
@@ -6067,9 +6079,9 @@
       <c r="B128" s="9">
         <v>126</v>
       </c>
-      <c r="C128" s="111"/>
-      <c r="D128" s="111"/>
-      <c r="E128" s="111"/>
+      <c r="C128" s="110"/>
+      <c r="D128" s="110"/>
+      <c r="E128" s="110"/>
       <c r="F128" s="9" t="s">
         <v>125</v>
       </c>
@@ -6078,9 +6090,9 @@
       <c r="B129" s="9">
         <v>127</v>
       </c>
-      <c r="C129" s="111"/>
-      <c r="D129" s="111"/>
-      <c r="E129" s="111"/>
+      <c r="C129" s="110"/>
+      <c r="D129" s="110"/>
+      <c r="E129" s="110"/>
       <c r="F129" s="9" t="s">
         <v>126</v>
       </c>
@@ -6089,9 +6101,9 @@
       <c r="B130" s="9">
         <v>128</v>
       </c>
-      <c r="C130" s="111"/>
-      <c r="D130" s="111"/>
-      <c r="E130" s="111"/>
+      <c r="C130" s="110"/>
+      <c r="D130" s="110"/>
+      <c r="E130" s="110"/>
       <c r="F130" s="9" t="s">
         <v>127</v>
       </c>
@@ -6100,9 +6112,9 @@
       <c r="B131" s="9">
         <v>129</v>
       </c>
-      <c r="C131" s="111"/>
-      <c r="D131" s="111"/>
-      <c r="E131" s="111"/>
+      <c r="C131" s="110"/>
+      <c r="D131" s="110"/>
+      <c r="E131" s="110"/>
       <c r="F131" s="9" t="s">
         <v>128</v>
       </c>
@@ -6111,9 +6123,9 @@
       <c r="B132" s="9">
         <v>130</v>
       </c>
-      <c r="C132" s="111"/>
-      <c r="D132" s="111"/>
-      <c r="E132" s="111"/>
+      <c r="C132" s="110"/>
+      <c r="D132" s="110"/>
+      <c r="E132" s="110"/>
       <c r="F132" s="9" t="s">
         <v>475</v>
       </c>
@@ -6122,8 +6134,8 @@
       <c r="B133" s="9">
         <v>131</v>
       </c>
-      <c r="C133" s="111"/>
-      <c r="D133" s="111"/>
+      <c r="C133" s="110"/>
+      <c r="D133" s="110"/>
       <c r="E133" s="26">
         <v>37</v>
       </c>
@@ -6135,9 +6147,9 @@
       <c r="B134" s="9">
         <v>132</v>
       </c>
-      <c r="C134" s="111"/>
-      <c r="D134" s="111"/>
-      <c r="E134" s="111">
+      <c r="C134" s="110"/>
+      <c r="D134" s="110"/>
+      <c r="E134" s="110">
         <v>38</v>
       </c>
       <c r="F134" s="9" t="s">
@@ -6148,9 +6160,9 @@
       <c r="B135" s="9">
         <v>133</v>
       </c>
-      <c r="C135" s="111"/>
-      <c r="D135" s="111"/>
-      <c r="E135" s="111"/>
+      <c r="C135" s="110"/>
+      <c r="D135" s="110"/>
+      <c r="E135" s="110"/>
       <c r="F135" s="9" t="s">
         <v>131</v>
       </c>
@@ -6159,9 +6171,9 @@
       <c r="B136" s="9">
         <v>134</v>
       </c>
-      <c r="C136" s="111"/>
-      <c r="D136" s="111"/>
-      <c r="E136" s="111" t="s">
+      <c r="C136" s="110"/>
+      <c r="D136" s="110"/>
+      <c r="E136" s="110" t="s">
         <v>224</v>
       </c>
       <c r="F136" s="9" t="s">
@@ -6172,9 +6184,9 @@
       <c r="B137" s="9">
         <v>135</v>
       </c>
-      <c r="C137" s="111"/>
-      <c r="D137" s="111"/>
-      <c r="E137" s="111"/>
+      <c r="C137" s="110"/>
+      <c r="D137" s="110"/>
+      <c r="E137" s="110"/>
       <c r="F137" s="9" t="s">
         <v>133</v>
       </c>
@@ -6183,10 +6195,10 @@
       <c r="B138" s="9">
         <v>136</v>
       </c>
-      <c r="C138" s="112" t="s">
+      <c r="C138" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="D138" s="112" t="s">
+      <c r="D138" s="109" t="s">
         <v>225</v>
       </c>
       <c r="E138" s="27">
@@ -6200,9 +6212,9 @@
       <c r="B139" s="9">
         <v>137</v>
       </c>
-      <c r="C139" s="112"/>
-      <c r="D139" s="112"/>
-      <c r="E139" s="112">
+      <c r="C139" s="109"/>
+      <c r="D139" s="109"/>
+      <c r="E139" s="109">
         <v>1</v>
       </c>
       <c r="F139" s="9" t="s">
@@ -6213,9 +6225,9 @@
       <c r="B140" s="9">
         <v>138</v>
       </c>
-      <c r="C140" s="112"/>
-      <c r="D140" s="112"/>
-      <c r="E140" s="112"/>
+      <c r="C140" s="109"/>
+      <c r="D140" s="109"/>
+      <c r="E140" s="109"/>
       <c r="F140" s="9" t="s">
         <v>136</v>
       </c>
@@ -6224,9 +6236,9 @@
       <c r="B141" s="9">
         <v>139</v>
       </c>
-      <c r="C141" s="112"/>
-      <c r="D141" s="112"/>
-      <c r="E141" s="112"/>
+      <c r="C141" s="109"/>
+      <c r="D141" s="109"/>
+      <c r="E141" s="109"/>
       <c r="F141" s="9" t="s">
         <v>137</v>
       </c>
@@ -6235,9 +6247,9 @@
       <c r="B142" s="9">
         <v>140</v>
       </c>
-      <c r="C142" s="112"/>
-      <c r="D142" s="112"/>
-      <c r="E142" s="112"/>
+      <c r="C142" s="109"/>
+      <c r="D142" s="109"/>
+      <c r="E142" s="109"/>
       <c r="F142" s="9" t="s">
         <v>138</v>
       </c>
@@ -6246,9 +6258,9 @@
       <c r="B143" s="9">
         <v>141</v>
       </c>
-      <c r="C143" s="112"/>
-      <c r="D143" s="112"/>
-      <c r="E143" s="112"/>
+      <c r="C143" s="109"/>
+      <c r="D143" s="109"/>
+      <c r="E143" s="109"/>
       <c r="F143" s="9" t="s">
         <v>139</v>
       </c>
@@ -6257,9 +6269,9 @@
       <c r="B144" s="9">
         <v>142</v>
       </c>
-      <c r="C144" s="112"/>
-      <c r="D144" s="112"/>
-      <c r="E144" s="112"/>
+      <c r="C144" s="109"/>
+      <c r="D144" s="109"/>
+      <c r="E144" s="109"/>
       <c r="F144" s="9" t="s">
         <v>140</v>
       </c>
@@ -6268,9 +6280,9 @@
       <c r="B145" s="9">
         <v>143</v>
       </c>
-      <c r="C145" s="112"/>
-      <c r="D145" s="112"/>
-      <c r="E145" s="112"/>
+      <c r="C145" s="109"/>
+      <c r="D145" s="109"/>
+      <c r="E145" s="109"/>
       <c r="F145" s="9" t="s">
         <v>141</v>
       </c>
@@ -6279,9 +6291,9 @@
       <c r="B146" s="9">
         <v>144</v>
       </c>
-      <c r="C146" s="112"/>
-      <c r="D146" s="112"/>
-      <c r="E146" s="112"/>
+      <c r="C146" s="109"/>
+      <c r="D146" s="109"/>
+      <c r="E146" s="109"/>
       <c r="F146" s="9" t="s">
         <v>142</v>
       </c>
@@ -6290,9 +6302,9 @@
       <c r="B147" s="9">
         <v>145</v>
       </c>
-      <c r="C147" s="112"/>
-      <c r="D147" s="112"/>
-      <c r="E147" s="112"/>
+      <c r="C147" s="109"/>
+      <c r="D147" s="109"/>
+      <c r="E147" s="109"/>
       <c r="F147" s="9" t="s">
         <v>143</v>
       </c>
@@ -6301,9 +6313,9 @@
       <c r="B148" s="9">
         <v>146</v>
       </c>
-      <c r="C148" s="112"/>
-      <c r="D148" s="112"/>
-      <c r="E148" s="112"/>
+      <c r="C148" s="109"/>
+      <c r="D148" s="109"/>
+      <c r="E148" s="109"/>
       <c r="F148" s="9" t="s">
         <v>144</v>
       </c>
@@ -6312,9 +6324,9 @@
       <c r="B149" s="9">
         <v>147</v>
       </c>
-      <c r="C149" s="112"/>
-      <c r="D149" s="112"/>
-      <c r="E149" s="112"/>
+      <c r="C149" s="109"/>
+      <c r="D149" s="109"/>
+      <c r="E149" s="109"/>
       <c r="F149" s="9" t="s">
         <v>147</v>
       </c>
@@ -6323,9 +6335,9 @@
       <c r="B150" s="9">
         <v>148</v>
       </c>
-      <c r="C150" s="112"/>
-      <c r="D150" s="112"/>
-      <c r="E150" s="112"/>
+      <c r="C150" s="109"/>
+      <c r="D150" s="109"/>
+      <c r="E150" s="109"/>
       <c r="F150" s="9" t="s">
         <v>148</v>
       </c>
@@ -6334,9 +6346,9 @@
       <c r="B151" s="9">
         <v>149</v>
       </c>
-      <c r="C151" s="112"/>
-      <c r="D151" s="112"/>
-      <c r="E151" s="112"/>
+      <c r="C151" s="109"/>
+      <c r="D151" s="109"/>
+      <c r="E151" s="109"/>
       <c r="F151" s="9" t="s">
         <v>150</v>
       </c>
@@ -6345,9 +6357,9 @@
       <c r="B152" s="9">
         <v>150</v>
       </c>
-      <c r="C152" s="112"/>
-      <c r="D152" s="112"/>
-      <c r="E152" s="112"/>
+      <c r="C152" s="109"/>
+      <c r="D152" s="109"/>
+      <c r="E152" s="109"/>
       <c r="F152" s="9" t="s">
         <v>151</v>
       </c>
@@ -6356,9 +6368,9 @@
       <c r="B153" s="9">
         <v>151</v>
       </c>
-      <c r="C153" s="112"/>
-      <c r="D153" s="112"/>
-      <c r="E153" s="112"/>
+      <c r="C153" s="109"/>
+      <c r="D153" s="109"/>
+      <c r="E153" s="109"/>
       <c r="F153" s="9" t="s">
         <v>152</v>
       </c>
@@ -6370,9 +6382,9 @@
       <c r="B154" s="9">
         <v>152</v>
       </c>
-      <c r="C154" s="112"/>
-      <c r="D154" s="112"/>
-      <c r="E154" s="112"/>
+      <c r="C154" s="109"/>
+      <c r="D154" s="109"/>
+      <c r="E154" s="109"/>
       <c r="F154" s="9" t="s">
         <v>153</v>
       </c>
@@ -6381,9 +6393,9 @@
       <c r="B155" s="9">
         <v>153</v>
       </c>
-      <c r="C155" s="112"/>
-      <c r="D155" s="112"/>
-      <c r="E155" s="112"/>
+      <c r="C155" s="109"/>
+      <c r="D155" s="109"/>
+      <c r="E155" s="109"/>
       <c r="F155" s="9" t="s">
         <v>145</v>
       </c>
@@ -6392,9 +6404,9 @@
       <c r="B156" s="9">
         <v>154</v>
       </c>
-      <c r="C156" s="112"/>
-      <c r="D156" s="112"/>
-      <c r="E156" s="112"/>
+      <c r="C156" s="109"/>
+      <c r="D156" s="109"/>
+      <c r="E156" s="109"/>
       <c r="F156" s="9" t="s">
         <v>146</v>
       </c>
@@ -6403,9 +6415,9 @@
       <c r="B157" s="9">
         <v>155</v>
       </c>
-      <c r="C157" s="112"/>
-      <c r="D157" s="112"/>
-      <c r="E157" s="112"/>
+      <c r="C157" s="109"/>
+      <c r="D157" s="109"/>
+      <c r="E157" s="109"/>
       <c r="F157" s="9" t="s">
         <v>149</v>
       </c>
@@ -6423,9 +6435,9 @@
       <c r="B158" s="9">
         <v>156</v>
       </c>
-      <c r="C158" s="112"/>
-      <c r="D158" s="112"/>
-      <c r="E158" s="112"/>
+      <c r="C158" s="109"/>
+      <c r="D158" s="109"/>
+      <c r="E158" s="109"/>
       <c r="F158" s="9" t="s">
         <v>154</v>
       </c>
@@ -6434,9 +6446,9 @@
       <c r="B159" s="9">
         <v>157</v>
       </c>
-      <c r="C159" s="112"/>
-      <c r="D159" s="112"/>
-      <c r="E159" s="112"/>
+      <c r="C159" s="109"/>
+      <c r="D159" s="109"/>
+      <c r="E159" s="109"/>
       <c r="F159" s="9" t="s">
         <v>155</v>
       </c>
@@ -6445,9 +6457,9 @@
       <c r="B160" s="9">
         <v>158</v>
       </c>
-      <c r="C160" s="112"/>
-      <c r="D160" s="112"/>
-      <c r="E160" s="112"/>
+      <c r="C160" s="109"/>
+      <c r="D160" s="109"/>
+      <c r="E160" s="109"/>
       <c r="F160" s="9" t="s">
         <v>476</v>
       </c>
@@ -6456,9 +6468,9 @@
       <c r="B161" s="9">
         <v>159</v>
       </c>
-      <c r="C161" s="112"/>
-      <c r="D161" s="112"/>
-      <c r="E161" s="112"/>
+      <c r="C161" s="109"/>
+      <c r="D161" s="109"/>
+      <c r="E161" s="109"/>
       <c r="F161" s="9" t="s">
         <v>477</v>
       </c>
@@ -6467,9 +6479,9 @@
       <c r="B162" s="9">
         <v>160</v>
       </c>
-      <c r="C162" s="112"/>
-      <c r="D162" s="112"/>
-      <c r="E162" s="112">
+      <c r="C162" s="109"/>
+      <c r="D162" s="109"/>
+      <c r="E162" s="109">
         <v>2</v>
       </c>
       <c r="F162" s="9" t="s">
@@ -6480,9 +6492,9 @@
       <c r="B163" s="9">
         <v>161</v>
       </c>
-      <c r="C163" s="112"/>
-      <c r="D163" s="112"/>
-      <c r="E163" s="112"/>
+      <c r="C163" s="109"/>
+      <c r="D163" s="109"/>
+      <c r="E163" s="109"/>
       <c r="F163" s="9" t="s">
         <v>157</v>
       </c>
@@ -6491,9 +6503,9 @@
       <c r="B164" s="9">
         <v>162</v>
       </c>
-      <c r="C164" s="112"/>
-      <c r="D164" s="112"/>
-      <c r="E164" s="112"/>
+      <c r="C164" s="109"/>
+      <c r="D164" s="109"/>
+      <c r="E164" s="109"/>
       <c r="F164" s="9" t="s">
         <v>158</v>
       </c>
@@ -6502,9 +6514,9 @@
       <c r="B165" s="9">
         <v>163</v>
       </c>
-      <c r="C165" s="112"/>
-      <c r="D165" s="112"/>
-      <c r="E165" s="112">
+      <c r="C165" s="109"/>
+      <c r="D165" s="109"/>
+      <c r="E165" s="109">
         <v>3</v>
       </c>
       <c r="F165" s="9" t="s">
@@ -6515,9 +6527,9 @@
       <c r="B166" s="9">
         <v>164</v>
       </c>
-      <c r="C166" s="112"/>
-      <c r="D166" s="112"/>
-      <c r="E166" s="112"/>
+      <c r="C166" s="109"/>
+      <c r="D166" s="109"/>
+      <c r="E166" s="109"/>
       <c r="F166" s="9" t="s">
         <v>480</v>
       </c>
@@ -6532,9 +6544,9 @@
       <c r="B167" s="9">
         <v>165</v>
       </c>
-      <c r="C167" s="112"/>
-      <c r="D167" s="112"/>
-      <c r="E167" s="112"/>
+      <c r="C167" s="109"/>
+      <c r="D167" s="109"/>
+      <c r="E167" s="109"/>
       <c r="F167" s="9" t="s">
         <v>478</v>
       </c>
@@ -6543,9 +6555,9 @@
       <c r="B168" s="9">
         <v>166</v>
       </c>
-      <c r="C168" s="112"/>
-      <c r="D168" s="112"/>
-      <c r="E168" s="112"/>
+      <c r="C168" s="109"/>
+      <c r="D168" s="109"/>
+      <c r="E168" s="109"/>
       <c r="F168" s="9" t="s">
         <v>479</v>
       </c>
@@ -6554,9 +6566,9 @@
       <c r="B169" s="9">
         <v>167</v>
       </c>
-      <c r="C169" s="112"/>
-      <c r="D169" s="112"/>
-      <c r="E169" s="112">
+      <c r="C169" s="109"/>
+      <c r="D169" s="109"/>
+      <c r="E169" s="109">
         <v>4</v>
       </c>
       <c r="F169" s="9" t="s">
@@ -6576,9 +6588,9 @@
       <c r="B170" s="9">
         <v>168</v>
       </c>
-      <c r="C170" s="112"/>
-      <c r="D170" s="112"/>
-      <c r="E170" s="112"/>
+      <c r="C170" s="109"/>
+      <c r="D170" s="109"/>
+      <c r="E170" s="109"/>
       <c r="F170" s="9" t="s">
         <v>163</v>
       </c>
@@ -6590,9 +6602,9 @@
       <c r="B171" s="9">
         <v>169</v>
       </c>
-      <c r="C171" s="112"/>
-      <c r="D171" s="112"/>
-      <c r="E171" s="112"/>
+      <c r="C171" s="109"/>
+      <c r="D171" s="109"/>
+      <c r="E171" s="109"/>
       <c r="F171" s="9" t="s">
         <v>164</v>
       </c>
@@ -6604,9 +6616,9 @@
       <c r="B172" s="9">
         <v>170</v>
       </c>
-      <c r="C172" s="112"/>
-      <c r="D172" s="112"/>
-      <c r="E172" s="112"/>
+      <c r="C172" s="109"/>
+      <c r="D172" s="109"/>
+      <c r="E172" s="109"/>
       <c r="F172" s="9" t="s">
         <v>165</v>
       </c>
@@ -6618,9 +6630,9 @@
       <c r="B173" s="9">
         <v>171</v>
       </c>
-      <c r="C173" s="112"/>
-      <c r="D173" s="112"/>
-      <c r="E173" s="112"/>
+      <c r="C173" s="109"/>
+      <c r="D173" s="109"/>
+      <c r="E173" s="109"/>
       <c r="F173" s="9" t="s">
         <v>166</v>
       </c>
@@ -6632,9 +6644,9 @@
       <c r="B174" s="9">
         <v>172</v>
       </c>
-      <c r="C174" s="112"/>
-      <c r="D174" s="112"/>
-      <c r="E174" s="112"/>
+      <c r="C174" s="109"/>
+      <c r="D174" s="109"/>
+      <c r="E174" s="109"/>
       <c r="F174" s="9" t="s">
         <v>167</v>
       </c>
@@ -6646,9 +6658,9 @@
       <c r="B175" s="9">
         <v>173</v>
       </c>
-      <c r="C175" s="112"/>
-      <c r="D175" s="112"/>
-      <c r="E175" s="112"/>
+      <c r="C175" s="109"/>
+      <c r="D175" s="109"/>
+      <c r="E175" s="109"/>
       <c r="F175" s="9" t="s">
         <v>168</v>
       </c>
@@ -6660,9 +6672,9 @@
       <c r="B176" s="9">
         <v>174</v>
       </c>
-      <c r="C176" s="112"/>
-      <c r="D176" s="112"/>
-      <c r="E176" s="112"/>
+      <c r="C176" s="109"/>
+      <c r="D176" s="109"/>
+      <c r="E176" s="109"/>
       <c r="F176" s="9" t="s">
         <v>169</v>
       </c>
@@ -6674,9 +6686,9 @@
       <c r="B177" s="9">
         <v>175</v>
       </c>
-      <c r="C177" s="112"/>
-      <c r="D177" s="112"/>
-      <c r="E177" s="112"/>
+      <c r="C177" s="109"/>
+      <c r="D177" s="109"/>
+      <c r="E177" s="109"/>
       <c r="F177" s="9" t="s">
         <v>170</v>
       </c>
@@ -6688,9 +6700,9 @@
       <c r="B178" s="9">
         <v>176</v>
       </c>
-      <c r="C178" s="112"/>
-      <c r="D178" s="112"/>
-      <c r="E178" s="112"/>
+      <c r="C178" s="109"/>
+      <c r="D178" s="109"/>
+      <c r="E178" s="109"/>
       <c r="F178" s="9" t="s">
         <v>171</v>
       </c>
@@ -6702,9 +6714,9 @@
       <c r="B179" s="9">
         <v>177</v>
       </c>
-      <c r="C179" s="112"/>
-      <c r="D179" s="112"/>
-      <c r="E179" s="112"/>
+      <c r="C179" s="109"/>
+      <c r="D179" s="109"/>
+      <c r="E179" s="109"/>
       <c r="F179" s="9" t="s">
         <v>481</v>
       </c>
@@ -6713,9 +6725,9 @@
       <c r="B180" s="9">
         <v>178</v>
       </c>
-      <c r="C180" s="112"/>
-      <c r="D180" s="112"/>
-      <c r="E180" s="112"/>
+      <c r="C180" s="109"/>
+      <c r="D180" s="109"/>
+      <c r="E180" s="109"/>
       <c r="F180" s="9" t="s">
         <v>172</v>
       </c>
@@ -6727,9 +6739,9 @@
       <c r="B181" s="9">
         <v>179</v>
       </c>
-      <c r="C181" s="112"/>
-      <c r="D181" s="112"/>
-      <c r="E181" s="112"/>
+      <c r="C181" s="109"/>
+      <c r="D181" s="109"/>
+      <c r="E181" s="109"/>
       <c r="F181" s="9" t="s">
         <v>173</v>
       </c>
@@ -6741,9 +6753,9 @@
       <c r="B182" s="9">
         <v>180</v>
       </c>
-      <c r="C182" s="112"/>
-      <c r="D182" s="112"/>
-      <c r="E182" s="112"/>
+      <c r="C182" s="109"/>
+      <c r="D182" s="109"/>
+      <c r="E182" s="109"/>
       <c r="F182" s="9" t="s">
         <v>174</v>
       </c>
@@ -6755,9 +6767,9 @@
       <c r="B183" s="9">
         <v>181</v>
       </c>
-      <c r="C183" s="112"/>
-      <c r="D183" s="112"/>
-      <c r="E183" s="112"/>
+      <c r="C183" s="109"/>
+      <c r="D183" s="109"/>
+      <c r="E183" s="109"/>
       <c r="F183" s="9" t="s">
         <v>175</v>
       </c>
@@ -6769,9 +6781,9 @@
       <c r="B184" s="9">
         <v>182</v>
       </c>
-      <c r="C184" s="112"/>
-      <c r="D184" s="112"/>
-      <c r="E184" s="112"/>
+      <c r="C184" s="109"/>
+      <c r="D184" s="109"/>
+      <c r="E184" s="109"/>
       <c r="F184" s="9" t="s">
         <v>176</v>
       </c>
@@ -6783,9 +6795,9 @@
       <c r="B185" s="9">
         <v>183</v>
       </c>
-      <c r="C185" s="112"/>
-      <c r="D185" s="112"/>
-      <c r="E185" s="112"/>
+      <c r="C185" s="109"/>
+      <c r="D185" s="109"/>
+      <c r="E185" s="109"/>
       <c r="F185" s="9" t="s">
         <v>177</v>
       </c>
@@ -6797,9 +6809,9 @@
       <c r="B186" s="9">
         <v>184</v>
       </c>
-      <c r="C186" s="112"/>
-      <c r="D186" s="112"/>
-      <c r="E186" s="112"/>
+      <c r="C186" s="109"/>
+      <c r="D186" s="109"/>
+      <c r="E186" s="109"/>
       <c r="F186" s="9" t="s">
         <v>482</v>
       </c>
@@ -6808,9 +6820,9 @@
       <c r="B187" s="9">
         <v>185</v>
       </c>
-      <c r="C187" s="112"/>
-      <c r="D187" s="112"/>
-      <c r="E187" s="112">
+      <c r="C187" s="109"/>
+      <c r="D187" s="109"/>
+      <c r="E187" s="109">
         <v>5</v>
       </c>
       <c r="F187" s="9" t="s">
@@ -6821,9 +6833,9 @@
       <c r="B188" s="9">
         <v>186</v>
       </c>
-      <c r="C188" s="112"/>
-      <c r="D188" s="112"/>
-      <c r="E188" s="112"/>
+      <c r="C188" s="109"/>
+      <c r="D188" s="109"/>
+      <c r="E188" s="109"/>
       <c r="F188" s="9" t="s">
         <v>179</v>
       </c>
@@ -6832,9 +6844,9 @@
       <c r="B189" s="9">
         <v>187</v>
       </c>
-      <c r="C189" s="112"/>
-      <c r="D189" s="112"/>
-      <c r="E189" s="112"/>
+      <c r="C189" s="109"/>
+      <c r="D189" s="109"/>
+      <c r="E189" s="109"/>
       <c r="F189" s="9" t="s">
         <v>180</v>
       </c>
@@ -6843,9 +6855,9 @@
       <c r="B190" s="9">
         <v>188</v>
       </c>
-      <c r="C190" s="112"/>
-      <c r="D190" s="112"/>
-      <c r="E190" s="112"/>
+      <c r="C190" s="109"/>
+      <c r="D190" s="109"/>
+      <c r="E190" s="109"/>
       <c r="F190" s="9" t="s">
         <v>483</v>
       </c>
@@ -6854,9 +6866,9 @@
       <c r="B191" s="9">
         <v>189</v>
       </c>
-      <c r="C191" s="112"/>
-      <c r="D191" s="112"/>
-      <c r="E191" s="112"/>
+      <c r="C191" s="109"/>
+      <c r="D191" s="109"/>
+      <c r="E191" s="109"/>
       <c r="F191" s="9" t="s">
         <v>484</v>
       </c>
@@ -6865,9 +6877,9 @@
       <c r="B192" s="9">
         <v>190</v>
       </c>
-      <c r="C192" s="112"/>
-      <c r="D192" s="112"/>
-      <c r="E192" s="112"/>
+      <c r="C192" s="109"/>
+      <c r="D192" s="109"/>
+      <c r="E192" s="109"/>
       <c r="F192" s="9" t="s">
         <v>485</v>
       </c>
@@ -6876,9 +6888,9 @@
       <c r="B193" s="9">
         <v>191</v>
       </c>
-      <c r="C193" s="112"/>
-      <c r="D193" s="112"/>
-      <c r="E193" s="112">
+      <c r="C193" s="109"/>
+      <c r="D193" s="109"/>
+      <c r="E193" s="109">
         <v>6</v>
       </c>
       <c r="F193" s="9" t="s">
@@ -6889,9 +6901,9 @@
       <c r="B194" s="9">
         <v>192</v>
       </c>
-      <c r="C194" s="112"/>
-      <c r="D194" s="112"/>
-      <c r="E194" s="112"/>
+      <c r="C194" s="109"/>
+      <c r="D194" s="109"/>
+      <c r="E194" s="109"/>
       <c r="F194" s="9" t="s">
         <v>486</v>
       </c>
@@ -6900,9 +6912,9 @@
       <c r="B195" s="9">
         <v>193</v>
       </c>
-      <c r="C195" s="112"/>
-      <c r="D195" s="112"/>
-      <c r="E195" s="112"/>
+      <c r="C195" s="109"/>
+      <c r="D195" s="109"/>
+      <c r="E195" s="109"/>
       <c r="F195" s="9" t="s">
         <v>487</v>
       </c>
@@ -6911,9 +6923,9 @@
       <c r="B196" s="9">
         <v>194</v>
       </c>
-      <c r="C196" s="112"/>
-      <c r="D196" s="112"/>
-      <c r="E196" s="112"/>
+      <c r="C196" s="109"/>
+      <c r="D196" s="109"/>
+      <c r="E196" s="109"/>
       <c r="F196" s="9" t="s">
         <v>488</v>
       </c>
@@ -6922,9 +6934,9 @@
       <c r="B197" s="9">
         <v>195</v>
       </c>
-      <c r="C197" s="112"/>
-      <c r="D197" s="112"/>
-      <c r="E197" s="112"/>
+      <c r="C197" s="109"/>
+      <c r="D197" s="109"/>
+      <c r="E197" s="109"/>
       <c r="F197" s="9" t="s">
         <v>489</v>
       </c>
@@ -6933,8 +6945,8 @@
       <c r="B198" s="9">
         <v>196</v>
       </c>
-      <c r="C198" s="112"/>
-      <c r="D198" s="112"/>
+      <c r="C198" s="109"/>
+      <c r="D198" s="109"/>
       <c r="E198" s="27">
         <v>7</v>
       </c>
@@ -6946,9 +6958,9 @@
       <c r="B199" s="9">
         <v>197</v>
       </c>
-      <c r="C199" s="112"/>
-      <c r="D199" s="112"/>
-      <c r="E199" s="112" t="s">
+      <c r="C199" s="109"/>
+      <c r="D199" s="109"/>
+      <c r="E199" s="109" t="s">
         <v>540</v>
       </c>
       <c r="F199" s="9" t="s">
@@ -6959,9 +6971,9 @@
       <c r="B200" s="9">
         <v>198</v>
       </c>
-      <c r="C200" s="112"/>
-      <c r="D200" s="112"/>
-      <c r="E200" s="112"/>
+      <c r="C200" s="109"/>
+      <c r="D200" s="109"/>
+      <c r="E200" s="109"/>
       <c r="F200" s="9" t="s">
         <v>492</v>
       </c>
@@ -6970,9 +6982,9 @@
       <c r="B201" s="9">
         <v>199</v>
       </c>
-      <c r="C201" s="112"/>
-      <c r="D201" s="112"/>
-      <c r="E201" s="112">
+      <c r="C201" s="109"/>
+      <c r="D201" s="109"/>
+      <c r="E201" s="109">
         <v>10</v>
       </c>
       <c r="F201" s="9" t="s">
@@ -6983,9 +6995,9 @@
       <c r="B202" s="9">
         <v>200</v>
       </c>
-      <c r="C202" s="112"/>
-      <c r="D202" s="112"/>
-      <c r="E202" s="112"/>
+      <c r="C202" s="109"/>
+      <c r="D202" s="109"/>
+      <c r="E202" s="109"/>
       <c r="F202" s="9" t="s">
         <v>183</v>
       </c>
@@ -6994,9 +7006,9 @@
       <c r="B203" s="9">
         <v>201</v>
       </c>
-      <c r="C203" s="112"/>
-      <c r="D203" s="112"/>
-      <c r="E203" s="112"/>
+      <c r="C203" s="109"/>
+      <c r="D203" s="109"/>
+      <c r="E203" s="109"/>
       <c r="F203" s="9" t="s">
         <v>184</v>
       </c>
@@ -7005,9 +7017,9 @@
       <c r="B204" s="9">
         <v>202</v>
       </c>
-      <c r="C204" s="112"/>
-      <c r="D204" s="112"/>
-      <c r="E204" s="112"/>
+      <c r="C204" s="109"/>
+      <c r="D204" s="109"/>
+      <c r="E204" s="109"/>
       <c r="F204" s="9" t="s">
         <v>493</v>
       </c>
@@ -7016,9 +7028,9 @@
       <c r="B205" s="9">
         <v>203</v>
       </c>
-      <c r="C205" s="112"/>
-      <c r="D205" s="112"/>
-      <c r="E205" s="112"/>
+      <c r="C205" s="109"/>
+      <c r="D205" s="109"/>
+      <c r="E205" s="109"/>
       <c r="F205" s="9" t="s">
         <v>494</v>
       </c>
@@ -7027,9 +7039,9 @@
       <c r="B206" s="9">
         <v>204</v>
       </c>
-      <c r="C206" s="112"/>
-      <c r="D206" s="112"/>
-      <c r="E206" s="112"/>
+      <c r="C206" s="109"/>
+      <c r="D206" s="109"/>
+      <c r="E206" s="109"/>
       <c r="F206" s="9" t="s">
         <v>495</v>
       </c>
@@ -7038,9 +7050,9 @@
       <c r="B207" s="9">
         <v>205</v>
       </c>
-      <c r="C207" s="112"/>
-      <c r="D207" s="112"/>
-      <c r="E207" s="112">
+      <c r="C207" s="109"/>
+      <c r="D207" s="109"/>
+      <c r="E207" s="109">
         <v>11</v>
       </c>
       <c r="F207" s="9" t="s">
@@ -7051,9 +7063,9 @@
       <c r="B208" s="9">
         <v>206</v>
       </c>
-      <c r="C208" s="112"/>
-      <c r="D208" s="112"/>
-      <c r="E208" s="112"/>
+      <c r="C208" s="109"/>
+      <c r="D208" s="109"/>
+      <c r="E208" s="109"/>
       <c r="F208" s="9" t="s">
         <v>186</v>
       </c>
@@ -7062,9 +7074,9 @@
       <c r="B209" s="9">
         <v>207</v>
       </c>
-      <c r="C209" s="112"/>
-      <c r="D209" s="112"/>
-      <c r="E209" s="112"/>
+      <c r="C209" s="109"/>
+      <c r="D209" s="109"/>
+      <c r="E209" s="109"/>
       <c r="F209" s="9" t="s">
         <v>187</v>
       </c>
@@ -7073,9 +7085,9 @@
       <c r="B210" s="9">
         <v>208</v>
       </c>
-      <c r="C210" s="112"/>
-      <c r="D210" s="112"/>
-      <c r="E210" s="112"/>
+      <c r="C210" s="109"/>
+      <c r="D210" s="109"/>
+      <c r="E210" s="109"/>
       <c r="F210" s="9" t="s">
         <v>188</v>
       </c>
@@ -7084,9 +7096,9 @@
       <c r="B211" s="9">
         <v>209</v>
       </c>
-      <c r="C211" s="112"/>
-      <c r="D211" s="112"/>
-      <c r="E211" s="112"/>
+      <c r="C211" s="109"/>
+      <c r="D211" s="109"/>
+      <c r="E211" s="109"/>
       <c r="F211" s="9" t="s">
         <v>189</v>
       </c>
@@ -7095,9 +7107,9 @@
       <c r="B212" s="9">
         <v>210</v>
       </c>
-      <c r="C212" s="112"/>
-      <c r="D212" s="112"/>
-      <c r="E212" s="112"/>
+      <c r="C212" s="109"/>
+      <c r="D212" s="109"/>
+      <c r="E212" s="109"/>
       <c r="F212" s="9" t="s">
         <v>190</v>
       </c>
@@ -7106,9 +7118,9 @@
       <c r="B213" s="9">
         <v>211</v>
       </c>
-      <c r="C213" s="112"/>
-      <c r="D213" s="112"/>
-      <c r="E213" s="112"/>
+      <c r="C213" s="109"/>
+      <c r="D213" s="109"/>
+      <c r="E213" s="109"/>
       <c r="F213" s="9" t="s">
         <v>191</v>
       </c>
@@ -7117,9 +7129,9 @@
       <c r="B214" s="9">
         <v>212</v>
       </c>
-      <c r="C214" s="112"/>
-      <c r="D214" s="112"/>
-      <c r="E214" s="112"/>
+      <c r="C214" s="109"/>
+      <c r="D214" s="109"/>
+      <c r="E214" s="109"/>
       <c r="F214" s="9" t="s">
         <v>192</v>
       </c>
@@ -7128,9 +7140,9 @@
       <c r="B215" s="9">
         <v>213</v>
       </c>
-      <c r="C215" s="112"/>
-      <c r="D215" s="112"/>
-      <c r="E215" s="112"/>
+      <c r="C215" s="109"/>
+      <c r="D215" s="109"/>
+      <c r="E215" s="109"/>
       <c r="F215" s="9" t="s">
         <v>496</v>
       </c>
@@ -7139,9 +7151,9 @@
       <c r="B216" s="9">
         <v>214</v>
       </c>
-      <c r="C216" s="112"/>
-      <c r="D216" s="112"/>
-      <c r="E216" s="112">
+      <c r="C216" s="109"/>
+      <c r="D216" s="109"/>
+      <c r="E216" s="109">
         <v>14</v>
       </c>
       <c r="F216" s="9" t="s">
@@ -7152,9 +7164,9 @@
       <c r="B217" s="9">
         <v>215</v>
       </c>
-      <c r="C217" s="112"/>
-      <c r="D217" s="112"/>
-      <c r="E217" s="112"/>
+      <c r="C217" s="109"/>
+      <c r="D217" s="109"/>
+      <c r="E217" s="109"/>
       <c r="F217" s="9" t="s">
         <v>498</v>
       </c>
@@ -7163,9 +7175,9 @@
       <c r="B218" s="9">
         <v>216</v>
       </c>
-      <c r="C218" s="112"/>
-      <c r="D218" s="112"/>
-      <c r="E218" s="112"/>
+      <c r="C218" s="109"/>
+      <c r="D218" s="109"/>
+      <c r="E218" s="109"/>
       <c r="F218" s="9" t="s">
         <v>499</v>
       </c>
@@ -7174,9 +7186,9 @@
       <c r="B219" s="9">
         <v>217</v>
       </c>
-      <c r="C219" s="112"/>
-      <c r="D219" s="112"/>
-      <c r="E219" s="112"/>
+      <c r="C219" s="109"/>
+      <c r="D219" s="109"/>
+      <c r="E219" s="109"/>
       <c r="F219" s="9" t="s">
         <v>500</v>
       </c>
@@ -7185,9 +7197,9 @@
       <c r="B220" s="9">
         <v>218</v>
       </c>
-      <c r="C220" s="112"/>
-      <c r="D220" s="112"/>
-      <c r="E220" s="112"/>
+      <c r="C220" s="109"/>
+      <c r="D220" s="109"/>
+      <c r="E220" s="109"/>
       <c r="F220" s="9" t="s">
         <v>501</v>
       </c>
@@ -7196,9 +7208,9 @@
       <c r="B221" s="9">
         <v>219</v>
       </c>
-      <c r="C221" s="112"/>
-      <c r="D221" s="112"/>
-      <c r="E221" s="112"/>
+      <c r="C221" s="109"/>
+      <c r="D221" s="109"/>
+      <c r="E221" s="109"/>
       <c r="F221" s="9" t="s">
         <v>502</v>
       </c>
@@ -7207,9 +7219,9 @@
       <c r="B222" s="9">
         <v>220</v>
       </c>
-      <c r="C222" s="112"/>
-      <c r="D222" s="112"/>
-      <c r="E222" s="112"/>
+      <c r="C222" s="109"/>
+      <c r="D222" s="109"/>
+      <c r="E222" s="109"/>
       <c r="F222" s="9" t="s">
         <v>503</v>
       </c>
@@ -7218,9 +7230,9 @@
       <c r="B223" s="9">
         <v>221</v>
       </c>
-      <c r="C223" s="112"/>
-      <c r="D223" s="112"/>
-      <c r="E223" s="112"/>
+      <c r="C223" s="109"/>
+      <c r="D223" s="109"/>
+      <c r="E223" s="109"/>
       <c r="F223" s="9" t="s">
         <v>504</v>
       </c>
@@ -7229,9 +7241,9 @@
       <c r="B224" s="9">
         <v>222</v>
       </c>
-      <c r="C224" s="112"/>
-      <c r="D224" s="112"/>
-      <c r="E224" s="112"/>
+      <c r="C224" s="109"/>
+      <c r="D224" s="109"/>
+      <c r="E224" s="109"/>
       <c r="F224" s="9" t="s">
         <v>505</v>
       </c>
@@ -7240,9 +7252,9 @@
       <c r="B225" s="9">
         <v>223</v>
       </c>
-      <c r="C225" s="112"/>
-      <c r="D225" s="112"/>
-      <c r="E225" s="112"/>
+      <c r="C225" s="109"/>
+      <c r="D225" s="109"/>
+      <c r="E225" s="109"/>
       <c r="F225" s="9" t="s">
         <v>506</v>
       </c>
@@ -7251,9 +7263,9 @@
       <c r="B226" s="9">
         <v>224</v>
       </c>
-      <c r="C226" s="112"/>
-      <c r="D226" s="112"/>
-      <c r="E226" s="112"/>
+      <c r="C226" s="109"/>
+      <c r="D226" s="109"/>
+      <c r="E226" s="109"/>
       <c r="F226" s="9" t="s">
         <v>508</v>
       </c>
@@ -7262,9 +7274,9 @@
       <c r="B227" s="9">
         <v>225</v>
       </c>
-      <c r="C227" s="112"/>
-      <c r="D227" s="112"/>
-      <c r="E227" s="112"/>
+      <c r="C227" s="109"/>
+      <c r="D227" s="109"/>
+      <c r="E227" s="109"/>
       <c r="F227" s="9" t="s">
         <v>509</v>
       </c>
@@ -7273,9 +7285,9 @@
       <c r="B228" s="9">
         <v>226</v>
       </c>
-      <c r="C228" s="112"/>
-      <c r="D228" s="112"/>
-      <c r="E228" s="112"/>
+      <c r="C228" s="109"/>
+      <c r="D228" s="109"/>
+      <c r="E228" s="109"/>
       <c r="F228" s="9" t="s">
         <v>510</v>
       </c>
@@ -7284,9 +7296,9 @@
       <c r="B229" s="9">
         <v>227</v>
       </c>
-      <c r="C229" s="112"/>
-      <c r="D229" s="112"/>
-      <c r="E229" s="112"/>
+      <c r="C229" s="109"/>
+      <c r="D229" s="109"/>
+      <c r="E229" s="109"/>
       <c r="F229" s="9" t="s">
         <v>511</v>
       </c>
@@ -7295,9 +7307,9 @@
       <c r="B230" s="9">
         <v>228</v>
       </c>
-      <c r="C230" s="112"/>
-      <c r="D230" s="112"/>
-      <c r="E230" s="112"/>
+      <c r="C230" s="109"/>
+      <c r="D230" s="109"/>
+      <c r="E230" s="109"/>
       <c r="F230" s="9" t="s">
         <v>512</v>
       </c>
@@ -7306,9 +7318,9 @@
       <c r="B231" s="9">
         <v>229</v>
       </c>
-      <c r="C231" s="112"/>
-      <c r="D231" s="112"/>
-      <c r="E231" s="112"/>
+      <c r="C231" s="109"/>
+      <c r="D231" s="109"/>
+      <c r="E231" s="109"/>
       <c r="F231" s="9" t="s">
         <v>513</v>
       </c>
@@ -7317,9 +7329,9 @@
       <c r="B232" s="9">
         <v>230</v>
       </c>
-      <c r="C232" s="112"/>
-      <c r="D232" s="112"/>
-      <c r="E232" s="112"/>
+      <c r="C232" s="109"/>
+      <c r="D232" s="109"/>
+      <c r="E232" s="109"/>
       <c r="F232" s="9" t="s">
         <v>507</v>
       </c>
@@ -7328,9 +7340,9 @@
       <c r="B233" s="9">
         <v>231</v>
       </c>
-      <c r="C233" s="112"/>
-      <c r="D233" s="112"/>
-      <c r="E233" s="112"/>
+      <c r="C233" s="109"/>
+      <c r="D233" s="109"/>
+      <c r="E233" s="109"/>
       <c r="F233" s="9" t="s">
         <v>520</v>
       </c>
@@ -7339,9 +7351,9 @@
       <c r="B234" s="9">
         <v>232</v>
       </c>
-      <c r="C234" s="112"/>
-      <c r="D234" s="112"/>
-      <c r="E234" s="112"/>
+      <c r="C234" s="109"/>
+      <c r="D234" s="109"/>
+      <c r="E234" s="109"/>
       <c r="F234" s="9" t="s">
         <v>521</v>
       </c>
@@ -7350,9 +7362,9 @@
       <c r="B235" s="9">
         <v>233</v>
       </c>
-      <c r="C235" s="112"/>
-      <c r="D235" s="112"/>
-      <c r="E235" s="112"/>
+      <c r="C235" s="109"/>
+      <c r="D235" s="109"/>
+      <c r="E235" s="109"/>
       <c r="F235" s="9" t="s">
         <v>522</v>
       </c>
@@ -7361,9 +7373,9 @@
       <c r="B236" s="9">
         <v>234</v>
       </c>
-      <c r="C236" s="112"/>
-      <c r="D236" s="112"/>
-      <c r="E236" s="112"/>
+      <c r="C236" s="109"/>
+      <c r="D236" s="109"/>
+      <c r="E236" s="109"/>
       <c r="F236" s="9" t="s">
         <v>523</v>
       </c>
@@ -7372,9 +7384,9 @@
       <c r="B237" s="9">
         <v>235</v>
       </c>
-      <c r="C237" s="112"/>
-      <c r="D237" s="112"/>
-      <c r="E237" s="112"/>
+      <c r="C237" s="109"/>
+      <c r="D237" s="109"/>
+      <c r="E237" s="109"/>
       <c r="F237" s="9" t="s">
         <v>514</v>
       </c>
@@ -7383,9 +7395,9 @@
       <c r="B238" s="9">
         <v>236</v>
       </c>
-      <c r="C238" s="112"/>
-      <c r="D238" s="112"/>
-      <c r="E238" s="112"/>
+      <c r="C238" s="109"/>
+      <c r="D238" s="109"/>
+      <c r="E238" s="109"/>
       <c r="F238" s="9" t="s">
         <v>515</v>
       </c>
@@ -7394,9 +7406,9 @@
       <c r="B239" s="9">
         <v>237</v>
       </c>
-      <c r="C239" s="112"/>
-      <c r="D239" s="112"/>
-      <c r="E239" s="112"/>
+      <c r="C239" s="109"/>
+      <c r="D239" s="109"/>
+      <c r="E239" s="109"/>
       <c r="F239" s="9" t="s">
         <v>516</v>
       </c>
@@ -7405,9 +7417,9 @@
       <c r="B240" s="9">
         <v>238</v>
       </c>
-      <c r="C240" s="112"/>
-      <c r="D240" s="112"/>
-      <c r="E240" s="112"/>
+      <c r="C240" s="109"/>
+      <c r="D240" s="109"/>
+      <c r="E240" s="109"/>
       <c r="F240" s="9" t="s">
         <v>517</v>
       </c>
@@ -7416,9 +7428,9 @@
       <c r="B241" s="9">
         <v>239</v>
       </c>
-      <c r="C241" s="112"/>
-      <c r="D241" s="112"/>
-      <c r="E241" s="112"/>
+      <c r="C241" s="109"/>
+      <c r="D241" s="109"/>
+      <c r="E241" s="109"/>
       <c r="F241" s="9" t="s">
         <v>518</v>
       </c>
@@ -7427,9 +7439,9 @@
       <c r="B242" s="9">
         <v>240</v>
       </c>
-      <c r="C242" s="112"/>
-      <c r="D242" s="112"/>
-      <c r="E242" s="112"/>
+      <c r="C242" s="109"/>
+      <c r="D242" s="109"/>
+      <c r="E242" s="109"/>
       <c r="F242" s="9" t="s">
         <v>519</v>
       </c>
@@ -7438,9 +7450,9 @@
       <c r="B243" s="9">
         <v>241</v>
       </c>
-      <c r="C243" s="112"/>
-      <c r="D243" s="112"/>
-      <c r="E243" s="112"/>
+      <c r="C243" s="109"/>
+      <c r="D243" s="109"/>
+      <c r="E243" s="109"/>
       <c r="F243" s="9" t="s">
         <v>524</v>
       </c>
@@ -7452,9 +7464,9 @@
       <c r="B244" s="9">
         <v>242</v>
       </c>
-      <c r="C244" s="112"/>
-      <c r="D244" s="112"/>
-      <c r="E244" s="112"/>
+      <c r="C244" s="109"/>
+      <c r="D244" s="109"/>
+      <c r="E244" s="109"/>
       <c r="F244" s="9" t="s">
         <v>525</v>
       </c>
@@ -7463,9 +7475,9 @@
       <c r="B245" s="9">
         <v>243</v>
       </c>
-      <c r="C245" s="112"/>
-      <c r="D245" s="112"/>
-      <c r="E245" s="112"/>
+      <c r="C245" s="109"/>
+      <c r="D245" s="109"/>
+      <c r="E245" s="109"/>
       <c r="F245" s="9" t="s">
         <v>526</v>
       </c>
@@ -7474,9 +7486,9 @@
       <c r="B246" s="9">
         <v>244</v>
       </c>
-      <c r="C246" s="112"/>
-      <c r="D246" s="112"/>
-      <c r="E246" s="112"/>
+      <c r="C246" s="109"/>
+      <c r="D246" s="109"/>
+      <c r="E246" s="109"/>
       <c r="F246" s="9" t="s">
         <v>527</v>
       </c>
@@ -7485,9 +7497,9 @@
       <c r="B247" s="9">
         <v>245</v>
       </c>
-      <c r="C247" s="112"/>
-      <c r="D247" s="112"/>
-      <c r="E247" s="112"/>
+      <c r="C247" s="109"/>
+      <c r="D247" s="109"/>
+      <c r="E247" s="109"/>
       <c r="F247" s="9" t="s">
         <v>528</v>
       </c>
@@ -7496,9 +7508,9 @@
       <c r="B248" s="9">
         <v>246</v>
       </c>
-      <c r="C248" s="112"/>
-      <c r="D248" s="112"/>
-      <c r="E248" s="112"/>
+      <c r="C248" s="109"/>
+      <c r="D248" s="109"/>
+      <c r="E248" s="109"/>
       <c r="F248" s="9" t="s">
         <v>529</v>
       </c>
@@ -7507,9 +7519,9 @@
       <c r="B249" s="9">
         <v>247</v>
       </c>
-      <c r="C249" s="112"/>
-      <c r="D249" s="112"/>
-      <c r="E249" s="112"/>
+      <c r="C249" s="109"/>
+      <c r="D249" s="109"/>
+      <c r="E249" s="109"/>
       <c r="F249" s="9" t="s">
         <v>530</v>
       </c>
@@ -7518,9 +7530,9 @@
       <c r="B250" s="9">
         <v>248</v>
       </c>
-      <c r="C250" s="112"/>
-      <c r="D250" s="112"/>
-      <c r="E250" s="112"/>
+      <c r="C250" s="109"/>
+      <c r="D250" s="109"/>
+      <c r="E250" s="109"/>
       <c r="F250" s="9" t="s">
         <v>530</v>
       </c>
@@ -7529,9 +7541,9 @@
       <c r="B251" s="9">
         <v>249</v>
       </c>
-      <c r="C251" s="112"/>
-      <c r="D251" s="112"/>
-      <c r="E251" s="112"/>
+      <c r="C251" s="109"/>
+      <c r="D251" s="109"/>
+      <c r="E251" s="109"/>
       <c r="F251" s="9" t="s">
         <v>531</v>
       </c>
@@ -7540,9 +7552,9 @@
       <c r="B252" s="9">
         <v>250</v>
       </c>
-      <c r="C252" s="112"/>
-      <c r="D252" s="112"/>
-      <c r="E252" s="112"/>
+      <c r="C252" s="109"/>
+      <c r="D252" s="109"/>
+      <c r="E252" s="109"/>
       <c r="F252" s="9" t="s">
         <v>532</v>
       </c>
@@ -7551,9 +7563,9 @@
       <c r="B253" s="9">
         <v>251</v>
       </c>
-      <c r="C253" s="112"/>
-      <c r="D253" s="112"/>
-      <c r="E253" s="112"/>
+      <c r="C253" s="109"/>
+      <c r="D253" s="109"/>
+      <c r="E253" s="109"/>
       <c r="F253" s="9" t="s">
         <v>533</v>
       </c>
@@ -7562,8 +7574,8 @@
       <c r="B254" s="9">
         <v>252</v>
       </c>
-      <c r="C254" s="112"/>
-      <c r="D254" s="112"/>
+      <c r="C254" s="109"/>
+      <c r="D254" s="109"/>
       <c r="E254" s="27">
         <v>15</v>
       </c>
@@ -7575,9 +7587,9 @@
       <c r="B255" s="9">
         <v>253</v>
       </c>
-      <c r="C255" s="112"/>
-      <c r="D255" s="112"/>
-      <c r="E255" s="112">
+      <c r="C255" s="109"/>
+      <c r="D255" s="109"/>
+      <c r="E255" s="109">
         <v>20</v>
       </c>
       <c r="F255" s="9" t="s">
@@ -7588,9 +7600,9 @@
       <c r="B256" s="9">
         <v>254</v>
       </c>
-      <c r="C256" s="112"/>
-      <c r="D256" s="112"/>
-      <c r="E256" s="112"/>
+      <c r="C256" s="109"/>
+      <c r="D256" s="109"/>
+      <c r="E256" s="109"/>
       <c r="F256" s="9" t="s">
         <v>194</v>
       </c>
@@ -7599,9 +7611,9 @@
       <c r="B257" s="9">
         <v>255</v>
       </c>
-      <c r="C257" s="112"/>
-      <c r="D257" s="112"/>
-      <c r="E257" s="112"/>
+      <c r="C257" s="109"/>
+      <c r="D257" s="109"/>
+      <c r="E257" s="109"/>
       <c r="F257" s="9" t="s">
         <v>195</v>
       </c>
@@ -7610,9 +7622,9 @@
       <c r="B258" s="9">
         <v>256</v>
       </c>
-      <c r="C258" s="112"/>
-      <c r="D258" s="112"/>
-      <c r="E258" s="112">
+      <c r="C258" s="109"/>
+      <c r="D258" s="109"/>
+      <c r="E258" s="109">
         <v>30</v>
       </c>
       <c r="F258" s="9" t="s">
@@ -7623,9 +7635,9 @@
       <c r="B259" s="9">
         <v>257</v>
       </c>
-      <c r="C259" s="112"/>
-      <c r="D259" s="112"/>
-      <c r="E259" s="112"/>
+      <c r="C259" s="109"/>
+      <c r="D259" s="109"/>
+      <c r="E259" s="109"/>
       <c r="F259" s="9" t="s">
         <v>197</v>
       </c>
@@ -7634,9 +7646,9 @@
       <c r="B260" s="9">
         <v>258</v>
       </c>
-      <c r="C260" s="112"/>
-      <c r="D260" s="112"/>
-      <c r="E260" s="112"/>
+      <c r="C260" s="109"/>
+      <c r="D260" s="109"/>
+      <c r="E260" s="109"/>
       <c r="F260" s="9" t="s">
         <v>198</v>
       </c>
@@ -7645,9 +7657,9 @@
       <c r="B261" s="9">
         <v>259</v>
       </c>
-      <c r="C261" s="112"/>
-      <c r="D261" s="112"/>
-      <c r="E261" s="112"/>
+      <c r="C261" s="109"/>
+      <c r="D261" s="109"/>
+      <c r="E261" s="109"/>
       <c r="F261" s="9" t="s">
         <v>199</v>
       </c>
@@ -7656,9 +7668,9 @@
       <c r="B262" s="9">
         <v>260</v>
       </c>
-      <c r="C262" s="112"/>
-      <c r="D262" s="112"/>
-      <c r="E262" s="112"/>
+      <c r="C262" s="109"/>
+      <c r="D262" s="109"/>
+      <c r="E262" s="109"/>
       <c r="F262" s="9" t="s">
         <v>200</v>
       </c>
@@ -7667,9 +7679,9 @@
       <c r="B263" s="9">
         <v>261</v>
       </c>
-      <c r="C263" s="112"/>
-      <c r="D263" s="112"/>
-      <c r="E263" s="112"/>
+      <c r="C263" s="109"/>
+      <c r="D263" s="109"/>
+      <c r="E263" s="109"/>
       <c r="F263" s="9" t="s">
         <v>201</v>
       </c>
@@ -7678,9 +7690,9 @@
       <c r="B264" s="9">
         <v>262</v>
       </c>
-      <c r="C264" s="112"/>
-      <c r="D264" s="112"/>
-      <c r="E264" s="112"/>
+      <c r="C264" s="109"/>
+      <c r="D264" s="109"/>
+      <c r="E264" s="109"/>
       <c r="F264" s="9" t="s">
         <v>202</v>
       </c>
@@ -7689,9 +7701,9 @@
       <c r="B265" s="9">
         <v>263</v>
       </c>
-      <c r="C265" s="112"/>
-      <c r="D265" s="112"/>
-      <c r="E265" s="112">
+      <c r="C265" s="109"/>
+      <c r="D265" s="109"/>
+      <c r="E265" s="109">
         <v>31</v>
       </c>
       <c r="F265" s="9" t="s">
@@ -7702,9 +7714,9 @@
       <c r="B266" s="9">
         <v>264</v>
       </c>
-      <c r="C266" s="112"/>
-      <c r="D266" s="112"/>
-      <c r="E266" s="112"/>
+      <c r="C266" s="109"/>
+      <c r="D266" s="109"/>
+      <c r="E266" s="109"/>
       <c r="F266" s="9" t="s">
         <v>204</v>
       </c>
@@ -7713,9 +7725,9 @@
       <c r="B267" s="9">
         <v>265</v>
       </c>
-      <c r="C267" s="112"/>
-      <c r="D267" s="112"/>
-      <c r="E267" s="112">
+      <c r="C267" s="109"/>
+      <c r="D267" s="109"/>
+      <c r="E267" s="109">
         <v>32</v>
       </c>
       <c r="F267" s="9" t="s">
@@ -7726,9 +7738,9 @@
       <c r="B268" s="9">
         <v>266</v>
       </c>
-      <c r="C268" s="112"/>
-      <c r="D268" s="112"/>
-      <c r="E268" s="112"/>
+      <c r="C268" s="109"/>
+      <c r="D268" s="109"/>
+      <c r="E268" s="109"/>
       <c r="F268" s="9" t="s">
         <v>206</v>
       </c>
@@ -7737,9 +7749,9 @@
       <c r="B269" s="9">
         <v>267</v>
       </c>
-      <c r="C269" s="112"/>
-      <c r="D269" s="112"/>
-      <c r="E269" s="112"/>
+      <c r="C269" s="109"/>
+      <c r="D269" s="109"/>
+      <c r="E269" s="109"/>
       <c r="F269" s="9" t="s">
         <v>207</v>
       </c>
@@ -7748,8 +7760,8 @@
       <c r="B270" s="9">
         <v>268</v>
       </c>
-      <c r="C270" s="112"/>
-      <c r="D270" s="112"/>
+      <c r="C270" s="109"/>
+      <c r="D270" s="109"/>
       <c r="E270" s="27">
         <v>33</v>
       </c>
@@ -7761,9 +7773,9 @@
       <c r="B271" s="9">
         <v>269</v>
       </c>
-      <c r="C271" s="112"/>
-      <c r="D271" s="112"/>
-      <c r="E271" s="112">
+      <c r="C271" s="109"/>
+      <c r="D271" s="109"/>
+      <c r="E271" s="109">
         <v>34</v>
       </c>
       <c r="F271" s="9" t="s">
@@ -7774,9 +7786,9 @@
       <c r="B272" s="9">
         <v>270</v>
       </c>
-      <c r="C272" s="112"/>
-      <c r="D272" s="112"/>
-      <c r="E272" s="112"/>
+      <c r="C272" s="109"/>
+      <c r="D272" s="109"/>
+      <c r="E272" s="109"/>
       <c r="F272" s="9" t="s">
         <v>210</v>
       </c>
@@ -7785,9 +7797,9 @@
       <c r="B273" s="9">
         <v>271</v>
       </c>
-      <c r="C273" s="112"/>
-      <c r="D273" s="112"/>
-      <c r="E273" s="112"/>
+      <c r="C273" s="109"/>
+      <c r="D273" s="109"/>
+      <c r="E273" s="109"/>
       <c r="F273" s="9" t="s">
         <v>211</v>
       </c>
@@ -7796,9 +7808,9 @@
       <c r="B274" s="9">
         <v>272</v>
       </c>
-      <c r="C274" s="112"/>
-      <c r="D274" s="112"/>
-      <c r="E274" s="112">
+      <c r="C274" s="109"/>
+      <c r="D274" s="109"/>
+      <c r="E274" s="109">
         <v>40</v>
       </c>
       <c r="F274" s="9" t="s">
@@ -7809,9 +7821,9 @@
       <c r="B275" s="9">
         <v>273</v>
       </c>
-      <c r="C275" s="112"/>
-      <c r="D275" s="112"/>
-      <c r="E275" s="112"/>
+      <c r="C275" s="109"/>
+      <c r="D275" s="109"/>
+      <c r="E275" s="109"/>
       <c r="F275" s="9" t="s">
         <v>213</v>
       </c>
@@ -7820,9 +7832,9 @@
       <c r="B276" s="9">
         <v>274</v>
       </c>
-      <c r="C276" s="112"/>
-      <c r="D276" s="112"/>
-      <c r="E276" s="112">
+      <c r="C276" s="109"/>
+      <c r="D276" s="109"/>
+      <c r="E276" s="109">
         <v>50</v>
       </c>
       <c r="F276" s="9" t="s">
@@ -7833,9 +7845,9 @@
       <c r="B277" s="9">
         <v>275</v>
       </c>
-      <c r="C277" s="112"/>
-      <c r="D277" s="112"/>
-      <c r="E277" s="112"/>
+      <c r="C277" s="109"/>
+      <c r="D277" s="109"/>
+      <c r="E277" s="109"/>
       <c r="F277" s="9" t="s">
         <v>215</v>
       </c>
@@ -7844,9 +7856,9 @@
       <c r="B278" s="9">
         <v>276</v>
       </c>
-      <c r="C278" s="112"/>
-      <c r="D278" s="112"/>
-      <c r="E278" s="112"/>
+      <c r="C278" s="109"/>
+      <c r="D278" s="109"/>
+      <c r="E278" s="109"/>
       <c r="F278" s="9" t="s">
         <v>216</v>
       </c>
@@ -7855,9 +7867,9 @@
       <c r="B279" s="9">
         <v>277</v>
       </c>
-      <c r="C279" s="112"/>
-      <c r="D279" s="112"/>
-      <c r="E279" s="112"/>
+      <c r="C279" s="109"/>
+      <c r="D279" s="109"/>
+      <c r="E279" s="109"/>
       <c r="F279" s="9" t="s">
         <v>217</v>
       </c>
@@ -7866,8 +7878,8 @@
       <c r="B280" s="9">
         <v>278</v>
       </c>
-      <c r="C280" s="112"/>
-      <c r="D280" s="112"/>
+      <c r="C280" s="109"/>
+      <c r="D280" s="109"/>
       <c r="E280" s="27" t="s">
         <v>226</v>
       </c>
@@ -7879,8 +7891,8 @@
       <c r="B281" s="9">
         <v>279</v>
       </c>
-      <c r="C281" s="112"/>
-      <c r="D281" s="112"/>
+      <c r="C281" s="109"/>
+      <c r="D281" s="109"/>
       <c r="E281" s="27" t="s">
         <v>227</v>
       </c>
@@ -7892,8 +7904,8 @@
       <c r="B282" s="9">
         <v>280</v>
       </c>
-      <c r="C282" s="112"/>
-      <c r="D282" s="112"/>
+      <c r="C282" s="109"/>
+      <c r="D282" s="109"/>
       <c r="E282" s="27" t="s">
         <v>394</v>
       </c>
@@ -7931,10 +7943,10 @@
       <c r="B284" s="9">
         <v>282</v>
       </c>
-      <c r="C284" s="113" t="s">
+      <c r="C284" s="108" t="s">
         <v>228</v>
       </c>
-      <c r="D284" s="113" t="s">
+      <c r="D284" s="108" t="s">
         <v>222</v>
       </c>
       <c r="E284" s="28">
@@ -7957,9 +7969,9 @@
       <c r="B285" s="9">
         <v>283</v>
       </c>
-      <c r="C285" s="113"/>
-      <c r="D285" s="113"/>
-      <c r="E285" s="113">
+      <c r="C285" s="108"/>
+      <c r="D285" s="108"/>
+      <c r="E285" s="108">
         <v>2</v>
       </c>
       <c r="F285" s="9" t="s">
@@ -7979,9 +7991,9 @@
       <c r="B286" s="9">
         <v>284</v>
       </c>
-      <c r="C286" s="113"/>
-      <c r="D286" s="113"/>
-      <c r="E286" s="113"/>
+      <c r="C286" s="108"/>
+      <c r="D286" s="108"/>
+      <c r="E286" s="108"/>
       <c r="F286" s="9" t="s">
         <v>1</v>
       </c>
@@ -7993,9 +8005,9 @@
       <c r="B287" s="9">
         <v>285</v>
       </c>
-      <c r="C287" s="113"/>
-      <c r="D287" s="113"/>
-      <c r="E287" s="113"/>
+      <c r="C287" s="108"/>
+      <c r="D287" s="108"/>
+      <c r="E287" s="108"/>
       <c r="F287" s="9" t="s">
         <v>2</v>
       </c>
@@ -8007,9 +8019,9 @@
       <c r="B288" s="9">
         <v>286</v>
       </c>
-      <c r="C288" s="113"/>
-      <c r="D288" s="113"/>
-      <c r="E288" s="113"/>
+      <c r="C288" s="108"/>
+      <c r="D288" s="108"/>
+      <c r="E288" s="108"/>
       <c r="F288" s="9" t="s">
         <v>3</v>
       </c>
@@ -8024,9 +8036,9 @@
       <c r="B289" s="9">
         <v>287</v>
       </c>
-      <c r="C289" s="113"/>
-      <c r="D289" s="113"/>
-      <c r="E289" s="113">
+      <c r="C289" s="108"/>
+      <c r="D289" s="108"/>
+      <c r="E289" s="108">
         <v>3</v>
       </c>
       <c r="F289" s="9" t="s">
@@ -8040,9 +8052,9 @@
       <c r="B290" s="9">
         <v>288</v>
       </c>
-      <c r="C290" s="113"/>
-      <c r="D290" s="113"/>
-      <c r="E290" s="113"/>
+      <c r="C290" s="108"/>
+      <c r="D290" s="108"/>
+      <c r="E290" s="108"/>
       <c r="F290" s="9" t="s">
         <v>5</v>
       </c>
@@ -8054,9 +8066,9 @@
       <c r="B291" s="9">
         <v>289</v>
       </c>
-      <c r="C291" s="113"/>
-      <c r="D291" s="113"/>
-      <c r="E291" s="113">
+      <c r="C291" s="108"/>
+      <c r="D291" s="108"/>
+      <c r="E291" s="108">
         <v>4</v>
       </c>
       <c r="F291" s="9" t="s">
@@ -8067,9 +8079,9 @@
       <c r="B292" s="9">
         <v>290</v>
       </c>
-      <c r="C292" s="113"/>
-      <c r="D292" s="113"/>
-      <c r="E292" s="113"/>
+      <c r="C292" s="108"/>
+      <c r="D292" s="108"/>
+      <c r="E292" s="108"/>
       <c r="F292" s="9" t="s">
         <v>7</v>
       </c>
@@ -8079,9 +8091,9 @@
       <c r="B293" s="9">
         <v>291</v>
       </c>
-      <c r="C293" s="113"/>
-      <c r="D293" s="113"/>
-      <c r="E293" s="113">
+      <c r="C293" s="108"/>
+      <c r="D293" s="108"/>
+      <c r="E293" s="108">
         <v>5</v>
       </c>
       <c r="F293" s="9" t="s">
@@ -8096,9 +8108,9 @@
       <c r="B294" s="9">
         <v>292</v>
       </c>
-      <c r="C294" s="113"/>
-      <c r="D294" s="113"/>
-      <c r="E294" s="113"/>
+      <c r="C294" s="108"/>
+      <c r="D294" s="108"/>
+      <c r="E294" s="108"/>
       <c r="F294" s="9" t="s">
         <v>8</v>
       </c>
@@ -8110,9 +8122,9 @@
       <c r="B295" s="9">
         <v>293</v>
       </c>
-      <c r="C295" s="113"/>
-      <c r="D295" s="113"/>
-      <c r="E295" s="113"/>
+      <c r="C295" s="108"/>
+      <c r="D295" s="108"/>
+      <c r="E295" s="108"/>
       <c r="F295" s="9" t="s">
         <v>539</v>
       </c>
@@ -8127,9 +8139,9 @@
       <c r="B296" s="9">
         <v>294</v>
       </c>
-      <c r="C296" s="113"/>
-      <c r="D296" s="113"/>
-      <c r="E296" s="113">
+      <c r="C296" s="108"/>
+      <c r="D296" s="108"/>
+      <c r="E296" s="108">
         <v>10</v>
       </c>
       <c r="F296" s="9" t="s">
@@ -8149,9 +8161,9 @@
       <c r="B297" s="9">
         <v>295</v>
       </c>
-      <c r="C297" s="113"/>
-      <c r="D297" s="113"/>
-      <c r="E297" s="113"/>
+      <c r="C297" s="108"/>
+      <c r="D297" s="108"/>
+      <c r="E297" s="108"/>
       <c r="F297" s="9" t="s">
         <v>10</v>
       </c>
@@ -8209,6 +8221,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="E3:E27"/>
+    <mergeCell ref="E28:E31"/>
+    <mergeCell ref="E33:E37"/>
+    <mergeCell ref="E38:E40"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="E44:E53"/>
+    <mergeCell ref="E54:E86"/>
+    <mergeCell ref="E87:E91"/>
+    <mergeCell ref="E92:E98"/>
+    <mergeCell ref="E99:E107"/>
+    <mergeCell ref="E108:E117"/>
+    <mergeCell ref="E118:E126"/>
+    <mergeCell ref="E127:E132"/>
+    <mergeCell ref="E134:E135"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="E139:E161"/>
+    <mergeCell ref="E162:E164"/>
+    <mergeCell ref="E165:E168"/>
+    <mergeCell ref="E169:E186"/>
+    <mergeCell ref="E187:E192"/>
+    <mergeCell ref="E267:E269"/>
+    <mergeCell ref="E271:E273"/>
+    <mergeCell ref="E193:E197"/>
+    <mergeCell ref="E199:E200"/>
+    <mergeCell ref="E201:E206"/>
+    <mergeCell ref="E207:E215"/>
+    <mergeCell ref="E216:E253"/>
     <mergeCell ref="C284:C297"/>
     <mergeCell ref="C138:C282"/>
     <mergeCell ref="C3:C137"/>
@@ -8225,33 +8264,6 @@
     <mergeCell ref="E255:E257"/>
     <mergeCell ref="E258:E264"/>
     <mergeCell ref="E265:E266"/>
-    <mergeCell ref="E267:E269"/>
-    <mergeCell ref="E271:E273"/>
-    <mergeCell ref="E193:E197"/>
-    <mergeCell ref="E199:E200"/>
-    <mergeCell ref="E201:E206"/>
-    <mergeCell ref="E207:E215"/>
-    <mergeCell ref="E216:E253"/>
-    <mergeCell ref="E139:E161"/>
-    <mergeCell ref="E162:E164"/>
-    <mergeCell ref="E165:E168"/>
-    <mergeCell ref="E169:E186"/>
-    <mergeCell ref="E187:E192"/>
-    <mergeCell ref="E108:E117"/>
-    <mergeCell ref="E118:E126"/>
-    <mergeCell ref="E127:E132"/>
-    <mergeCell ref="E134:E135"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="E44:E53"/>
-    <mergeCell ref="E54:E86"/>
-    <mergeCell ref="E87:E91"/>
-    <mergeCell ref="E92:E98"/>
-    <mergeCell ref="E99:E107"/>
-    <mergeCell ref="E3:E27"/>
-    <mergeCell ref="E28:E31"/>
-    <mergeCell ref="E33:E37"/>
-    <mergeCell ref="E38:E40"/>
-    <mergeCell ref="E41:E43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -8332,16 +8344,16 @@
       <c r="B4" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="C4" s="132" t="s">
+      <c r="C4" s="117" t="s">
         <v>417</v>
       </c>
-      <c r="D4" s="132"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="132"/>
-      <c r="I4" s="132"/>
-      <c r="J4" s="132"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="15" t="s">
@@ -8428,7 +8440,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="114" t="s">
+      <c r="A9" s="112" t="s">
         <v>936</v>
       </c>
       <c r="B9" s="136" t="s">
@@ -8460,21 +8472,21 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="114"/>
+      <c r="A10" s="112"/>
       <c r="B10" s="137"/>
-      <c r="C10" s="125" t="s">
+      <c r="C10" s="119" t="s">
         <v>940</v>
       </c>
-      <c r="D10" s="128"/>
-      <c r="E10" s="128"/>
-      <c r="F10" s="128"/>
-      <c r="G10" s="128"/>
-      <c r="H10" s="128"/>
-      <c r="I10" s="128"/>
-      <c r="J10" s="126"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="120"/>
+      <c r="H10" s="120"/>
+      <c r="I10" s="120"/>
+      <c r="J10" s="121"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="114"/>
+      <c r="A11" s="112"/>
       <c r="B11" s="136" t="s">
         <v>938</v>
       </c>
@@ -8508,16 +8520,16 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="137"/>
-      <c r="C12" s="125" t="s">
+      <c r="C12" s="119" t="s">
         <v>941</v>
       </c>
-      <c r="D12" s="128"/>
-      <c r="E12" s="128"/>
-      <c r="F12" s="128"/>
-      <c r="G12" s="128"/>
-      <c r="H12" s="128"/>
-      <c r="I12" s="128"/>
-      <c r="J12" s="126"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="120"/>
+      <c r="F12" s="120"/>
+      <c r="G12" s="120"/>
+      <c r="H12" s="120"/>
+      <c r="I12" s="120"/>
+      <c r="J12" s="121"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I15" s="1" t="s">
@@ -9252,7 +9264,7 @@
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="114" t="s">
+      <c r="B5" s="112" t="s">
         <v>546</v>
       </c>
       <c r="C5" t="s">
@@ -9261,49 +9273,49 @@
       <c r="D5" t="s">
         <v>241</v>
       </c>
-      <c r="E5" s="114">
+      <c r="E5" s="112">
         <v>16</v>
       </c>
       <c r="F5" s="21"/>
-      <c r="G5" s="114">
+      <c r="G5" s="112">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="114"/>
+      <c r="B6" s="112"/>
       <c r="C6" t="s">
         <v>543</v>
       </c>
       <c r="D6" t="s">
         <v>237</v>
       </c>
-      <c r="E6" s="114"/>
+      <c r="E6" s="112"/>
       <c r="F6" s="21"/>
-      <c r="G6" s="114"/>
+      <c r="G6" s="112"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="114"/>
+      <c r="B7" s="112"/>
       <c r="C7" t="s">
         <v>544</v>
       </c>
       <c r="D7" t="s">
         <v>238</v>
       </c>
-      <c r="E7" s="114"/>
+      <c r="E7" s="112"/>
       <c r="F7" s="21"/>
-      <c r="G7" s="114"/>
+      <c r="G7" s="112"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="114"/>
+      <c r="B8" s="112"/>
       <c r="C8" t="s">
         <v>545</v>
       </c>
       <c r="D8" t="s">
         <v>239</v>
       </c>
-      <c r="E8" s="114"/>
+      <c r="E8" s="112"/>
       <c r="F8" s="21"/>
-      <c r="G8" s="114"/>
+      <c r="G8" s="112"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
@@ -9323,7 +9335,7 @@
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="114" t="s">
+      <c r="B10" s="112" t="s">
         <v>322</v>
       </c>
       <c r="C10" t="s">
@@ -9332,184 +9344,184 @@
       <c r="D10" t="s">
         <v>243</v>
       </c>
-      <c r="E10" s="114">
+      <c r="E10" s="112">
         <v>16</v>
       </c>
       <c r="F10" s="21"/>
-      <c r="G10" s="114">
+      <c r="G10" s="112">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="114"/>
+      <c r="B11" s="112"/>
       <c r="C11" t="s">
         <v>269</v>
       </c>
       <c r="D11" t="s">
         <v>244</v>
       </c>
-      <c r="E11" s="114"/>
+      <c r="E11" s="112"/>
       <c r="F11" s="21"/>
-      <c r="G11" s="114"/>
+      <c r="G11" s="112"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="114"/>
+      <c r="B12" s="112"/>
       <c r="C12" t="s">
         <v>270</v>
       </c>
       <c r="D12" t="s">
         <v>245</v>
       </c>
-      <c r="E12" s="114"/>
+      <c r="E12" s="112"/>
       <c r="F12" s="21"/>
-      <c r="G12" s="114"/>
+      <c r="G12" s="112"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="114"/>
+      <c r="B13" s="112"/>
       <c r="C13" t="s">
         <v>271</v>
       </c>
       <c r="D13" t="s">
         <v>246</v>
       </c>
-      <c r="E13" s="114"/>
+      <c r="E13" s="112"/>
       <c r="F13" s="21"/>
-      <c r="G13" s="114"/>
+      <c r="G13" s="112"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="114"/>
+      <c r="B14" s="112"/>
       <c r="C14" t="s">
         <v>272</v>
       </c>
       <c r="D14" t="s">
         <v>242</v>
       </c>
-      <c r="E14" s="114"/>
+      <c r="E14" s="112"/>
       <c r="F14" s="21"/>
-      <c r="G14" s="114"/>
+      <c r="G14" s="112"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="114"/>
+      <c r="B15" s="112"/>
       <c r="C15" t="s">
         <v>273</v>
       </c>
       <c r="D15" t="s">
         <v>247</v>
       </c>
-      <c r="E15" s="114"/>
+      <c r="E15" s="112"/>
       <c r="F15" s="21"/>
-      <c r="G15" s="114"/>
+      <c r="G15" s="112"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="114"/>
+      <c r="B16" s="112"/>
       <c r="C16" t="s">
         <v>274</v>
       </c>
       <c r="D16" t="s">
         <v>260</v>
       </c>
-      <c r="E16" s="114"/>
+      <c r="E16" s="112"/>
       <c r="F16" s="21"/>
-      <c r="G16" s="114"/>
+      <c r="G16" s="112"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="114"/>
+      <c r="B17" s="112"/>
       <c r="C17" t="s">
         <v>275</v>
       </c>
       <c r="D17" t="s">
         <v>261</v>
       </c>
-      <c r="E17" s="114"/>
+      <c r="E17" s="112"/>
       <c r="F17" s="21"/>
-      <c r="G17" s="114"/>
+      <c r="G17" s="112"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="114"/>
+      <c r="B18" s="112"/>
       <c r="C18" t="s">
         <v>276</v>
       </c>
       <c r="D18" t="s">
         <v>262</v>
       </c>
-      <c r="E18" s="114"/>
+      <c r="E18" s="112"/>
       <c r="F18" s="21"/>
-      <c r="G18" s="114"/>
+      <c r="G18" s="112"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B19" s="114"/>
+      <c r="B19" s="112"/>
       <c r="C19" t="s">
         <v>277</v>
       </c>
       <c r="D19" t="s">
         <v>263</v>
       </c>
-      <c r="E19" s="114"/>
+      <c r="E19" s="112"/>
       <c r="F19" s="21"/>
-      <c r="G19" s="114"/>
+      <c r="G19" s="112"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="114"/>
+      <c r="B20" s="112"/>
       <c r="C20" t="s">
         <v>278</v>
       </c>
       <c r="D20" t="s">
         <v>264</v>
       </c>
-      <c r="E20" s="114"/>
+      <c r="E20" s="112"/>
       <c r="F20" s="21"/>
-      <c r="G20" s="114"/>
+      <c r="G20" s="112"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B21" s="114"/>
+      <c r="B21" s="112"/>
       <c r="C21" t="s">
         <v>279</v>
       </c>
       <c r="D21" t="s">
         <v>265</v>
       </c>
-      <c r="E21" s="114"/>
+      <c r="E21" s="112"/>
       <c r="F21" s="21"/>
-      <c r="G21" s="114"/>
+      <c r="G21" s="112"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="114"/>
+      <c r="B22" s="112"/>
       <c r="C22" t="s">
         <v>280</v>
       </c>
       <c r="D22" t="s">
         <v>266</v>
       </c>
-      <c r="E22" s="114"/>
+      <c r="E22" s="112"/>
       <c r="F22" s="21"/>
-      <c r="G22" s="114"/>
+      <c r="G22" s="112"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B23" s="114"/>
+      <c r="B23" s="112"/>
       <c r="C23" t="s">
         <v>281</v>
       </c>
       <c r="D23" t="s">
         <v>267</v>
       </c>
-      <c r="E23" s="114"/>
+      <c r="E23" s="112"/>
       <c r="F23" s="21"/>
-      <c r="G23" s="114"/>
+      <c r="G23" s="112"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="114"/>
+      <c r="B24" s="112"/>
       <c r="C24" s="70" t="s">
         <v>847</v>
       </c>
       <c r="D24" s="70" t="s">
         <v>848</v>
       </c>
-      <c r="E24" s="114"/>
+      <c r="E24" s="112"/>
       <c r="F24" s="21"/>
-      <c r="G24" s="114"/>
+      <c r="G24" s="112"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="114" t="s">
+      <c r="B25" s="112" t="s">
         <v>321</v>
       </c>
       <c r="C25" t="s">
@@ -9518,237 +9530,237 @@
       <c r="D25" t="s">
         <v>301</v>
       </c>
-      <c r="E25" s="114"/>
+      <c r="E25" s="112"/>
       <c r="F25" s="21"/>
-      <c r="G25" s="114"/>
+      <c r="G25" s="112"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B26" s="114"/>
+      <c r="B26" s="112"/>
       <c r="C26" t="s">
         <v>283</v>
       </c>
       <c r="D26" t="s">
         <v>302</v>
       </c>
-      <c r="E26" s="114"/>
+      <c r="E26" s="112"/>
       <c r="F26" s="21"/>
-      <c r="G26" s="114"/>
+      <c r="G26" s="112"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B27" s="114"/>
+      <c r="B27" s="112"/>
       <c r="C27" t="s">
         <v>284</v>
       </c>
       <c r="D27" t="s">
         <v>303</v>
       </c>
-      <c r="E27" s="114"/>
+      <c r="E27" s="112"/>
       <c r="F27" s="21"/>
-      <c r="G27" s="114"/>
+      <c r="G27" s="112"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="114"/>
+      <c r="B28" s="112"/>
       <c r="C28" t="s">
         <v>285</v>
       </c>
       <c r="D28" t="s">
         <v>304</v>
       </c>
-      <c r="E28" s="114"/>
+      <c r="E28" s="112"/>
       <c r="F28" s="21"/>
-      <c r="G28" s="114"/>
+      <c r="G28" s="112"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B29" s="114"/>
+      <c r="B29" s="112"/>
       <c r="C29" t="s">
         <v>286</v>
       </c>
       <c r="D29" t="s">
         <v>305</v>
       </c>
-      <c r="E29" s="114"/>
+      <c r="E29" s="112"/>
       <c r="F29" s="21"/>
-      <c r="G29" s="114"/>
+      <c r="G29" s="112"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B30" s="114"/>
+      <c r="B30" s="112"/>
       <c r="C30" t="s">
         <v>287</v>
       </c>
       <c r="D30" t="s">
         <v>306</v>
       </c>
-      <c r="E30" s="114"/>
+      <c r="E30" s="112"/>
       <c r="F30" s="21"/>
-      <c r="G30" s="114"/>
+      <c r="G30" s="112"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B31" s="114"/>
+      <c r="B31" s="112"/>
       <c r="C31" t="s">
         <v>288</v>
       </c>
       <c r="D31" t="s">
         <v>307</v>
       </c>
-      <c r="E31" s="114"/>
+      <c r="E31" s="112"/>
       <c r="F31" s="21"/>
-      <c r="G31" s="114"/>
+      <c r="G31" s="112"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B32" s="114"/>
+      <c r="B32" s="112"/>
       <c r="C32" t="s">
         <v>289</v>
       </c>
       <c r="D32" t="s">
         <v>308</v>
       </c>
-      <c r="E32" s="114"/>
+      <c r="E32" s="112"/>
       <c r="F32" s="21"/>
-      <c r="G32" s="114"/>
+      <c r="G32" s="112"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="114"/>
+      <c r="B33" s="112"/>
       <c r="C33" t="s">
         <v>290</v>
       </c>
       <c r="D33" t="s">
         <v>309</v>
       </c>
-      <c r="E33" s="114"/>
+      <c r="E33" s="112"/>
       <c r="F33" s="21"/>
-      <c r="G33" s="114"/>
+      <c r="G33" s="112"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="114"/>
+      <c r="B34" s="112"/>
       <c r="C34" s="30" t="s">
         <v>596</v>
       </c>
       <c r="D34" t="s">
         <v>597</v>
       </c>
-      <c r="E34" s="114"/>
+      <c r="E34" s="112"/>
       <c r="F34" s="21"/>
-      <c r="G34" s="114"/>
+      <c r="G34" s="112"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B35" s="114"/>
+      <c r="B35" s="112"/>
       <c r="C35" t="s">
         <v>291</v>
       </c>
       <c r="D35" t="s">
         <v>310</v>
       </c>
-      <c r="E35" s="114"/>
+      <c r="E35" s="112"/>
       <c r="F35" s="21"/>
-      <c r="G35" s="114"/>
+      <c r="G35" s="112"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B36" s="114"/>
+      <c r="B36" s="112"/>
       <c r="C36" t="s">
         <v>292</v>
       </c>
       <c r="D36" t="s">
         <v>311</v>
       </c>
-      <c r="E36" s="114"/>
+      <c r="E36" s="112"/>
       <c r="F36" s="21"/>
-      <c r="G36" s="114"/>
+      <c r="G36" s="112"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B37" s="114"/>
+      <c r="B37" s="112"/>
       <c r="C37" t="s">
         <v>293</v>
       </c>
       <c r="D37" t="s">
         <v>312</v>
       </c>
-      <c r="E37" s="114"/>
+      <c r="E37" s="112"/>
       <c r="F37" s="21"/>
-      <c r="G37" s="114"/>
+      <c r="G37" s="112"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="114"/>
+      <c r="B38" s="112"/>
       <c r="C38" t="s">
         <v>294</v>
       </c>
       <c r="D38" t="s">
         <v>313</v>
       </c>
-      <c r="E38" s="114"/>
+      <c r="E38" s="112"/>
       <c r="F38" s="21"/>
-      <c r="G38" s="114"/>
+      <c r="G38" s="112"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B39" s="114"/>
+      <c r="B39" s="112"/>
       <c r="C39" t="s">
         <v>295</v>
       </c>
       <c r="D39" t="s">
         <v>314</v>
       </c>
-      <c r="E39" s="114"/>
+      <c r="E39" s="112"/>
       <c r="F39" s="21"/>
-      <c r="G39" s="114"/>
+      <c r="G39" s="112"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="114"/>
+      <c r="B40" s="112"/>
       <c r="C40" t="s">
         <v>296</v>
       </c>
       <c r="D40" t="s">
         <v>315</v>
       </c>
-      <c r="E40" s="114"/>
+      <c r="E40" s="112"/>
       <c r="F40" s="21"/>
-      <c r="G40" s="114"/>
+      <c r="G40" s="112"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="114"/>
+      <c r="B41" s="112"/>
       <c r="C41" t="s">
         <v>297</v>
       </c>
       <c r="D41" t="s">
         <v>316</v>
       </c>
-      <c r="E41" s="114"/>
+      <c r="E41" s="112"/>
       <c r="F41" s="21"/>
-      <c r="G41" s="114"/>
+      <c r="G41" s="112"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B42" s="114"/>
+      <c r="B42" s="112"/>
       <c r="C42" t="s">
         <v>298</v>
       </c>
       <c r="D42" t="s">
         <v>317</v>
       </c>
-      <c r="E42" s="114"/>
+      <c r="E42" s="112"/>
       <c r="F42" s="21"/>
-      <c r="G42" s="114"/>
+      <c r="G42" s="112"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B43" s="114"/>
+      <c r="B43" s="112"/>
       <c r="C43" t="s">
         <v>299</v>
       </c>
       <c r="D43" t="s">
         <v>318</v>
       </c>
-      <c r="E43" s="114"/>
+      <c r="E43" s="112"/>
       <c r="F43" s="21"/>
-      <c r="G43" s="114"/>
+      <c r="G43" s="112"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B44" s="114"/>
+      <c r="B44" s="112"/>
       <c r="C44" t="s">
         <v>300</v>
       </c>
       <c r="D44" t="s">
         <v>319</v>
       </c>
-      <c r="E44" s="114"/>
+      <c r="E44" s="112"/>
       <c r="F44" s="21"/>
-      <c r="G44" s="114"/>
+      <c r="G44" s="112"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
@@ -9925,11 +9937,11 @@
       <c r="C57" t="s">
         <v>556</v>
       </c>
-      <c r="E57" s="114">
+      <c r="E57" s="112">
         <v>8</v>
       </c>
       <c r="F57" s="21"/>
-      <c r="G57" s="114">
+      <c r="G57" s="112">
         <v>17</v>
       </c>
     </row>
@@ -9940,9 +9952,9 @@
       <c r="C58" t="s">
         <v>557</v>
       </c>
-      <c r="E58" s="114"/>
+      <c r="E58" s="112"/>
       <c r="F58" s="21"/>
-      <c r="G58" s="114"/>
+      <c r="G58" s="112"/>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
@@ -9951,9 +9963,9 @@
       <c r="C59" t="s">
         <v>558</v>
       </c>
-      <c r="E59" s="114"/>
+      <c r="E59" s="112"/>
       <c r="F59" s="21"/>
-      <c r="G59" s="114"/>
+      <c r="G59" s="112"/>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
@@ -9962,9 +9974,9 @@
       <c r="C60" t="s">
         <v>559</v>
       </c>
-      <c r="E60" s="114"/>
+      <c r="E60" s="112"/>
       <c r="F60" s="21"/>
-      <c r="G60" s="114"/>
+      <c r="G60" s="112"/>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
@@ -9973,9 +9985,9 @@
       <c r="C61" t="s">
         <v>560</v>
       </c>
-      <c r="E61" s="114"/>
+      <c r="E61" s="112"/>
       <c r="F61" s="21"/>
-      <c r="G61" s="114"/>
+      <c r="G61" s="112"/>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
@@ -9987,9 +9999,9 @@
       <c r="D62" t="s">
         <v>377</v>
       </c>
-      <c r="E62" s="114"/>
+      <c r="E62" s="112"/>
       <c r="F62" s="21"/>
-      <c r="G62" s="114"/>
+      <c r="G62" s="112"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
@@ -9998,9 +10010,9 @@
       <c r="C63" t="s">
         <v>562</v>
       </c>
-      <c r="E63" s="114"/>
+      <c r="E63" s="112"/>
       <c r="F63" s="21"/>
-      <c r="G63" s="114"/>
+      <c r="G63" s="112"/>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
@@ -10009,9 +10021,9 @@
       <c r="C64" t="s">
         <v>563</v>
       </c>
-      <c r="E64" s="114"/>
+      <c r="E64" s="112"/>
       <c r="F64" s="21"/>
-      <c r="G64" s="114"/>
+      <c r="G64" s="112"/>
     </row>
     <row r="65" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B65" s="31" t="s">
@@ -10039,10 +10051,10 @@
       <c r="F66" s="37" t="s">
         <v>625</v>
       </c>
-      <c r="G66" s="114">
+      <c r="G66" s="112">
         <v>21</v>
       </c>
-      <c r="H66" s="115" t="s">
+      <c r="H66" s="111" t="s">
         <v>678</v>
       </c>
     </row>
@@ -10059,8 +10071,8 @@
       <c r="F67" s="1">
         <v>2</v>
       </c>
-      <c r="G67" s="114"/>
-      <c r="H67" s="115"/>
+      <c r="G67" s="112"/>
+      <c r="H67" s="111"/>
     </row>
     <row r="68" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
@@ -10075,8 +10087,8 @@
       <c r="F68" s="1">
         <v>1</v>
       </c>
-      <c r="G68" s="114"/>
-      <c r="H68" s="115"/>
+      <c r="G68" s="112"/>
+      <c r="H68" s="111"/>
     </row>
     <row r="69" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
@@ -10091,7 +10103,7 @@
       <c r="F69" s="1">
         <v>1</v>
       </c>
-      <c r="G69" s="114"/>
+      <c r="G69" s="112"/>
       <c r="H69" s="42"/>
     </row>
     <row r="70" spans="2:13" x14ac:dyDescent="0.3">
@@ -10104,7 +10116,7 @@
       <c r="E70" s="1">
         <v>8</v>
       </c>
-      <c r="G70" s="114"/>
+      <c r="G70" s="112"/>
       <c r="H70" s="42"/>
     </row>
     <row r="71" spans="2:13" x14ac:dyDescent="0.3">
@@ -10133,7 +10145,7 @@
       <c r="F72" s="1">
         <v>3</v>
       </c>
-      <c r="G72" s="114">
+      <c r="G72" s="112">
         <v>21</v>
       </c>
       <c r="H72" s="42"/>
@@ -10151,7 +10163,7 @@
       <c r="F73" s="1">
         <v>0</v>
       </c>
-      <c r="G73" s="114"/>
+      <c r="G73" s="112"/>
       <c r="H73" s="42"/>
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.3">
@@ -10167,7 +10179,7 @@
       <c r="F74" s="1">
         <v>1</v>
       </c>
-      <c r="G74" s="114"/>
+      <c r="G74" s="112"/>
       <c r="H74" s="42"/>
     </row>
     <row r="75" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -10493,11 +10505,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="H66:H68"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="G10:G44"/>
-    <mergeCell ref="G57:G64"/>
-    <mergeCell ref="G66:G70"/>
     <mergeCell ref="G72:G74"/>
     <mergeCell ref="E57:E64"/>
     <mergeCell ref="B25:B44"/>
@@ -10505,6 +10512,11 @@
     <mergeCell ref="E10:E44"/>
     <mergeCell ref="E5:E8"/>
     <mergeCell ref="B10:B24"/>
+    <mergeCell ref="H66:H68"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="G10:G44"/>
+    <mergeCell ref="G57:G64"/>
+    <mergeCell ref="G66:G70"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -10896,7 +10908,7 @@
         <v>343</v>
       </c>
       <c r="D9" t="s">
-        <v>359</v>
+        <v>1018</v>
       </c>
       <c r="E9" t="s">
         <v>360</v>
@@ -11462,7 +11474,7 @@
         <v>817</v>
       </c>
       <c r="F24" s="46"/>
-      <c r="H24" s="116"/>
+      <c r="H24" s="107"/>
       <c r="J24" s="6"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
@@ -11492,7 +11504,7 @@
         <v>348</v>
       </c>
       <c r="F25" s="46"/>
-      <c r="H25" s="116"/>
+      <c r="H25" s="107"/>
       <c r="J25" s="6"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
@@ -13061,6 +13073,15 @@
       <c r="B149">
         <v>8</v>
       </c>
+      <c r="C149" t="s">
+        <v>367</v>
+      </c>
+      <c r="D149" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E149" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150">
@@ -13456,6 +13477,15 @@
       </c>
       <c r="B187">
         <v>6</v>
+      </c>
+      <c r="C187" t="s">
+        <v>343</v>
+      </c>
+      <c r="D187" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E187" t="s">
+        <v>1020</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
@@ -13580,7 +13610,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBDE0FB1-7DD1-4E21-83BF-00F92B42EB01}">
-  <dimension ref="A2:F257"/>
+  <dimension ref="A2:F274"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" style="1" customWidth="1"/>
@@ -13623,7 +13653,7 @@
       <c r="E3" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="F3" s="117" t="s">
+      <c r="F3" s="113" t="s">
         <v>233</v>
       </c>
     </row>
@@ -13643,7 +13673,7 @@
       <c r="E4" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="F4" s="114"/>
+      <c r="F4" s="112"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
@@ -13655,7 +13685,7 @@
       <c r="C5" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F5" s="114"/>
+      <c r="F5" s="112"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
@@ -13667,7 +13697,7 @@
       <c r="C6" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F6" s="114"/>
+      <c r="F6" s="112"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
@@ -13679,7 +13709,7 @@
       <c r="C7" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F7" s="114"/>
+      <c r="F7" s="112"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
@@ -13691,7 +13721,7 @@
       <c r="C8" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F8" s="114"/>
+      <c r="F8" s="112"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
@@ -13781,7 +13811,7 @@
       <c r="C15" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F15" s="114" t="s">
+      <c r="F15" s="112" t="s">
         <v>361</v>
       </c>
     </row>
@@ -13795,7 +13825,7 @@
       <c r="C16" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F16" s="114"/>
+      <c r="F16" s="112"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
@@ -13807,7 +13837,7 @@
       <c r="C17" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F17" s="114"/>
+      <c r="F17" s="112"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
@@ -13819,7 +13849,7 @@
       <c r="C18" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F18" s="114"/>
+      <c r="F18" s="112"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
@@ -13831,7 +13861,7 @@
       <c r="C19" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F19" s="114"/>
+      <c r="F19" s="112"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
@@ -13843,7 +13873,7 @@
       <c r="C20" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F20" s="114"/>
+      <c r="F20" s="112"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
@@ -13855,7 +13885,7 @@
       <c r="C21" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F21" s="114"/>
+      <c r="F21" s="112"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
@@ -13867,7 +13897,7 @@
       <c r="C22" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F22" s="114"/>
+      <c r="F22" s="112"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
@@ -13879,7 +13909,7 @@
       <c r="C23" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F23" s="114"/>
+      <c r="F23" s="112"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
@@ -13891,7 +13921,7 @@
       <c r="C24" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F24" s="114"/>
+      <c r="F24" s="112"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
@@ -13903,7 +13933,7 @@
       <c r="C25" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F25" s="114"/>
+      <c r="F25" s="112"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
@@ -13915,7 +13945,7 @@
       <c r="C26" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F26" s="114"/>
+      <c r="F26" s="112"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
@@ -13927,7 +13957,7 @@
       <c r="C27" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F27" s="114"/>
+      <c r="F27" s="112"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
@@ -13939,7 +13969,7 @@
       <c r="C28" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F28" s="114"/>
+      <c r="F28" s="112"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
@@ -13951,7 +13981,7 @@
       <c r="C29" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F29" s="114"/>
+      <c r="F29" s="112"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
@@ -13963,7 +13993,7 @@
       <c r="C30" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F30" s="114"/>
+      <c r="F30" s="112"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
@@ -13975,7 +14005,7 @@
       <c r="C31" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F31" s="114"/>
+      <c r="F31" s="112"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
@@ -13987,7 +14017,7 @@
       <c r="C32" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F32" s="114"/>
+      <c r="F32" s="112"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
@@ -13999,7 +14029,7 @@
       <c r="C33" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F33" s="114"/>
+      <c r="F33" s="112"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
@@ -14011,7 +14041,7 @@
       <c r="C34" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F34" s="114"/>
+      <c r="F34" s="112"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
@@ -14023,7 +14053,7 @@
       <c r="C35" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F35" s="114"/>
+      <c r="F35" s="112"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
@@ -14035,7 +14065,7 @@
       <c r="C36" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F36" s="114"/>
+      <c r="F36" s="112"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
@@ -14047,7 +14077,7 @@
       <c r="C37" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F37" s="114"/>
+      <c r="F37" s="112"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
@@ -14059,7 +14089,7 @@
       <c r="C38" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F38" s="114"/>
+      <c r="F38" s="112"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
@@ -14071,7 +14101,7 @@
       <c r="C39" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F39" s="114"/>
+      <c r="F39" s="112"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
@@ -14083,7 +14113,7 @@
       <c r="C40" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F40" s="114" t="s">
+      <c r="F40" s="112" t="s">
         <v>372</v>
       </c>
     </row>
@@ -14097,7 +14127,7 @@
       <c r="C41" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F41" s="114"/>
+      <c r="F41" s="112"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
@@ -14109,7 +14139,7 @@
       <c r="C42" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F42" s="114"/>
+      <c r="F42" s="112"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
@@ -14129,7 +14159,7 @@
       <c r="C44" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F44" s="114" t="s">
+      <c r="F44" s="112" t="s">
         <v>371</v>
       </c>
     </row>
@@ -14143,7 +14173,7 @@
       <c r="C45" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F45" s="114"/>
+      <c r="F45" s="112"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
@@ -14155,7 +14185,7 @@
       <c r="C46" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F46" s="114"/>
+      <c r="F46" s="112"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
@@ -14170,7 +14200,7 @@
       <c r="E47" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="F47" s="114" t="s">
+      <c r="F47" s="112" t="s">
         <v>229</v>
       </c>
     </row>
@@ -14187,7 +14217,7 @@
       <c r="E48" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="F48" s="114"/>
+      <c r="F48" s="112"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
@@ -14205,7 +14235,7 @@
       <c r="E49" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="F49" s="114"/>
+      <c r="F49" s="112"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
@@ -14254,6 +14284,9 @@
       <c r="B55" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="C55" s="1" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
@@ -14262,6 +14295,9 @@
       <c r="B56" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="C56" s="1" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
@@ -15818,9 +15854,90 @@
         <v>253</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>254</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A260" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A261" s="1">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A262" s="1">
+        <v>402</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A263" s="1">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A264" s="1">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A265" s="1">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A266" s="1">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A267" s="1">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A268" s="1">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A269" s="1">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A270" s="1">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A271" s="1">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A272" s="1">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A273" s="1">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A274" s="1">
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -15832,6 +15949,7 @@
     <mergeCell ref="F3:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15880,7 +15998,7 @@
       <c r="E3" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="F3" s="117" t="s">
+      <c r="F3" s="113" t="s">
         <v>233</v>
       </c>
     </row>
@@ -15900,7 +16018,7 @@
       <c r="E4" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="F4" s="114"/>
+      <c r="F4" s="112"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
@@ -15912,7 +16030,7 @@
       <c r="C5" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="F5" s="114"/>
+      <c r="F5" s="112"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
@@ -15921,7 +16039,7 @@
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="114"/>
+      <c r="F6" s="112"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
@@ -15930,7 +16048,7 @@
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="114"/>
+      <c r="F7" s="112"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
@@ -15939,7 +16057,7 @@
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="114"/>
+      <c r="F8" s="112"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
@@ -16026,7 +16144,7 @@
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="114" t="s">
+      <c r="F15" s="112" t="s">
         <v>361</v>
       </c>
     </row>
@@ -16037,7 +16155,7 @@
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="114"/>
+      <c r="F16" s="112"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
@@ -16046,7 +16164,7 @@
       <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="114"/>
+      <c r="F17" s="112"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
@@ -16055,7 +16173,7 @@
       <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="114"/>
+      <c r="F18" s="112"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
@@ -16064,7 +16182,7 @@
       <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="114"/>
+      <c r="F19" s="112"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
@@ -16073,7 +16191,7 @@
       <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="114"/>
+      <c r="F20" s="112"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
@@ -16082,7 +16200,7 @@
       <c r="B21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="114"/>
+      <c r="F21" s="112"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
@@ -16091,7 +16209,7 @@
       <c r="B22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="114"/>
+      <c r="F22" s="112"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
@@ -16100,7 +16218,7 @@
       <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="114"/>
+      <c r="F23" s="112"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
@@ -16109,7 +16227,7 @@
       <c r="B24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="114"/>
+      <c r="F24" s="112"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
@@ -16118,7 +16236,7 @@
       <c r="B25" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F25" s="114"/>
+      <c r="F25" s="112"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
@@ -16127,7 +16245,7 @@
       <c r="B26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F26" s="114"/>
+      <c r="F26" s="112"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
@@ -16136,7 +16254,7 @@
       <c r="B27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F27" s="114"/>
+      <c r="F27" s="112"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
@@ -16145,7 +16263,7 @@
       <c r="B28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F28" s="114"/>
+      <c r="F28" s="112"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
@@ -16154,7 +16272,7 @@
       <c r="B29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F29" s="114"/>
+      <c r="F29" s="112"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
@@ -16163,7 +16281,7 @@
       <c r="B30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="114"/>
+      <c r="F30" s="112"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
@@ -16172,7 +16290,7 @@
       <c r="B31" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F31" s="114"/>
+      <c r="F31" s="112"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
@@ -16181,7 +16299,7 @@
       <c r="B32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F32" s="114"/>
+      <c r="F32" s="112"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
@@ -16190,7 +16308,7 @@
       <c r="B33" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F33" s="114"/>
+      <c r="F33" s="112"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
@@ -16199,7 +16317,7 @@
       <c r="B34" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F34" s="114"/>
+      <c r="F34" s="112"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
@@ -16208,7 +16326,7 @@
       <c r="B35" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F35" s="114"/>
+      <c r="F35" s="112"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
@@ -16217,7 +16335,7 @@
       <c r="B36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F36" s="114"/>
+      <c r="F36" s="112"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
@@ -16226,7 +16344,7 @@
       <c r="B37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F37" s="114"/>
+      <c r="F37" s="112"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
@@ -16235,7 +16353,7 @@
       <c r="B38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F38" s="114"/>
+      <c r="F38" s="112"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
@@ -16244,7 +16362,7 @@
       <c r="B39" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F39" s="114"/>
+      <c r="F39" s="112"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
@@ -16253,7 +16371,7 @@
       <c r="B40" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F40" s="114" t="s">
+      <c r="F40" s="112" t="s">
         <v>372</v>
       </c>
     </row>
@@ -16264,7 +16382,7 @@
       <c r="B41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F41" s="114"/>
+      <c r="F41" s="112"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
@@ -16273,7 +16391,7 @@
       <c r="B42" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F42" s="114"/>
+      <c r="F42" s="112"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
@@ -16290,7 +16408,7 @@
       <c r="B44" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F44" s="114" t="s">
+      <c r="F44" s="112" t="s">
         <v>371</v>
       </c>
     </row>
@@ -16301,7 +16419,7 @@
       <c r="B45" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F45" s="114"/>
+      <c r="F45" s="112"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
@@ -16310,7 +16428,7 @@
       <c r="B46" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F46" s="114"/>
+      <c r="F46" s="112"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
@@ -16325,7 +16443,7 @@
       <c r="E47" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="F47" s="114" t="s">
+      <c r="F47" s="112" t="s">
         <v>229</v>
       </c>
     </row>
@@ -16342,7 +16460,7 @@
       <c r="E48" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="F48" s="114"/>
+      <c r="F48" s="112"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
@@ -16360,7 +16478,7 @@
       <c r="E49" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="F49" s="114"/>
+      <c r="F49" s="112"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
@@ -17959,38 +18077,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="D2" s="118" t="s">
+      <c r="D2" s="114" t="s">
         <v>401</v>
       </c>
-      <c r="E2" s="118"/>
-      <c r="F2" s="118"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
       <c r="G2" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="H2" s="119" t="s">
+      <c r="H2" s="115" t="s">
         <v>402</v>
       </c>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
       <c r="K2" s="5" t="s">
         <v>404</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="N2" s="118" t="s">
+      <c r="N2" s="114" t="s">
         <v>401</v>
       </c>
-      <c r="O2" s="118"/>
-      <c r="P2" s="118"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="114"/>
       <c r="Q2" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="R2" s="119" t="s">
+      <c r="R2" s="115" t="s">
         <v>402</v>
       </c>
-      <c r="S2" s="119"/>
-      <c r="T2" s="119"/>
+      <c r="S2" s="115"/>
+      <c r="T2" s="115"/>
       <c r="U2" s="5" t="s">
         <v>404</v>
       </c>
@@ -18407,38 +18525,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="110"/>
-      <c r="AC1" s="110"/>
-      <c r="AD1" s="110"/>
-      <c r="AE1" s="110"/>
-      <c r="AF1" s="110"/>
-      <c r="AG1" s="110"/>
-      <c r="AH1" s="110"/>
-      <c r="AI1" s="110"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
+      <c r="W1" s="129"/>
+      <c r="X1" s="129"/>
+      <c r="Y1" s="129"/>
+      <c r="Z1" s="129"/>
+      <c r="AA1" s="129"/>
+      <c r="AB1" s="129"/>
+      <c r="AC1" s="129"/>
+      <c r="AD1" s="129"/>
+      <c r="AE1" s="129"/>
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="129"/>
+      <c r="AH1" s="129"/>
+      <c r="AI1" s="129"/>
     </row>
     <row r="2" spans="2:35" x14ac:dyDescent="0.3">
       <c r="C2" s="15" t="s">
@@ -18545,46 +18663,46 @@
       <c r="C4" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="D4" s="132" t="s">
+      <c r="D4" s="117" t="s">
         <v>420</v>
       </c>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="132"/>
-      <c r="I4" s="132"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132" t="s">
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
+      <c r="L4" s="117" t="s">
         <v>419</v>
       </c>
-      <c r="M4" s="132"/>
-      <c r="N4" s="132"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="132"/>
-      <c r="Q4" s="132"/>
-      <c r="R4" s="132"/>
-      <c r="S4" s="132"/>
-      <c r="T4" s="132" t="s">
+      <c r="M4" s="117"/>
+      <c r="N4" s="117"/>
+      <c r="O4" s="117"/>
+      <c r="P4" s="117"/>
+      <c r="Q4" s="117"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="117"/>
+      <c r="T4" s="117" t="s">
         <v>418</v>
       </c>
-      <c r="U4" s="132"/>
-      <c r="V4" s="132"/>
-      <c r="W4" s="132"/>
-      <c r="X4" s="132"/>
-      <c r="Y4" s="132"/>
-      <c r="Z4" s="132"/>
-      <c r="AA4" s="132"/>
-      <c r="AB4" s="132" t="s">
+      <c r="U4" s="117"/>
+      <c r="V4" s="117"/>
+      <c r="W4" s="117"/>
+      <c r="X4" s="117"/>
+      <c r="Y4" s="117"/>
+      <c r="Z4" s="117"/>
+      <c r="AA4" s="117"/>
+      <c r="AB4" s="117" t="s">
         <v>417</v>
       </c>
-      <c r="AC4" s="132"/>
-      <c r="AD4" s="132"/>
-      <c r="AE4" s="132"/>
-      <c r="AF4" s="132"/>
-      <c r="AG4" s="132"/>
-      <c r="AH4" s="132"/>
-      <c r="AI4" s="132"/>
+      <c r="AC4" s="117"/>
+      <c r="AD4" s="117"/>
+      <c r="AE4" s="117"/>
+      <c r="AF4" s="117"/>
+      <c r="AG4" s="117"/>
+      <c r="AH4" s="117"/>
+      <c r="AI4" s="117"/>
     </row>
     <row r="5" spans="2:35" x14ac:dyDescent="0.3">
       <c r="C5" s="15" t="s">
@@ -18900,44 +19018,44 @@
       <c r="B9" t="s">
         <v>162</v>
       </c>
-      <c r="D9" s="133" t="s">
+      <c r="D9" s="118" t="s">
         <v>359</v>
       </c>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="133"/>
-      <c r="K9" s="133"/>
-      <c r="L9" s="133" t="s">
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="118"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="118"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118" t="s">
         <v>422</v>
       </c>
-      <c r="M9" s="133"/>
-      <c r="N9" s="133"/>
-      <c r="O9" s="133"/>
-      <c r="P9" s="133"/>
-      <c r="Q9" s="133"/>
-      <c r="R9" s="133"/>
-      <c r="S9" s="133"/>
-      <c r="T9" s="133" t="s">
+      <c r="M9" s="118"/>
+      <c r="N9" s="118"/>
+      <c r="O9" s="118"/>
+      <c r="P9" s="118"/>
+      <c r="Q9" s="118"/>
+      <c r="R9" s="118"/>
+      <c r="S9" s="118"/>
+      <c r="T9" s="118" t="s">
         <v>423</v>
       </c>
-      <c r="U9" s="133"/>
-      <c r="V9" s="133"/>
-      <c r="W9" s="133"/>
-      <c r="X9" s="133"/>
-      <c r="Y9" s="133"/>
-      <c r="Z9" s="133"/>
-      <c r="AA9" s="133"/>
+      <c r="U9" s="118"/>
+      <c r="V9" s="118"/>
+      <c r="W9" s="118"/>
+      <c r="X9" s="118"/>
+      <c r="Y9" s="118"/>
+      <c r="Z9" s="118"/>
+      <c r="AA9" s="118"/>
       <c r="AB9" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="AC9" s="133" t="s">
+      <c r="AC9" s="118" t="s">
         <v>425</v>
       </c>
-      <c r="AD9" s="133"/>
-      <c r="AE9" s="133"/>
+      <c r="AD9" s="118"/>
+      <c r="AE9" s="118"/>
       <c r="AF9" s="5" t="s">
         <v>230</v>
       </c>
@@ -18955,36 +19073,36 @@
       <c r="C10" s="15" t="s">
         <v>426</v>
       </c>
-      <c r="D10" s="134">
+      <c r="D10" s="116">
         <v>128</v>
       </c>
-      <c r="E10" s="134"/>
-      <c r="F10" s="134"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="134"/>
-      <c r="I10" s="134"/>
-      <c r="J10" s="134"/>
-      <c r="K10" s="134"/>
-      <c r="L10" s="134">
+      <c r="E10" s="116"/>
+      <c r="F10" s="116"/>
+      <c r="G10" s="116"/>
+      <c r="H10" s="116"/>
+      <c r="I10" s="116"/>
+      <c r="J10" s="116"/>
+      <c r="K10" s="116"/>
+      <c r="L10" s="116">
         <v>100</v>
       </c>
-      <c r="M10" s="134"/>
-      <c r="N10" s="134"/>
-      <c r="O10" s="134"/>
-      <c r="P10" s="134"/>
-      <c r="Q10" s="134"/>
-      <c r="R10" s="134"/>
-      <c r="S10" s="134"/>
-      <c r="T10" s="134">
+      <c r="M10" s="116"/>
+      <c r="N10" s="116"/>
+      <c r="O10" s="116"/>
+      <c r="P10" s="116"/>
+      <c r="Q10" s="116"/>
+      <c r="R10" s="116"/>
+      <c r="S10" s="116"/>
+      <c r="T10" s="116">
         <v>128</v>
       </c>
-      <c r="U10" s="134"/>
-      <c r="V10" s="134"/>
-      <c r="W10" s="134"/>
-      <c r="X10" s="134"/>
-      <c r="Y10" s="134"/>
-      <c r="Z10" s="134"/>
-      <c r="AA10" s="134"/>
+      <c r="U10" s="116"/>
+      <c r="V10" s="116"/>
+      <c r="W10" s="116"/>
+      <c r="X10" s="116"/>
+      <c r="Y10" s="116"/>
+      <c r="Z10" s="116"/>
+      <c r="AA10" s="116"/>
       <c r="AB10" s="5">
         <v>1</v>
       </c>
@@ -19014,44 +19132,44 @@
       <c r="C11" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="D11" s="134">
+      <c r="D11" s="116">
         <v>80</v>
       </c>
-      <c r="E11" s="134"/>
-      <c r="F11" s="134"/>
-      <c r="G11" s="134"/>
-      <c r="H11" s="134"/>
-      <c r="I11" s="134"/>
-      <c r="J11" s="134"/>
-      <c r="K11" s="134"/>
-      <c r="L11" s="134">
+      <c r="E11" s="116"/>
+      <c r="F11" s="116"/>
+      <c r="G11" s="116"/>
+      <c r="H11" s="116"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="116"/>
+      <c r="L11" s="116">
         <v>64</v>
       </c>
-      <c r="M11" s="134"/>
-      <c r="N11" s="134"/>
-      <c r="O11" s="134"/>
-      <c r="P11" s="134"/>
-      <c r="Q11" s="134"/>
-      <c r="R11" s="134"/>
-      <c r="S11" s="134"/>
-      <c r="T11" s="134">
+      <c r="M11" s="116"/>
+      <c r="N11" s="116"/>
+      <c r="O11" s="116"/>
+      <c r="P11" s="116"/>
+      <c r="Q11" s="116"/>
+      <c r="R11" s="116"/>
+      <c r="S11" s="116"/>
+      <c r="T11" s="116">
         <v>80</v>
       </c>
-      <c r="U11" s="134"/>
-      <c r="V11" s="134"/>
-      <c r="W11" s="134"/>
-      <c r="X11" s="134"/>
-      <c r="Y11" s="134"/>
-      <c r="Z11" s="134"/>
-      <c r="AA11" s="134"/>
-      <c r="AB11" s="125"/>
-      <c r="AC11" s="128"/>
-      <c r="AD11" s="128"/>
-      <c r="AE11" s="128"/>
-      <c r="AF11" s="128"/>
-      <c r="AG11" s="128"/>
-      <c r="AH11" s="128"/>
-      <c r="AI11" s="126"/>
+      <c r="U11" s="116"/>
+      <c r="V11" s="116"/>
+      <c r="W11" s="116"/>
+      <c r="X11" s="116"/>
+      <c r="Y11" s="116"/>
+      <c r="Z11" s="116"/>
+      <c r="AA11" s="116"/>
+      <c r="AB11" s="119"/>
+      <c r="AC11" s="120"/>
+      <c r="AD11" s="120"/>
+      <c r="AE11" s="120"/>
+      <c r="AF11" s="120"/>
+      <c r="AG11" s="120"/>
+      <c r="AH11" s="120"/>
+      <c r="AI11" s="121"/>
     </row>
     <row r="12" spans="2:35" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C12" s="24"/>
@@ -19060,36 +19178,36 @@
       <c r="B14" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="133" t="s">
+      <c r="D14" s="118" t="s">
         <v>428</v>
       </c>
-      <c r="E14" s="133"/>
-      <c r="F14" s="133"/>
-      <c r="G14" s="133"/>
-      <c r="H14" s="133"/>
-      <c r="I14" s="133"/>
-      <c r="J14" s="133"/>
-      <c r="K14" s="133"/>
-      <c r="L14" s="133" t="s">
+      <c r="E14" s="118"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="118"/>
+      <c r="J14" s="118"/>
+      <c r="K14" s="118"/>
+      <c r="L14" s="118" t="s">
         <v>429</v>
       </c>
-      <c r="M14" s="133"/>
-      <c r="N14" s="133"/>
-      <c r="O14" s="133"/>
-      <c r="P14" s="133"/>
-      <c r="Q14" s="133"/>
-      <c r="R14" s="133"/>
-      <c r="S14" s="133"/>
-      <c r="T14" s="133" t="s">
+      <c r="M14" s="118"/>
+      <c r="N14" s="118"/>
+      <c r="O14" s="118"/>
+      <c r="P14" s="118"/>
+      <c r="Q14" s="118"/>
+      <c r="R14" s="118"/>
+      <c r="S14" s="118"/>
+      <c r="T14" s="118" t="s">
         <v>430</v>
       </c>
-      <c r="U14" s="133"/>
-      <c r="V14" s="133"/>
-      <c r="W14" s="133"/>
-      <c r="X14" s="133"/>
-      <c r="Y14" s="133"/>
-      <c r="Z14" s="133"/>
-      <c r="AA14" s="133"/>
+      <c r="U14" s="118"/>
+      <c r="V14" s="118"/>
+      <c r="W14" s="118"/>
+      <c r="X14" s="118"/>
+      <c r="Y14" s="118"/>
+      <c r="Z14" s="118"/>
+      <c r="AA14" s="118"/>
       <c r="AB14" s="5" t="s">
         <v>230</v>
       </c>
@@ -19122,36 +19240,36 @@
       <c r="C15" s="15" t="s">
         <v>426</v>
       </c>
-      <c r="D15" s="134">
+      <c r="D15" s="116">
         <v>128</v>
       </c>
-      <c r="E15" s="134"/>
-      <c r="F15" s="134"/>
-      <c r="G15" s="134"/>
-      <c r="H15" s="134"/>
-      <c r="I15" s="134"/>
-      <c r="J15" s="134"/>
-      <c r="K15" s="134"/>
-      <c r="L15" s="134">
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="116"/>
+      <c r="H15" s="116"/>
+      <c r="I15" s="116"/>
+      <c r="J15" s="116"/>
+      <c r="K15" s="116"/>
+      <c r="L15" s="116">
         <v>128</v>
       </c>
-      <c r="M15" s="134"/>
-      <c r="N15" s="134"/>
-      <c r="O15" s="134"/>
-      <c r="P15" s="134"/>
-      <c r="Q15" s="134"/>
-      <c r="R15" s="134"/>
-      <c r="S15" s="134"/>
-      <c r="T15" s="134">
+      <c r="M15" s="116"/>
+      <c r="N15" s="116"/>
+      <c r="O15" s="116"/>
+      <c r="P15" s="116"/>
+      <c r="Q15" s="116"/>
+      <c r="R15" s="116"/>
+      <c r="S15" s="116"/>
+      <c r="T15" s="116">
         <v>128</v>
       </c>
-      <c r="U15" s="134"/>
-      <c r="V15" s="134"/>
-      <c r="W15" s="134"/>
-      <c r="X15" s="134"/>
-      <c r="Y15" s="134"/>
-      <c r="Z15" s="134"/>
-      <c r="AA15" s="134"/>
+      <c r="U15" s="116"/>
+      <c r="V15" s="116"/>
+      <c r="W15" s="116"/>
+      <c r="X15" s="116"/>
+      <c r="Y15" s="116"/>
+      <c r="Z15" s="116"/>
+      <c r="AA15" s="116"/>
       <c r="AB15" s="5">
         <v>0</v>
       </c>
@@ -19181,73 +19299,73 @@
       <c r="C16" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="D16" s="134">
+      <c r="D16" s="116">
         <v>80</v>
       </c>
-      <c r="E16" s="134"/>
-      <c r="F16" s="134"/>
-      <c r="G16" s="134"/>
-      <c r="H16" s="134"/>
-      <c r="I16" s="134"/>
-      <c r="J16" s="134"/>
-      <c r="K16" s="134"/>
-      <c r="L16" s="134">
-        <v>0</v>
-      </c>
-      <c r="M16" s="134"/>
-      <c r="N16" s="134"/>
-      <c r="O16" s="134"/>
-      <c r="P16" s="134"/>
-      <c r="Q16" s="134"/>
-      <c r="R16" s="134"/>
-      <c r="S16" s="134"/>
-      <c r="T16" s="134">
+      <c r="E16" s="116"/>
+      <c r="F16" s="116"/>
+      <c r="G16" s="116"/>
+      <c r="H16" s="116"/>
+      <c r="I16" s="116"/>
+      <c r="J16" s="116"/>
+      <c r="K16" s="116"/>
+      <c r="L16" s="116">
+        <v>0</v>
+      </c>
+      <c r="M16" s="116"/>
+      <c r="N16" s="116"/>
+      <c r="O16" s="116"/>
+      <c r="P16" s="116"/>
+      <c r="Q16" s="116"/>
+      <c r="R16" s="116"/>
+      <c r="S16" s="116"/>
+      <c r="T16" s="116">
         <v>255</v>
       </c>
-      <c r="U16" s="134"/>
-      <c r="V16" s="134"/>
-      <c r="W16" s="134"/>
-      <c r="X16" s="134"/>
-      <c r="Y16" s="134"/>
-      <c r="Z16" s="134"/>
-      <c r="AA16" s="134"/>
-      <c r="AB16" s="125">
+      <c r="U16" s="116"/>
+      <c r="V16" s="116"/>
+      <c r="W16" s="116"/>
+      <c r="X16" s="116"/>
+      <c r="Y16" s="116"/>
+      <c r="Z16" s="116"/>
+      <c r="AA16" s="116"/>
+      <c r="AB16" s="119">
         <v>80</v>
       </c>
-      <c r="AC16" s="128"/>
-      <c r="AD16" s="128"/>
-      <c r="AE16" s="128"/>
-      <c r="AF16" s="128"/>
-      <c r="AG16" s="128"/>
-      <c r="AH16" s="128"/>
-      <c r="AI16" s="126"/>
+      <c r="AC16" s="120"/>
+      <c r="AD16" s="120"/>
+      <c r="AE16" s="120"/>
+      <c r="AF16" s="120"/>
+      <c r="AG16" s="120"/>
+      <c r="AH16" s="120"/>
+      <c r="AI16" s="121"/>
     </row>
     <row r="18" spans="1:53" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="133" t="s">
+      <c r="D18" s="118" t="s">
         <v>433</v>
       </c>
-      <c r="E18" s="133"/>
-      <c r="F18" s="133"/>
-      <c r="G18" s="133"/>
-      <c r="H18" s="133"/>
-      <c r="I18" s="133"/>
-      <c r="J18" s="133"/>
-      <c r="K18" s="133"/>
-      <c r="L18" s="133" t="s">
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="118"/>
+      <c r="I18" s="118"/>
+      <c r="J18" s="118"/>
+      <c r="K18" s="118"/>
+      <c r="L18" s="118" t="s">
         <v>434</v>
       </c>
-      <c r="M18" s="133"/>
-      <c r="N18" s="133"/>
-      <c r="O18" s="133"/>
-      <c r="P18" s="133"/>
-      <c r="Q18" s="133"/>
-      <c r="R18" s="133"/>
-      <c r="S18" s="133"/>
-      <c r="T18" s="133"/>
-      <c r="U18" s="133"/>
+      <c r="M18" s="118"/>
+      <c r="N18" s="118"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="118"/>
+      <c r="Q18" s="118"/>
+      <c r="R18" s="118"/>
+      <c r="S18" s="118"/>
+      <c r="T18" s="118"/>
+      <c r="U18" s="118"/>
       <c r="V18" s="5" t="s">
         <v>230</v>
       </c>
@@ -19295,28 +19413,28 @@
       <c r="C19" s="15" t="s">
         <v>426</v>
       </c>
-      <c r="D19" s="134">
+      <c r="D19" s="116">
         <v>128</v>
       </c>
-      <c r="E19" s="134"/>
-      <c r="F19" s="134"/>
-      <c r="G19" s="134"/>
-      <c r="H19" s="134"/>
-      <c r="I19" s="134"/>
-      <c r="J19" s="134"/>
-      <c r="K19" s="134"/>
-      <c r="L19" s="134">
+      <c r="E19" s="116"/>
+      <c r="F19" s="116"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="116"/>
+      <c r="I19" s="116"/>
+      <c r="J19" s="116"/>
+      <c r="K19" s="116"/>
+      <c r="L19" s="116">
         <v>999</v>
       </c>
-      <c r="M19" s="134"/>
-      <c r="N19" s="134"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="134"/>
-      <c r="Q19" s="134"/>
-      <c r="R19" s="134"/>
-      <c r="S19" s="134"/>
-      <c r="T19" s="134"/>
-      <c r="U19" s="134"/>
+      <c r="M19" s="116"/>
+      <c r="N19" s="116"/>
+      <c r="O19" s="116"/>
+      <c r="P19" s="116"/>
+      <c r="Q19" s="116"/>
+      <c r="R19" s="116"/>
+      <c r="S19" s="116"/>
+      <c r="T19" s="116"/>
+      <c r="U19" s="116"/>
       <c r="V19" s="5"/>
       <c r="W19" s="5"/>
       <c r="X19" s="5"/>
@@ -19349,14 +19467,14 @@
       </c>
     </row>
     <row r="20" spans="1:53" x14ac:dyDescent="0.3">
-      <c r="D20" s="125"/>
-      <c r="E20" s="128"/>
-      <c r="F20" s="128"/>
-      <c r="G20" s="128"/>
-      <c r="H20" s="128"/>
-      <c r="I20" s="128"/>
-      <c r="J20" s="128"/>
-      <c r="K20" s="126"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="120"/>
+      <c r="J20" s="120"/>
+      <c r="K20" s="121"/>
       <c r="L20" s="9">
         <v>1</v>
       </c>
@@ -19405,86 +19523,86 @@
       <c r="AA20" s="5">
         <v>0</v>
       </c>
-      <c r="AB20" s="125"/>
-      <c r="AC20" s="128"/>
-      <c r="AD20" s="128"/>
-      <c r="AE20" s="128"/>
-      <c r="AF20" s="128"/>
-      <c r="AG20" s="128"/>
-      <c r="AH20" s="128"/>
-      <c r="AI20" s="126"/>
+      <c r="AB20" s="119"/>
+      <c r="AC20" s="120"/>
+      <c r="AD20" s="120"/>
+      <c r="AE20" s="120"/>
+      <c r="AF20" s="120"/>
+      <c r="AG20" s="120"/>
+      <c r="AH20" s="120"/>
+      <c r="AI20" s="121"/>
     </row>
     <row r="21" spans="1:53" x14ac:dyDescent="0.3">
       <c r="C21" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="D21" s="134">
+      <c r="D21" s="116">
         <v>80</v>
       </c>
-      <c r="E21" s="134"/>
-      <c r="F21" s="134"/>
-      <c r="G21" s="134"/>
-      <c r="H21" s="134"/>
-      <c r="I21" s="134"/>
-      <c r="J21" s="134"/>
-      <c r="K21" s="134"/>
-      <c r="L21" s="134" t="s">
+      <c r="E21" s="116"/>
+      <c r="F21" s="116"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="116"/>
+      <c r="I21" s="116"/>
+      <c r="J21" s="116"/>
+      <c r="K21" s="116"/>
+      <c r="L21" s="116" t="s">
         <v>435</v>
       </c>
-      <c r="M21" s="134"/>
-      <c r="N21" s="134"/>
-      <c r="O21" s="134"/>
-      <c r="P21" s="134"/>
-      <c r="Q21" s="134"/>
-      <c r="R21" s="134"/>
-      <c r="S21" s="134"/>
-      <c r="T21" s="134" t="s">
+      <c r="M21" s="116"/>
+      <c r="N21" s="116"/>
+      <c r="O21" s="116"/>
+      <c r="P21" s="116"/>
+      <c r="Q21" s="116"/>
+      <c r="R21" s="116"/>
+      <c r="S21" s="116"/>
+      <c r="T21" s="116" t="s">
         <v>436</v>
       </c>
-      <c r="U21" s="134"/>
-      <c r="V21" s="134"/>
-      <c r="W21" s="134"/>
-      <c r="X21" s="134"/>
-      <c r="Y21" s="134"/>
-      <c r="Z21" s="134"/>
-      <c r="AA21" s="134"/>
-      <c r="AB21" s="125">
+      <c r="U21" s="116"/>
+      <c r="V21" s="116"/>
+      <c r="W21" s="116"/>
+      <c r="X21" s="116"/>
+      <c r="Y21" s="116"/>
+      <c r="Z21" s="116"/>
+      <c r="AA21" s="116"/>
+      <c r="AB21" s="119">
         <v>8</v>
       </c>
-      <c r="AC21" s="128"/>
-      <c r="AD21" s="128"/>
-      <c r="AE21" s="128"/>
-      <c r="AF21" s="128"/>
-      <c r="AG21" s="128"/>
-      <c r="AH21" s="128"/>
-      <c r="AI21" s="126"/>
+      <c r="AC21" s="120"/>
+      <c r="AD21" s="120"/>
+      <c r="AE21" s="120"/>
+      <c r="AF21" s="120"/>
+      <c r="AG21" s="120"/>
+      <c r="AH21" s="120"/>
+      <c r="AI21" s="121"/>
     </row>
     <row r="22" spans="1:53" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C22" s="24"/>
     </row>
     <row r="24" spans="1:53" x14ac:dyDescent="0.3">
-      <c r="D24" s="133" t="s">
+      <c r="D24" s="118" t="s">
         <v>433</v>
       </c>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="133"/>
-      <c r="I24" s="133"/>
-      <c r="J24" s="133"/>
-      <c r="K24" s="133"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="118"/>
+      <c r="H24" s="118"/>
+      <c r="I24" s="118"/>
+      <c r="J24" s="118"/>
+      <c r="K24" s="118"/>
       <c r="L24" s="122" t="s">
         <v>434</v>
       </c>
-      <c r="M24" s="124"/>
-      <c r="N24" s="124"/>
-      <c r="O24" s="124"/>
-      <c r="P24" s="124"/>
-      <c r="Q24" s="124"/>
-      <c r="R24" s="124"/>
-      <c r="S24" s="124"/>
-      <c r="T24" s="124"/>
-      <c r="U24" s="124"/>
+      <c r="M24" s="123"/>
+      <c r="N24" s="123"/>
+      <c r="O24" s="123"/>
+      <c r="P24" s="123"/>
+      <c r="Q24" s="123"/>
+      <c r="R24" s="123"/>
+      <c r="S24" s="123"/>
+      <c r="T24" s="123"/>
+      <c r="U24" s="123"/>
       <c r="V24" s="5"/>
       <c r="W24" s="5"/>
       <c r="X24" s="5"/>
@@ -19511,16 +19629,16 @@
       <c r="C25" s="15" t="s">
         <v>426</v>
       </c>
-      <c r="D25" s="134">
+      <c r="D25" s="116">
         <v>128</v>
       </c>
-      <c r="E25" s="134"/>
-      <c r="F25" s="134"/>
-      <c r="G25" s="134"/>
-      <c r="H25" s="134"/>
-      <c r="I25" s="134"/>
-      <c r="J25" s="134"/>
-      <c r="K25" s="134"/>
+      <c r="E25" s="116"/>
+      <c r="F25" s="116"/>
+      <c r="G25" s="116"/>
+      <c r="H25" s="116"/>
+      <c r="I25" s="116"/>
+      <c r="J25" s="116"/>
+      <c r="K25" s="116"/>
       <c r="L25" s="16">
         <v>0</v>
       </c>
@@ -19598,46 +19716,46 @@
       <c r="C26" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="D26" s="134" t="s">
+      <c r="D26" s="116" t="s">
         <v>226</v>
       </c>
-      <c r="E26" s="134"/>
-      <c r="F26" s="134"/>
-      <c r="G26" s="134"/>
-      <c r="H26" s="134"/>
-      <c r="I26" s="134"/>
-      <c r="J26" s="134"/>
-      <c r="K26" s="134"/>
-      <c r="L26" s="125">
+      <c r="E26" s="116"/>
+      <c r="F26" s="116"/>
+      <c r="G26" s="116"/>
+      <c r="H26" s="116"/>
+      <c r="I26" s="116"/>
+      <c r="J26" s="116"/>
+      <c r="K26" s="116"/>
+      <c r="L26" s="119">
         <v>20</v>
       </c>
-      <c r="M26" s="128"/>
-      <c r="N26" s="128"/>
-      <c r="O26" s="128"/>
-      <c r="P26" s="128"/>
-      <c r="Q26" s="128"/>
-      <c r="R26" s="128"/>
-      <c r="S26" s="126"/>
-      <c r="T26" s="125">
+      <c r="M26" s="120"/>
+      <c r="N26" s="120"/>
+      <c r="O26" s="120"/>
+      <c r="P26" s="120"/>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="120"/>
+      <c r="S26" s="121"/>
+      <c r="T26" s="119">
         <v>40</v>
       </c>
-      <c r="U26" s="128"/>
-      <c r="V26" s="128"/>
-      <c r="W26" s="128"/>
-      <c r="X26" s="128"/>
-      <c r="Y26" s="128"/>
-      <c r="Z26" s="128"/>
-      <c r="AA26" s="126"/>
-      <c r="AB26" s="125">
+      <c r="U26" s="120"/>
+      <c r="V26" s="120"/>
+      <c r="W26" s="120"/>
+      <c r="X26" s="120"/>
+      <c r="Y26" s="120"/>
+      <c r="Z26" s="120"/>
+      <c r="AA26" s="121"/>
+      <c r="AB26" s="119">
         <v>88</v>
       </c>
-      <c r="AC26" s="128"/>
-      <c r="AD26" s="128"/>
-      <c r="AE26" s="128"/>
-      <c r="AF26" s="128"/>
-      <c r="AG26" s="128"/>
-      <c r="AH26" s="128"/>
-      <c r="AI26" s="126"/>
+      <c r="AC26" s="120"/>
+      <c r="AD26" s="120"/>
+      <c r="AE26" s="120"/>
+      <c r="AF26" s="120"/>
+      <c r="AG26" s="120"/>
+      <c r="AH26" s="120"/>
+      <c r="AI26" s="121"/>
     </row>
     <row r="29" spans="1:53" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
@@ -19694,13 +19812,13 @@
       <c r="T29" s="122" t="s">
         <v>361</v>
       </c>
-      <c r="U29" s="124"/>
-      <c r="V29" s="124"/>
-      <c r="W29" s="124"/>
-      <c r="X29" s="124"/>
-      <c r="Y29" s="124"/>
-      <c r="Z29" s="124"/>
-      <c r="AA29" s="123"/>
+      <c r="U29" s="123"/>
+      <c r="V29" s="123"/>
+      <c r="W29" s="123"/>
+      <c r="X29" s="123"/>
+      <c r="Y29" s="123"/>
+      <c r="Z29" s="123"/>
+      <c r="AA29" s="124"/>
       <c r="AB29" s="5" t="s">
         <v>230</v>
       </c>
@@ -19746,16 +19864,16 @@
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
-      <c r="T30" s="125">
+      <c r="T30" s="119">
         <v>128</v>
       </c>
-      <c r="U30" s="128"/>
-      <c r="V30" s="128"/>
-      <c r="W30" s="128"/>
-      <c r="X30" s="128"/>
-      <c r="Y30" s="128"/>
-      <c r="Z30" s="128"/>
-      <c r="AA30" s="126"/>
+      <c r="U30" s="120"/>
+      <c r="V30" s="120"/>
+      <c r="W30" s="120"/>
+      <c r="X30" s="120"/>
+      <c r="Y30" s="120"/>
+      <c r="Z30" s="120"/>
+      <c r="AA30" s="121"/>
       <c r="AB30" s="5"/>
       <c r="AC30" s="5"/>
       <c r="AD30" s="5"/>
@@ -19785,16 +19903,16 @@
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
-      <c r="T31" s="125">
+      <c r="T31" s="119">
         <v>80</v>
       </c>
-      <c r="U31" s="128"/>
-      <c r="V31" s="128"/>
-      <c r="W31" s="128"/>
-      <c r="X31" s="128"/>
-      <c r="Y31" s="128"/>
-      <c r="Z31" s="128"/>
-      <c r="AA31" s="126"/>
+      <c r="U31" s="120"/>
+      <c r="V31" s="120"/>
+      <c r="W31" s="120"/>
+      <c r="X31" s="120"/>
+      <c r="Y31" s="120"/>
+      <c r="Z31" s="120"/>
+      <c r="AA31" s="121"/>
       <c r="AB31" s="5"/>
       <c r="AC31" s="5"/>
       <c r="AD31" s="5"/>
@@ -19852,13 +19970,13 @@
       <c r="D34" s="122" t="s">
         <v>364</v>
       </c>
-      <c r="E34" s="124"/>
-      <c r="F34" s="124"/>
-      <c r="G34" s="124"/>
-      <c r="H34" s="124"/>
-      <c r="I34" s="124"/>
-      <c r="J34" s="124"/>
-      <c r="K34" s="123"/>
+      <c r="E34" s="123"/>
+      <c r="F34" s="123"/>
+      <c r="G34" s="123"/>
+      <c r="H34" s="123"/>
+      <c r="I34" s="123"/>
+      <c r="J34" s="123"/>
+      <c r="K34" s="124"/>
       <c r="L34" s="5" t="s">
         <v>230</v>
       </c>
@@ -19880,15 +19998,15 @@
       <c r="R34" s="122" t="s">
         <v>361</v>
       </c>
-      <c r="S34" s="124"/>
-      <c r="T34" s="124"/>
-      <c r="U34" s="124"/>
-      <c r="V34" s="124"/>
-      <c r="W34" s="124"/>
-      <c r="X34" s="124"/>
-      <c r="Y34" s="124"/>
-      <c r="Z34" s="124"/>
-      <c r="AA34" s="123"/>
+      <c r="S34" s="123"/>
+      <c r="T34" s="123"/>
+      <c r="U34" s="123"/>
+      <c r="V34" s="123"/>
+      <c r="W34" s="123"/>
+      <c r="X34" s="123"/>
+      <c r="Y34" s="123"/>
+      <c r="Z34" s="123"/>
+      <c r="AA34" s="124"/>
       <c r="AB34" s="5" t="s">
         <v>230</v>
       </c>
@@ -19932,18 +20050,18 @@
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
-      <c r="R35" s="125">
+      <c r="R35" s="119">
         <v>1023</v>
       </c>
-      <c r="S35" s="128"/>
-      <c r="T35" s="128"/>
-      <c r="U35" s="128"/>
-      <c r="V35" s="128"/>
-      <c r="W35" s="128"/>
-      <c r="X35" s="128"/>
-      <c r="Y35" s="128"/>
-      <c r="Z35" s="128"/>
-      <c r="AA35" s="126"/>
+      <c r="S35" s="120"/>
+      <c r="T35" s="120"/>
+      <c r="U35" s="120"/>
+      <c r="V35" s="120"/>
+      <c r="W35" s="120"/>
+      <c r="X35" s="120"/>
+      <c r="Y35" s="120"/>
+      <c r="Z35" s="120"/>
+      <c r="AA35" s="121"/>
       <c r="AB35" s="5"/>
       <c r="AC35" s="5"/>
       <c r="AD35" s="5"/>
@@ -19977,16 +20095,16 @@
       <c r="S36" s="5">
         <v>1</v>
       </c>
-      <c r="T36" s="125" t="s">
+      <c r="T36" s="119" t="s">
         <v>439</v>
       </c>
-      <c r="U36" s="128"/>
-      <c r="V36" s="128"/>
-      <c r="W36" s="128"/>
-      <c r="X36" s="128"/>
-      <c r="Y36" s="128"/>
-      <c r="Z36" s="128"/>
-      <c r="AA36" s="126"/>
+      <c r="U36" s="120"/>
+      <c r="V36" s="120"/>
+      <c r="W36" s="120"/>
+      <c r="X36" s="120"/>
+      <c r="Y36" s="120"/>
+      <c r="Z36" s="120"/>
+      <c r="AA36" s="121"/>
       <c r="AB36" s="5"/>
       <c r="AC36" s="5"/>
       <c r="AD36" s="5"/>
@@ -20044,13 +20162,13 @@
       <c r="D39" s="122" t="s">
         <v>443</v>
       </c>
-      <c r="E39" s="124"/>
-      <c r="F39" s="124"/>
-      <c r="G39" s="124"/>
-      <c r="H39" s="124"/>
-      <c r="I39" s="124"/>
-      <c r="J39" s="124"/>
-      <c r="K39" s="123"/>
+      <c r="E39" s="123"/>
+      <c r="F39" s="123"/>
+      <c r="G39" s="123"/>
+      <c r="H39" s="123"/>
+      <c r="I39" s="123"/>
+      <c r="J39" s="123"/>
+      <c r="K39" s="124"/>
       <c r="L39" s="5" t="s">
         <v>230</v>
       </c>
@@ -20205,23 +20323,23 @@
       <c r="D43" s="122" t="s">
         <v>445</v>
       </c>
-      <c r="E43" s="124"/>
-      <c r="F43" s="124"/>
-      <c r="G43" s="124"/>
-      <c r="H43" s="124"/>
-      <c r="I43" s="124"/>
-      <c r="J43" s="124"/>
-      <c r="K43" s="123"/>
+      <c r="E43" s="123"/>
+      <c r="F43" s="123"/>
+      <c r="G43" s="123"/>
+      <c r="H43" s="123"/>
+      <c r="I43" s="123"/>
+      <c r="J43" s="123"/>
+      <c r="K43" s="124"/>
       <c r="L43" s="122" t="s">
         <v>446</v>
       </c>
-      <c r="M43" s="124"/>
-      <c r="N43" s="124"/>
-      <c r="O43" s="124"/>
-      <c r="P43" s="124"/>
-      <c r="Q43" s="124"/>
-      <c r="R43" s="124"/>
-      <c r="S43" s="123"/>
+      <c r="M43" s="123"/>
+      <c r="N43" s="123"/>
+      <c r="O43" s="123"/>
+      <c r="P43" s="123"/>
+      <c r="Q43" s="123"/>
+      <c r="R43" s="123"/>
+      <c r="S43" s="124"/>
       <c r="T43" s="5" t="s">
         <v>230</v>
       </c>
@@ -20352,13 +20470,13 @@
       <c r="D47" s="122" t="s">
         <v>443</v>
       </c>
-      <c r="E47" s="124"/>
-      <c r="F47" s="124"/>
-      <c r="G47" s="124"/>
-      <c r="H47" s="124"/>
-      <c r="I47" s="124"/>
-      <c r="J47" s="124"/>
-      <c r="K47" s="123"/>
+      <c r="E47" s="123"/>
+      <c r="F47" s="123"/>
+      <c r="G47" s="123"/>
+      <c r="H47" s="123"/>
+      <c r="I47" s="123"/>
+      <c r="J47" s="123"/>
+      <c r="K47" s="124"/>
       <c r="L47" s="5" t="s">
         <v>230</v>
       </c>
@@ -20513,23 +20631,23 @@
       <c r="D51" s="122" t="s">
         <v>445</v>
       </c>
-      <c r="E51" s="124"/>
-      <c r="F51" s="124"/>
-      <c r="G51" s="124"/>
-      <c r="H51" s="124"/>
-      <c r="I51" s="124"/>
-      <c r="J51" s="124"/>
-      <c r="K51" s="123"/>
+      <c r="E51" s="123"/>
+      <c r="F51" s="123"/>
+      <c r="G51" s="123"/>
+      <c r="H51" s="123"/>
+      <c r="I51" s="123"/>
+      <c r="J51" s="123"/>
+      <c r="K51" s="124"/>
       <c r="L51" s="122" t="s">
         <v>446</v>
       </c>
-      <c r="M51" s="124"/>
-      <c r="N51" s="124"/>
-      <c r="O51" s="124"/>
-      <c r="P51" s="124"/>
-      <c r="Q51" s="124"/>
-      <c r="R51" s="124"/>
-      <c r="S51" s="123"/>
+      <c r="M51" s="123"/>
+      <c r="N51" s="123"/>
+      <c r="O51" s="123"/>
+      <c r="P51" s="123"/>
+      <c r="Q51" s="123"/>
+      <c r="R51" s="123"/>
+      <c r="S51" s="124"/>
       <c r="T51" s="5" t="s">
         <v>230</v>
       </c>
@@ -20660,13 +20778,13 @@
       <c r="D55" s="122" t="s">
         <v>443</v>
       </c>
-      <c r="E55" s="124"/>
-      <c r="F55" s="124"/>
-      <c r="G55" s="124"/>
-      <c r="H55" s="124"/>
-      <c r="I55" s="124"/>
-      <c r="J55" s="124"/>
-      <c r="K55" s="123"/>
+      <c r="E55" s="123"/>
+      <c r="F55" s="123"/>
+      <c r="G55" s="123"/>
+      <c r="H55" s="123"/>
+      <c r="I55" s="123"/>
+      <c r="J55" s="123"/>
+      <c r="K55" s="124"/>
       <c r="L55" s="5" t="s">
         <v>230</v>
       </c>
@@ -20821,23 +20939,23 @@
       <c r="D59" s="122" t="s">
         <v>445</v>
       </c>
-      <c r="E59" s="124"/>
-      <c r="F59" s="124"/>
-      <c r="G59" s="124"/>
-      <c r="H59" s="124"/>
-      <c r="I59" s="124"/>
-      <c r="J59" s="124"/>
-      <c r="K59" s="123"/>
+      <c r="E59" s="123"/>
+      <c r="F59" s="123"/>
+      <c r="G59" s="123"/>
+      <c r="H59" s="123"/>
+      <c r="I59" s="123"/>
+      <c r="J59" s="123"/>
+      <c r="K59" s="124"/>
       <c r="L59" s="122" t="s">
         <v>446</v>
       </c>
-      <c r="M59" s="124"/>
-      <c r="N59" s="124"/>
-      <c r="O59" s="124"/>
-      <c r="P59" s="124"/>
-      <c r="Q59" s="124"/>
-      <c r="R59" s="124"/>
-      <c r="S59" s="123"/>
+      <c r="M59" s="123"/>
+      <c r="N59" s="123"/>
+      <c r="O59" s="123"/>
+      <c r="P59" s="123"/>
+      <c r="Q59" s="123"/>
+      <c r="R59" s="123"/>
+      <c r="S59" s="124"/>
       <c r="T59" s="5" t="s">
         <v>230</v>
       </c>
@@ -20968,13 +21086,13 @@
       <c r="D63" s="122" t="s">
         <v>443</v>
       </c>
-      <c r="E63" s="124"/>
-      <c r="F63" s="124"/>
-      <c r="G63" s="124"/>
-      <c r="H63" s="124"/>
-      <c r="I63" s="124"/>
-      <c r="J63" s="124"/>
-      <c r="K63" s="123"/>
+      <c r="E63" s="123"/>
+      <c r="F63" s="123"/>
+      <c r="G63" s="123"/>
+      <c r="H63" s="123"/>
+      <c r="I63" s="123"/>
+      <c r="J63" s="123"/>
+      <c r="K63" s="124"/>
       <c r="L63" s="5" t="s">
         <v>230</v>
       </c>
@@ -21129,13 +21247,13 @@
       <c r="D67" s="122" t="s">
         <v>443</v>
       </c>
-      <c r="E67" s="124"/>
-      <c r="F67" s="124"/>
-      <c r="G67" s="124"/>
-      <c r="H67" s="124"/>
-      <c r="I67" s="124"/>
-      <c r="J67" s="124"/>
-      <c r="K67" s="123"/>
+      <c r="E67" s="123"/>
+      <c r="F67" s="123"/>
+      <c r="G67" s="123"/>
+      <c r="H67" s="123"/>
+      <c r="I67" s="123"/>
+      <c r="J67" s="123"/>
+      <c r="K67" s="124"/>
       <c r="L67" s="5" t="s">
         <v>230</v>
       </c>
@@ -21290,13 +21408,13 @@
       <c r="D71" s="122" t="s">
         <v>443</v>
       </c>
-      <c r="E71" s="124"/>
-      <c r="F71" s="124"/>
-      <c r="G71" s="124"/>
-      <c r="H71" s="124"/>
-      <c r="I71" s="124"/>
-      <c r="J71" s="124"/>
-      <c r="K71" s="123"/>
+      <c r="E71" s="123"/>
+      <c r="F71" s="123"/>
+      <c r="G71" s="123"/>
+      <c r="H71" s="123"/>
+      <c r="I71" s="123"/>
+      <c r="J71" s="123"/>
+      <c r="K71" s="124"/>
       <c r="L71" s="5" t="s">
         <v>230</v>
       </c>
@@ -21363,7 +21481,7 @@
       <c r="AG71" s="122" t="s">
         <v>444</v>
       </c>
-      <c r="AH71" s="123"/>
+      <c r="AH71" s="124"/>
       <c r="AI71" s="22"/>
     </row>
     <row r="72" spans="1:54" x14ac:dyDescent="0.3">
@@ -21399,8 +21517,8 @@
       <c r="AD72" s="5"/>
       <c r="AE72" s="5"/>
       <c r="AF72" s="5"/>
-      <c r="AG72" s="125"/>
-      <c r="AH72" s="126"/>
+      <c r="AG72" s="119"/>
+      <c r="AH72" s="121"/>
       <c r="AI72" s="5"/>
     </row>
     <row r="73" spans="1:54" x14ac:dyDescent="0.3">
@@ -21436,8 +21554,8 @@
       <c r="AD73" s="5"/>
       <c r="AE73" s="5"/>
       <c r="AF73" s="5"/>
-      <c r="AG73" s="125"/>
-      <c r="AH73" s="126"/>
+      <c r="AG73" s="119"/>
+      <c r="AH73" s="121"/>
       <c r="AI73" s="5"/>
     </row>
     <row r="75" spans="1:54" x14ac:dyDescent="0.3">
@@ -21447,13 +21565,13 @@
       <c r="D75" s="122" t="s">
         <v>443</v>
       </c>
-      <c r="E75" s="124"/>
-      <c r="F75" s="124"/>
-      <c r="G75" s="124"/>
-      <c r="H75" s="124"/>
-      <c r="I75" s="124"/>
-      <c r="J75" s="124"/>
-      <c r="K75" s="123"/>
+      <c r="E75" s="123"/>
+      <c r="F75" s="123"/>
+      <c r="G75" s="123"/>
+      <c r="H75" s="123"/>
+      <c r="I75" s="123"/>
+      <c r="J75" s="123"/>
+      <c r="K75" s="124"/>
       <c r="L75" s="5" t="s">
         <v>230</v>
       </c>
@@ -21520,7 +21638,7 @@
       <c r="AG75" s="122" t="s">
         <v>444</v>
       </c>
-      <c r="AH75" s="123"/>
+      <c r="AH75" s="124"/>
       <c r="AI75" s="14" t="s">
         <v>447</v>
       </c>
@@ -21558,8 +21676,8 @@
       <c r="AD76" s="5"/>
       <c r="AE76" s="5"/>
       <c r="AF76" s="5"/>
-      <c r="AG76" s="125"/>
-      <c r="AH76" s="126"/>
+      <c r="AG76" s="119"/>
+      <c r="AH76" s="121"/>
       <c r="AI76" s="5"/>
     </row>
     <row r="77" spans="1:54" x14ac:dyDescent="0.3">
@@ -21595,8 +21713,8 @@
       <c r="AD77" s="5"/>
       <c r="AE77" s="5"/>
       <c r="AF77" s="5"/>
-      <c r="AG77" s="125"/>
-      <c r="AH77" s="126"/>
+      <c r="AG77" s="119"/>
+      <c r="AH77" s="121"/>
       <c r="AI77" s="5"/>
       <c r="AL77" t="s">
         <v>377</v>
@@ -21653,35 +21771,35 @@
       <c r="D80" s="122" t="s">
         <v>564</v>
       </c>
-      <c r="E80" s="124"/>
-      <c r="F80" s="124"/>
-      <c r="G80" s="124"/>
-      <c r="H80" s="124"/>
-      <c r="I80" s="124"/>
-      <c r="J80" s="124"/>
-      <c r="K80" s="123"/>
+      <c r="E80" s="123"/>
+      <c r="F80" s="123"/>
+      <c r="G80" s="123"/>
+      <c r="H80" s="123"/>
+      <c r="I80" s="123"/>
+      <c r="J80" s="123"/>
+      <c r="K80" s="124"/>
       <c r="L80" s="14" t="s">
         <v>565</v>
       </c>
       <c r="M80" s="122" t="s">
         <v>566</v>
       </c>
-      <c r="N80" s="124"/>
-      <c r="O80" s="124"/>
-      <c r="P80" s="124"/>
-      <c r="Q80" s="124"/>
-      <c r="R80" s="124"/>
-      <c r="S80" s="123"/>
+      <c r="N80" s="123"/>
+      <c r="O80" s="123"/>
+      <c r="P80" s="123"/>
+      <c r="Q80" s="123"/>
+      <c r="R80" s="123"/>
+      <c r="S80" s="124"/>
       <c r="T80" s="122" t="s">
         <v>423</v>
       </c>
-      <c r="U80" s="124"/>
-      <c r="V80" s="124"/>
-      <c r="W80" s="124"/>
-      <c r="X80" s="124"/>
-      <c r="Y80" s="124"/>
-      <c r="Z80" s="124"/>
-      <c r="AA80" s="123"/>
+      <c r="U80" s="123"/>
+      <c r="V80" s="123"/>
+      <c r="W80" s="123"/>
+      <c r="X80" s="123"/>
+      <c r="Y80" s="123"/>
+      <c r="Z80" s="123"/>
+      <c r="AA80" s="124"/>
       <c r="AB80" s="14" t="s">
         <v>567</v>
       </c>
@@ -21796,31 +21914,31 @@
       <c r="D84" s="122" t="s">
         <v>576</v>
       </c>
-      <c r="E84" s="124"/>
-      <c r="F84" s="124"/>
-      <c r="G84" s="124"/>
-      <c r="H84" s="124"/>
-      <c r="I84" s="124"/>
-      <c r="J84" s="124"/>
-      <c r="K84" s="123"/>
+      <c r="E84" s="123"/>
+      <c r="F84" s="123"/>
+      <c r="G84" s="123"/>
+      <c r="H84" s="123"/>
+      <c r="I84" s="123"/>
+      <c r="J84" s="123"/>
+      <c r="K84" s="124"/>
       <c r="L84" s="122" t="s">
         <v>577</v>
       </c>
-      <c r="M84" s="124"/>
-      <c r="N84" s="124"/>
-      <c r="O84" s="124"/>
-      <c r="P84" s="124"/>
-      <c r="Q84" s="124"/>
-      <c r="R84" s="124"/>
-      <c r="S84" s="123"/>
+      <c r="M84" s="123"/>
+      <c r="N84" s="123"/>
+      <c r="O84" s="123"/>
+      <c r="P84" s="123"/>
+      <c r="Q84" s="123"/>
+      <c r="R84" s="123"/>
+      <c r="S84" s="124"/>
       <c r="T84" s="14" t="s">
         <v>578</v>
       </c>
-      <c r="U84" s="120" t="s">
+      <c r="U84" s="130" t="s">
         <v>579</v>
       </c>
-      <c r="V84" s="127"/>
-      <c r="W84" s="127"/>
+      <c r="V84" s="132"/>
+      <c r="W84" s="132"/>
       <c r="X84" s="14" t="s">
         <v>580</v>
       </c>
@@ -21944,33 +22062,33 @@
       <c r="D88" s="122" t="s">
         <v>673</v>
       </c>
-      <c r="E88" s="124"/>
-      <c r="F88" s="124"/>
-      <c r="G88" s="124"/>
-      <c r="H88" s="124"/>
-      <c r="I88" s="124"/>
+      <c r="E88" s="123"/>
+      <c r="F88" s="123"/>
+      <c r="G88" s="123"/>
+      <c r="H88" s="123"/>
+      <c r="I88" s="123"/>
       <c r="J88" s="122" t="s">
         <v>674</v>
       </c>
-      <c r="K88" s="124"/>
-      <c r="L88" s="124"/>
-      <c r="M88" s="124"/>
-      <c r="N88" s="124"/>
-      <c r="O88" s="124"/>
-      <c r="P88" s="123"/>
-      <c r="Q88" s="129" t="s">
+      <c r="K88" s="123"/>
+      <c r="L88" s="123"/>
+      <c r="M88" s="123"/>
+      <c r="N88" s="123"/>
+      <c r="O88" s="123"/>
+      <c r="P88" s="124"/>
+      <c r="Q88" s="125" t="s">
         <v>669</v>
       </c>
-      <c r="R88" s="130"/>
-      <c r="S88" s="130"/>
-      <c r="T88" s="130"/>
-      <c r="U88" s="130"/>
-      <c r="V88" s="130"/>
-      <c r="W88" s="130"/>
-      <c r="X88" s="130"/>
-      <c r="Y88" s="130"/>
-      <c r="Z88" s="130"/>
-      <c r="AA88" s="131"/>
+      <c r="R88" s="126"/>
+      <c r="S88" s="126"/>
+      <c r="T88" s="126"/>
+      <c r="U88" s="126"/>
+      <c r="V88" s="126"/>
+      <c r="W88" s="126"/>
+      <c r="X88" s="126"/>
+      <c r="Y88" s="126"/>
+      <c r="Z88" s="126"/>
+      <c r="AA88" s="127"/>
       <c r="AB88" s="14" t="s">
         <v>670</v>
       </c>
@@ -21993,36 +22111,36 @@
       <c r="C89" s="15" t="s">
         <v>675</v>
       </c>
-      <c r="D89" s="125">
+      <c r="D89" s="119">
         <v>20</v>
       </c>
-      <c r="E89" s="128"/>
-      <c r="F89" s="128"/>
-      <c r="G89" s="128"/>
-      <c r="H89" s="128"/>
-      <c r="I89" s="126"/>
-      <c r="J89" s="125">
+      <c r="E89" s="120"/>
+      <c r="F89" s="120"/>
+      <c r="G89" s="120"/>
+      <c r="H89" s="120"/>
+      <c r="I89" s="121"/>
+      <c r="J89" s="119">
         <v>6</v>
       </c>
-      <c r="K89" s="128"/>
-      <c r="L89" s="128"/>
-      <c r="M89" s="128"/>
-      <c r="N89" s="128"/>
-      <c r="O89" s="128"/>
-      <c r="P89" s="126"/>
-      <c r="Q89" s="125">
+      <c r="K89" s="120"/>
+      <c r="L89" s="120"/>
+      <c r="M89" s="120"/>
+      <c r="N89" s="120"/>
+      <c r="O89" s="120"/>
+      <c r="P89" s="121"/>
+      <c r="Q89" s="119">
         <v>49</v>
       </c>
-      <c r="R89" s="128"/>
-      <c r="S89" s="128"/>
-      <c r="T89" s="128"/>
-      <c r="U89" s="128"/>
-      <c r="V89" s="128"/>
-      <c r="W89" s="128"/>
-      <c r="X89" s="128"/>
-      <c r="Y89" s="128"/>
-      <c r="Z89" s="128"/>
-      <c r="AA89" s="126"/>
+      <c r="R89" s="120"/>
+      <c r="S89" s="120"/>
+      <c r="T89" s="120"/>
+      <c r="U89" s="120"/>
+      <c r="V89" s="120"/>
+      <c r="W89" s="120"/>
+      <c r="X89" s="120"/>
+      <c r="Y89" s="120"/>
+      <c r="Z89" s="120"/>
+      <c r="AA89" s="121"/>
       <c r="AB89" s="5">
         <v>1</v>
       </c>
@@ -22156,46 +22274,46 @@
       <c r="C91" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="D91" s="125">
+      <c r="D91" s="119">
         <v>80</v>
       </c>
-      <c r="E91" s="128"/>
-      <c r="F91" s="128"/>
-      <c r="G91" s="128"/>
-      <c r="H91" s="128"/>
-      <c r="I91" s="128"/>
-      <c r="J91" s="128"/>
-      <c r="K91" s="126"/>
-      <c r="L91" s="125">
+      <c r="E91" s="120"/>
+      <c r="F91" s="120"/>
+      <c r="G91" s="120"/>
+      <c r="H91" s="120"/>
+      <c r="I91" s="120"/>
+      <c r="J91" s="120"/>
+      <c r="K91" s="121"/>
+      <c r="L91" s="119">
         <v>30</v>
       </c>
-      <c r="M91" s="128"/>
-      <c r="N91" s="128"/>
-      <c r="O91" s="128"/>
-      <c r="P91" s="128"/>
-      <c r="Q91" s="128"/>
-      <c r="R91" s="128"/>
-      <c r="S91" s="126"/>
-      <c r="T91" s="125">
+      <c r="M91" s="120"/>
+      <c r="N91" s="120"/>
+      <c r="O91" s="120"/>
+      <c r="P91" s="120"/>
+      <c r="Q91" s="120"/>
+      <c r="R91" s="120"/>
+      <c r="S91" s="121"/>
+      <c r="T91" s="119">
         <v>49</v>
       </c>
-      <c r="U91" s="128"/>
-      <c r="V91" s="128"/>
-      <c r="W91" s="128"/>
-      <c r="X91" s="128"/>
-      <c r="Y91" s="128"/>
-      <c r="Z91" s="128"/>
-      <c r="AA91" s="126"/>
-      <c r="AB91" s="125">
+      <c r="U91" s="120"/>
+      <c r="V91" s="120"/>
+      <c r="W91" s="120"/>
+      <c r="X91" s="120"/>
+      <c r="Y91" s="120"/>
+      <c r="Z91" s="120"/>
+      <c r="AA91" s="121"/>
+      <c r="AB91" s="119">
         <v>80</v>
       </c>
-      <c r="AC91" s="128"/>
-      <c r="AD91" s="128"/>
-      <c r="AE91" s="128"/>
-      <c r="AF91" s="128"/>
-      <c r="AG91" s="128"/>
-      <c r="AH91" s="128"/>
-      <c r="AI91" s="126"/>
+      <c r="AC91" s="120"/>
+      <c r="AD91" s="120"/>
+      <c r="AE91" s="120"/>
+      <c r="AF91" s="120"/>
+      <c r="AG91" s="120"/>
+      <c r="AH91" s="120"/>
+      <c r="AI91" s="121"/>
     </row>
     <row r="93" spans="2:56" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
@@ -22204,23 +22322,23 @@
       <c r="D93" s="122" t="s">
         <v>882</v>
       </c>
-      <c r="E93" s="124"/>
-      <c r="F93" s="124"/>
-      <c r="G93" s="124"/>
-      <c r="H93" s="124"/>
-      <c r="I93" s="124"/>
-      <c r="J93" s="124"/>
-      <c r="K93" s="123"/>
+      <c r="E93" s="123"/>
+      <c r="F93" s="123"/>
+      <c r="G93" s="123"/>
+      <c r="H93" s="123"/>
+      <c r="I93" s="123"/>
+      <c r="J93" s="123"/>
+      <c r="K93" s="124"/>
       <c r="L93" s="122" t="s">
         <v>881</v>
       </c>
-      <c r="M93" s="124"/>
-      <c r="N93" s="124"/>
-      <c r="O93" s="124"/>
-      <c r="P93" s="124"/>
-      <c r="Q93" s="124"/>
-      <c r="R93" s="124"/>
-      <c r="S93" s="123"/>
+      <c r="M93" s="123"/>
+      <c r="N93" s="123"/>
+      <c r="O93" s="123"/>
+      <c r="P93" s="123"/>
+      <c r="Q93" s="123"/>
+      <c r="R93" s="123"/>
+      <c r="S93" s="124"/>
       <c r="T93" s="16"/>
       <c r="U93" s="41" t="s">
         <v>883</v>
@@ -22228,17 +22346,17 @@
       <c r="V93" s="122" t="s">
         <v>884</v>
       </c>
-      <c r="W93" s="124"/>
-      <c r="X93" s="124"/>
-      <c r="Y93" s="124"/>
-      <c r="Z93" s="124"/>
-      <c r="AA93" s="123"/>
+      <c r="W93" s="123"/>
+      <c r="X93" s="123"/>
+      <c r="Y93" s="123"/>
+      <c r="Z93" s="123"/>
+      <c r="AA93" s="124"/>
       <c r="AB93" s="5"/>
       <c r="AC93" s="5"/>
-      <c r="AD93" s="120" t="s">
+      <c r="AD93" s="130" t="s">
         <v>885</v>
       </c>
-      <c r="AE93" s="121"/>
+      <c r="AE93" s="131"/>
       <c r="AF93" s="14" t="s">
         <v>432</v>
       </c>
@@ -22248,7 +22366,7 @@
       <c r="AH93" s="122" t="s">
         <v>887</v>
       </c>
-      <c r="AI93" s="123"/>
+      <c r="AI93" s="124"/>
     </row>
     <row r="94" spans="2:56" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
@@ -22257,22 +22375,22 @@
       <c r="C94" s="15" t="s">
         <v>426</v>
       </c>
-      <c r="D94" s="125"/>
-      <c r="E94" s="128"/>
-      <c r="F94" s="128"/>
-      <c r="G94" s="128"/>
-      <c r="H94" s="128"/>
-      <c r="I94" s="128"/>
-      <c r="J94" s="128"/>
-      <c r="K94" s="126"/>
-      <c r="L94" s="125"/>
-      <c r="M94" s="128"/>
-      <c r="N94" s="128"/>
-      <c r="O94" s="128"/>
-      <c r="P94" s="128"/>
-      <c r="Q94" s="128"/>
-      <c r="R94" s="128"/>
-      <c r="S94" s="126"/>
+      <c r="D94" s="119"/>
+      <c r="E94" s="120"/>
+      <c r="F94" s="120"/>
+      <c r="G94" s="120"/>
+      <c r="H94" s="120"/>
+      <c r="I94" s="120"/>
+      <c r="J94" s="120"/>
+      <c r="K94" s="121"/>
+      <c r="L94" s="119"/>
+      <c r="M94" s="120"/>
+      <c r="N94" s="120"/>
+      <c r="O94" s="120"/>
+      <c r="P94" s="120"/>
+      <c r="Q94" s="120"/>
+      <c r="R94" s="120"/>
+      <c r="S94" s="121"/>
       <c r="T94" s="5">
         <v>0</v>
       </c>
@@ -22350,33 +22468,33 @@
       <c r="D97" s="122" t="s">
         <v>673</v>
       </c>
-      <c r="E97" s="124"/>
-      <c r="F97" s="124"/>
-      <c r="G97" s="124"/>
-      <c r="H97" s="124"/>
-      <c r="I97" s="123"/>
+      <c r="E97" s="123"/>
+      <c r="F97" s="123"/>
+      <c r="G97" s="123"/>
+      <c r="H97" s="123"/>
+      <c r="I97" s="124"/>
       <c r="J97" s="122" t="s">
         <v>674</v>
       </c>
-      <c r="K97" s="124"/>
-      <c r="L97" s="124"/>
-      <c r="M97" s="124"/>
-      <c r="N97" s="124"/>
-      <c r="O97" s="124"/>
-      <c r="P97" s="123"/>
-      <c r="Q97" s="129" t="s">
+      <c r="K97" s="123"/>
+      <c r="L97" s="123"/>
+      <c r="M97" s="123"/>
+      <c r="N97" s="123"/>
+      <c r="O97" s="123"/>
+      <c r="P97" s="124"/>
+      <c r="Q97" s="125" t="s">
         <v>669</v>
       </c>
-      <c r="R97" s="130"/>
-      <c r="S97" s="130"/>
-      <c r="T97" s="130"/>
-      <c r="U97" s="130"/>
-      <c r="V97" s="130"/>
-      <c r="W97" s="130"/>
-      <c r="X97" s="130"/>
-      <c r="Y97" s="130"/>
-      <c r="Z97" s="130"/>
-      <c r="AA97" s="131"/>
+      <c r="R97" s="126"/>
+      <c r="S97" s="126"/>
+      <c r="T97" s="126"/>
+      <c r="U97" s="126"/>
+      <c r="V97" s="126"/>
+      <c r="W97" s="126"/>
+      <c r="X97" s="126"/>
+      <c r="Y97" s="126"/>
+      <c r="Z97" s="126"/>
+      <c r="AA97" s="127"/>
       <c r="AB97" s="14" t="s">
         <v>670</v>
       </c>
@@ -22399,36 +22517,36 @@
       <c r="C98" s="15" t="s">
         <v>675</v>
       </c>
-      <c r="D98" s="125">
+      <c r="D98" s="119">
         <v>20</v>
       </c>
-      <c r="E98" s="128"/>
-      <c r="F98" s="128"/>
-      <c r="G98" s="128"/>
-      <c r="H98" s="128"/>
-      <c r="I98" s="126"/>
-      <c r="J98" s="125">
+      <c r="E98" s="120"/>
+      <c r="F98" s="120"/>
+      <c r="G98" s="120"/>
+      <c r="H98" s="120"/>
+      <c r="I98" s="121"/>
+      <c r="J98" s="119">
         <v>4</v>
       </c>
-      <c r="K98" s="128"/>
-      <c r="L98" s="128"/>
-      <c r="M98" s="128"/>
-      <c r="N98" s="128"/>
-      <c r="O98" s="128"/>
-      <c r="P98" s="126"/>
-      <c r="Q98" s="125">
+      <c r="K98" s="120"/>
+      <c r="L98" s="120"/>
+      <c r="M98" s="120"/>
+      <c r="N98" s="120"/>
+      <c r="O98" s="120"/>
+      <c r="P98" s="121"/>
+      <c r="Q98" s="119">
         <v>49</v>
       </c>
-      <c r="R98" s="128"/>
-      <c r="S98" s="128"/>
-      <c r="T98" s="128"/>
-      <c r="U98" s="128"/>
-      <c r="V98" s="128"/>
-      <c r="W98" s="128"/>
-      <c r="X98" s="128"/>
-      <c r="Y98" s="128"/>
-      <c r="Z98" s="128"/>
-      <c r="AA98" s="126"/>
+      <c r="R98" s="120"/>
+      <c r="S98" s="120"/>
+      <c r="T98" s="120"/>
+      <c r="U98" s="120"/>
+      <c r="V98" s="120"/>
+      <c r="W98" s="120"/>
+      <c r="X98" s="120"/>
+      <c r="Y98" s="120"/>
+      <c r="Z98" s="120"/>
+      <c r="AA98" s="121"/>
       <c r="AB98" s="5">
         <v>1</v>
       </c>
@@ -22556,46 +22674,46 @@
       <c r="C100" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="D100" s="125">
+      <c r="D100" s="119">
         <v>80</v>
       </c>
-      <c r="E100" s="128"/>
-      <c r="F100" s="128"/>
-      <c r="G100" s="128"/>
-      <c r="H100" s="128"/>
-      <c r="I100" s="128"/>
-      <c r="J100" s="128"/>
-      <c r="K100" s="126"/>
-      <c r="L100" s="125">
+      <c r="E100" s="120"/>
+      <c r="F100" s="120"/>
+      <c r="G100" s="120"/>
+      <c r="H100" s="120"/>
+      <c r="I100" s="120"/>
+      <c r="J100" s="120"/>
+      <c r="K100" s="121"/>
+      <c r="L100" s="119">
         <v>20</v>
       </c>
-      <c r="M100" s="128"/>
-      <c r="N100" s="128"/>
-      <c r="O100" s="128"/>
-      <c r="P100" s="128"/>
-      <c r="Q100" s="128"/>
-      <c r="R100" s="128"/>
-      <c r="S100" s="126"/>
-      <c r="T100" s="125">
+      <c r="M100" s="120"/>
+      <c r="N100" s="120"/>
+      <c r="O100" s="120"/>
+      <c r="P100" s="120"/>
+      <c r="Q100" s="120"/>
+      <c r="R100" s="120"/>
+      <c r="S100" s="121"/>
+      <c r="T100" s="119">
         <v>49</v>
       </c>
-      <c r="U100" s="128"/>
-      <c r="V100" s="128"/>
-      <c r="W100" s="128"/>
-      <c r="X100" s="128"/>
-      <c r="Y100" s="128"/>
-      <c r="Z100" s="128"/>
-      <c r="AA100" s="126"/>
-      <c r="AB100" s="125">
+      <c r="U100" s="120"/>
+      <c r="V100" s="120"/>
+      <c r="W100" s="120"/>
+      <c r="X100" s="120"/>
+      <c r="Y100" s="120"/>
+      <c r="Z100" s="120"/>
+      <c r="AA100" s="121"/>
+      <c r="AB100" s="119">
         <v>80</v>
       </c>
-      <c r="AC100" s="128"/>
-      <c r="AD100" s="128"/>
-      <c r="AE100" s="128"/>
-      <c r="AF100" s="128"/>
-      <c r="AG100" s="128"/>
-      <c r="AH100" s="128"/>
-      <c r="AI100" s="126"/>
+      <c r="AC100" s="120"/>
+      <c r="AD100" s="120"/>
+      <c r="AE100" s="120"/>
+      <c r="AF100" s="120"/>
+      <c r="AG100" s="120"/>
+      <c r="AH100" s="120"/>
+      <c r="AI100" s="121"/>
     </row>
     <row r="102" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
@@ -22604,31 +22722,31 @@
       <c r="D102" s="122" t="s">
         <v>576</v>
       </c>
-      <c r="E102" s="124"/>
-      <c r="F102" s="124"/>
-      <c r="G102" s="124"/>
-      <c r="H102" s="124"/>
-      <c r="I102" s="124"/>
-      <c r="J102" s="124"/>
-      <c r="K102" s="123"/>
+      <c r="E102" s="123"/>
+      <c r="F102" s="123"/>
+      <c r="G102" s="123"/>
+      <c r="H102" s="123"/>
+      <c r="I102" s="123"/>
+      <c r="J102" s="123"/>
+      <c r="K102" s="124"/>
       <c r="L102" s="122" t="s">
         <v>577</v>
       </c>
-      <c r="M102" s="124"/>
-      <c r="N102" s="124"/>
-      <c r="O102" s="124"/>
-      <c r="P102" s="124"/>
-      <c r="Q102" s="124"/>
-      <c r="R102" s="124"/>
-      <c r="S102" s="123"/>
+      <c r="M102" s="123"/>
+      <c r="N102" s="123"/>
+      <c r="O102" s="123"/>
+      <c r="P102" s="123"/>
+      <c r="Q102" s="123"/>
+      <c r="R102" s="123"/>
+      <c r="S102" s="124"/>
       <c r="T102" s="14" t="s">
         <v>877</v>
       </c>
       <c r="U102" s="122" t="s">
         <v>878</v>
       </c>
-      <c r="V102" s="124"/>
-      <c r="W102" s="124"/>
+      <c r="V102" s="123"/>
+      <c r="W102" s="123"/>
       <c r="X102" s="14" t="s">
         <v>580</v>
       </c>
@@ -22659,22 +22777,22 @@
       <c r="C103" s="15" t="s">
         <v>426</v>
       </c>
-      <c r="D103" s="125"/>
-      <c r="E103" s="128"/>
-      <c r="F103" s="128"/>
-      <c r="G103" s="128"/>
-      <c r="H103" s="128"/>
-      <c r="I103" s="128"/>
-      <c r="J103" s="128"/>
-      <c r="K103" s="126"/>
-      <c r="L103" s="125"/>
-      <c r="M103" s="128"/>
-      <c r="N103" s="128"/>
-      <c r="O103" s="128"/>
-      <c r="P103" s="128"/>
-      <c r="Q103" s="128"/>
-      <c r="R103" s="128"/>
-      <c r="S103" s="126"/>
+      <c r="D103" s="119"/>
+      <c r="E103" s="120"/>
+      <c r="F103" s="120"/>
+      <c r="G103" s="120"/>
+      <c r="H103" s="120"/>
+      <c r="I103" s="120"/>
+      <c r="J103" s="120"/>
+      <c r="K103" s="121"/>
+      <c r="L103" s="119"/>
+      <c r="M103" s="120"/>
+      <c r="N103" s="120"/>
+      <c r="O103" s="120"/>
+      <c r="P103" s="120"/>
+      <c r="Q103" s="120"/>
+      <c r="R103" s="120"/>
+      <c r="S103" s="121"/>
       <c r="T103" s="5">
         <v>0</v>
       </c>
@@ -22749,36 +22867,36 @@
       <c r="B106" t="s">
         <v>117</v>
       </c>
-      <c r="D106" s="133" t="s">
+      <c r="D106" s="118" t="s">
         <v>673</v>
       </c>
-      <c r="E106" s="133"/>
-      <c r="F106" s="133"/>
-      <c r="G106" s="133"/>
-      <c r="H106" s="133"/>
-      <c r="I106" s="133"/>
-      <c r="J106" s="133" t="s">
+      <c r="E106" s="118"/>
+      <c r="F106" s="118"/>
+      <c r="G106" s="118"/>
+      <c r="H106" s="118"/>
+      <c r="I106" s="118"/>
+      <c r="J106" s="118" t="s">
         <v>674</v>
       </c>
-      <c r="K106" s="133"/>
-      <c r="L106" s="133"/>
-      <c r="M106" s="133"/>
-      <c r="N106" s="133"/>
-      <c r="O106" s="133"/>
-      <c r="P106" s="133"/>
-      <c r="Q106" s="135" t="s">
+      <c r="K106" s="118"/>
+      <c r="L106" s="118"/>
+      <c r="M106" s="118"/>
+      <c r="N106" s="118"/>
+      <c r="O106" s="118"/>
+      <c r="P106" s="118"/>
+      <c r="Q106" s="128" t="s">
         <v>669</v>
       </c>
-      <c r="R106" s="135"/>
-      <c r="S106" s="135"/>
-      <c r="T106" s="135"/>
-      <c r="U106" s="135"/>
-      <c r="V106" s="135"/>
-      <c r="W106" s="135"/>
-      <c r="X106" s="135"/>
-      <c r="Y106" s="135"/>
-      <c r="Z106" s="135"/>
-      <c r="AA106" s="135"/>
+      <c r="R106" s="128"/>
+      <c r="S106" s="128"/>
+      <c r="T106" s="128"/>
+      <c r="U106" s="128"/>
+      <c r="V106" s="128"/>
+      <c r="W106" s="128"/>
+      <c r="X106" s="128"/>
+      <c r="Y106" s="128"/>
+      <c r="Z106" s="128"/>
+      <c r="AA106" s="128"/>
       <c r="AB106" s="14" t="s">
         <v>670</v>
       </c>
@@ -22801,36 +22919,36 @@
       <c r="C107" s="15" t="s">
         <v>675</v>
       </c>
-      <c r="D107" s="125">
+      <c r="D107" s="119">
         <v>20</v>
       </c>
-      <c r="E107" s="128"/>
-      <c r="F107" s="128"/>
-      <c r="G107" s="128"/>
-      <c r="H107" s="128"/>
-      <c r="I107" s="126"/>
-      <c r="J107" s="125">
+      <c r="E107" s="120"/>
+      <c r="F107" s="120"/>
+      <c r="G107" s="120"/>
+      <c r="H107" s="120"/>
+      <c r="I107" s="121"/>
+      <c r="J107" s="119">
         <v>1</v>
       </c>
-      <c r="K107" s="128"/>
-      <c r="L107" s="128"/>
-      <c r="M107" s="128"/>
-      <c r="N107" s="128"/>
-      <c r="O107" s="128"/>
-      <c r="P107" s="126"/>
-      <c r="Q107" s="125">
+      <c r="K107" s="120"/>
+      <c r="L107" s="120"/>
+      <c r="M107" s="120"/>
+      <c r="N107" s="120"/>
+      <c r="O107" s="120"/>
+      <c r="P107" s="121"/>
+      <c r="Q107" s="119">
         <v>49</v>
       </c>
-      <c r="R107" s="128"/>
-      <c r="S107" s="128"/>
-      <c r="T107" s="128"/>
-      <c r="U107" s="128"/>
-      <c r="V107" s="128"/>
-      <c r="W107" s="128"/>
-      <c r="X107" s="128"/>
-      <c r="Y107" s="128"/>
-      <c r="Z107" s="128"/>
-      <c r="AA107" s="126"/>
+      <c r="R107" s="120"/>
+      <c r="S107" s="120"/>
+      <c r="T107" s="120"/>
+      <c r="U107" s="120"/>
+      <c r="V107" s="120"/>
+      <c r="W107" s="120"/>
+      <c r="X107" s="120"/>
+      <c r="Y107" s="120"/>
+      <c r="Z107" s="120"/>
+      <c r="AA107" s="121"/>
       <c r="AB107" s="5">
         <v>1</v>
       </c>
@@ -22958,175 +23076,175 @@
       <c r="C109" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="D109" s="125">
+      <c r="D109" s="119">
         <v>80</v>
       </c>
-      <c r="E109" s="128"/>
-      <c r="F109" s="128"/>
-      <c r="G109" s="128"/>
-      <c r="H109" s="128"/>
-      <c r="I109" s="128"/>
-      <c r="J109" s="128"/>
-      <c r="K109" s="126"/>
-      <c r="L109" s="125">
+      <c r="E109" s="120"/>
+      <c r="F109" s="120"/>
+      <c r="G109" s="120"/>
+      <c r="H109" s="120"/>
+      <c r="I109" s="120"/>
+      <c r="J109" s="120"/>
+      <c r="K109" s="121"/>
+      <c r="L109" s="119">
         <v>8</v>
       </c>
-      <c r="M109" s="128"/>
-      <c r="N109" s="128"/>
-      <c r="O109" s="128"/>
-      <c r="P109" s="128"/>
-      <c r="Q109" s="128"/>
-      <c r="R109" s="128"/>
-      <c r="S109" s="126"/>
-      <c r="T109" s="125">
+      <c r="M109" s="120"/>
+      <c r="N109" s="120"/>
+      <c r="O109" s="120"/>
+      <c r="P109" s="120"/>
+      <c r="Q109" s="120"/>
+      <c r="R109" s="120"/>
+      <c r="S109" s="121"/>
+      <c r="T109" s="119">
         <v>49</v>
       </c>
-      <c r="U109" s="128"/>
-      <c r="V109" s="128"/>
-      <c r="W109" s="128"/>
-      <c r="X109" s="128"/>
-      <c r="Y109" s="128"/>
-      <c r="Z109" s="128"/>
-      <c r="AA109" s="126"/>
-      <c r="AB109" s="125">
+      <c r="U109" s="120"/>
+      <c r="V109" s="120"/>
+      <c r="W109" s="120"/>
+      <c r="X109" s="120"/>
+      <c r="Y109" s="120"/>
+      <c r="Z109" s="120"/>
+      <c r="AA109" s="121"/>
+      <c r="AB109" s="119">
         <v>80</v>
       </c>
-      <c r="AC109" s="128"/>
-      <c r="AD109" s="128"/>
-      <c r="AE109" s="128"/>
-      <c r="AF109" s="128"/>
-      <c r="AG109" s="128"/>
-      <c r="AH109" s="128"/>
-      <c r="AI109" s="126"/>
+      <c r="AC109" s="120"/>
+      <c r="AD109" s="120"/>
+      <c r="AE109" s="120"/>
+      <c r="AF109" s="120"/>
+      <c r="AG109" s="120"/>
+      <c r="AH109" s="120"/>
+      <c r="AI109" s="121"/>
     </row>
     <row r="111" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B111" s="36" t="s">
         <v>524</v>
       </c>
-      <c r="D111" s="132" t="s">
+      <c r="D111" s="117" t="s">
         <v>649</v>
       </c>
-      <c r="E111" s="132"/>
-      <c r="F111" s="132"/>
-      <c r="G111" s="132"/>
-      <c r="H111" s="132"/>
-      <c r="I111" s="132"/>
-      <c r="J111" s="132"/>
-      <c r="K111" s="132"/>
-      <c r="L111" s="132" t="s">
+      <c r="E111" s="117"/>
+      <c r="F111" s="117"/>
+      <c r="G111" s="117"/>
+      <c r="H111" s="117"/>
+      <c r="I111" s="117"/>
+      <c r="J111" s="117"/>
+      <c r="K111" s="117"/>
+      <c r="L111" s="117" t="s">
         <v>650</v>
       </c>
-      <c r="M111" s="132"/>
-      <c r="N111" s="132"/>
-      <c r="O111" s="132"/>
-      <c r="P111" s="132"/>
-      <c r="Q111" s="132"/>
-      <c r="R111" s="132"/>
-      <c r="S111" s="132"/>
-      <c r="T111" s="132" t="s">
+      <c r="M111" s="117"/>
+      <c r="N111" s="117"/>
+      <c r="O111" s="117"/>
+      <c r="P111" s="117"/>
+      <c r="Q111" s="117"/>
+      <c r="R111" s="117"/>
+      <c r="S111" s="117"/>
+      <c r="T111" s="117" t="s">
         <v>420</v>
       </c>
-      <c r="U111" s="132"/>
-      <c r="V111" s="132"/>
-      <c r="W111" s="132"/>
-      <c r="X111" s="132"/>
-      <c r="Y111" s="132"/>
-      <c r="Z111" s="132"/>
-      <c r="AA111" s="132"/>
-      <c r="AB111" s="132" t="s">
+      <c r="U111" s="117"/>
+      <c r="V111" s="117"/>
+      <c r="W111" s="117"/>
+      <c r="X111" s="117"/>
+      <c r="Y111" s="117"/>
+      <c r="Z111" s="117"/>
+      <c r="AA111" s="117"/>
+      <c r="AB111" s="117" t="s">
         <v>419</v>
       </c>
-      <c r="AC111" s="132"/>
-      <c r="AD111" s="132"/>
-      <c r="AE111" s="132"/>
-      <c r="AF111" s="132"/>
-      <c r="AG111" s="132"/>
-      <c r="AH111" s="132"/>
-      <c r="AI111" s="132"/>
-      <c r="AJ111" s="132" t="s">
+      <c r="AC111" s="117"/>
+      <c r="AD111" s="117"/>
+      <c r="AE111" s="117"/>
+      <c r="AF111" s="117"/>
+      <c r="AG111" s="117"/>
+      <c r="AH111" s="117"/>
+      <c r="AI111" s="117"/>
+      <c r="AJ111" s="117" t="s">
         <v>418</v>
       </c>
-      <c r="AK111" s="132"/>
-      <c r="AL111" s="132"/>
-      <c r="AM111" s="132"/>
-      <c r="AN111" s="132"/>
-      <c r="AO111" s="132"/>
-      <c r="AP111" s="132"/>
-      <c r="AQ111" s="132"/>
-      <c r="AR111" s="132" t="s">
+      <c r="AK111" s="117"/>
+      <c r="AL111" s="117"/>
+      <c r="AM111" s="117"/>
+      <c r="AN111" s="117"/>
+      <c r="AO111" s="117"/>
+      <c r="AP111" s="117"/>
+      <c r="AQ111" s="117"/>
+      <c r="AR111" s="117" t="s">
         <v>417</v>
       </c>
-      <c r="AS111" s="132"/>
-      <c r="AT111" s="132"/>
-      <c r="AU111" s="132"/>
-      <c r="AV111" s="132"/>
-      <c r="AW111" s="132"/>
-      <c r="AX111" s="132"/>
-      <c r="AY111" s="132"/>
+      <c r="AS111" s="117"/>
+      <c r="AT111" s="117"/>
+      <c r="AU111" s="117"/>
+      <c r="AV111" s="117"/>
+      <c r="AW111" s="117"/>
+      <c r="AX111" s="117"/>
+      <c r="AY111" s="117"/>
     </row>
     <row r="112" spans="2:51" x14ac:dyDescent="0.3">
       <c r="D112" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="E112" s="133" t="s">
+      <c r="E112" s="118" t="s">
         <v>651</v>
       </c>
-      <c r="F112" s="133"/>
-      <c r="G112" s="133"/>
-      <c r="H112" s="133"/>
-      <c r="I112" s="133" t="s">
+      <c r="F112" s="118"/>
+      <c r="G112" s="118"/>
+      <c r="H112" s="118"/>
+      <c r="I112" s="118" t="s">
         <v>658</v>
       </c>
-      <c r="J112" s="133"/>
-      <c r="K112" s="133"/>
-      <c r="L112" s="133"/>
-      <c r="M112" s="133"/>
-      <c r="N112" s="133"/>
-      <c r="O112" s="133"/>
-      <c r="P112" s="133"/>
+      <c r="J112" s="118"/>
+      <c r="K112" s="118"/>
+      <c r="L112" s="118"/>
+      <c r="M112" s="118"/>
+      <c r="N112" s="118"/>
+      <c r="O112" s="118"/>
+      <c r="P112" s="118"/>
       <c r="Q112" s="122" t="s">
         <v>569</v>
       </c>
-      <c r="R112" s="123"/>
+      <c r="R112" s="124"/>
       <c r="S112" s="122" t="s">
         <v>657</v>
       </c>
-      <c r="T112" s="124"/>
-      <c r="U112" s="124"/>
-      <c r="V112" s="124"/>
-      <c r="W112" s="124"/>
-      <c r="X112" s="124"/>
-      <c r="Y112" s="124"/>
-      <c r="Z112" s="123"/>
+      <c r="T112" s="123"/>
+      <c r="U112" s="123"/>
+      <c r="V112" s="123"/>
+      <c r="W112" s="123"/>
+      <c r="X112" s="123"/>
+      <c r="Y112" s="123"/>
+      <c r="Z112" s="124"/>
       <c r="AA112" s="122" t="s">
         <v>655</v>
       </c>
-      <c r="AB112" s="124"/>
-      <c r="AC112" s="124"/>
-      <c r="AD112" s="124"/>
-      <c r="AE112" s="124"/>
-      <c r="AF112" s="124"/>
-      <c r="AG112" s="124"/>
-      <c r="AH112" s="123"/>
+      <c r="AB112" s="123"/>
+      <c r="AC112" s="123"/>
+      <c r="AD112" s="123"/>
+      <c r="AE112" s="123"/>
+      <c r="AF112" s="123"/>
+      <c r="AG112" s="123"/>
+      <c r="AH112" s="124"/>
       <c r="AI112" s="122" t="s">
         <v>656</v>
       </c>
-      <c r="AJ112" s="124"/>
-      <c r="AK112" s="124"/>
-      <c r="AL112" s="124"/>
-      <c r="AM112" s="124"/>
-      <c r="AN112" s="124"/>
-      <c r="AO112" s="124"/>
-      <c r="AP112" s="123"/>
+      <c r="AJ112" s="123"/>
+      <c r="AK112" s="123"/>
+      <c r="AL112" s="123"/>
+      <c r="AM112" s="123"/>
+      <c r="AN112" s="123"/>
+      <c r="AO112" s="123"/>
+      <c r="AP112" s="124"/>
       <c r="AQ112" s="122" t="s">
         <v>652</v>
       </c>
-      <c r="AR112" s="123"/>
+      <c r="AR112" s="124"/>
       <c r="AS112" s="122" t="s">
         <v>653</v>
       </c>
-      <c r="AT112" s="124"/>
-      <c r="AU112" s="123"/>
+      <c r="AT112" s="123"/>
+      <c r="AU112" s="124"/>
       <c r="AV112" s="5"/>
       <c r="AW112" s="5"/>
       <c r="AX112" s="5"/>
@@ -23279,253 +23397,253 @@
       </c>
     </row>
     <row r="114" spans="2:75" x14ac:dyDescent="0.3">
-      <c r="D114" s="125" t="s">
+      <c r="D114" s="119" t="s">
         <v>664</v>
       </c>
-      <c r="E114" s="128"/>
-      <c r="F114" s="128"/>
-      <c r="G114" s="128"/>
-      <c r="H114" s="128"/>
-      <c r="I114" s="128"/>
-      <c r="J114" s="128"/>
-      <c r="K114" s="126"/>
-      <c r="L114" s="125" t="s">
+      <c r="E114" s="120"/>
+      <c r="F114" s="120"/>
+      <c r="G114" s="120"/>
+      <c r="H114" s="120"/>
+      <c r="I114" s="120"/>
+      <c r="J114" s="120"/>
+      <c r="K114" s="121"/>
+      <c r="L114" s="119" t="s">
         <v>654</v>
       </c>
-      <c r="M114" s="128"/>
-      <c r="N114" s="128"/>
-      <c r="O114" s="128"/>
-      <c r="P114" s="128"/>
-      <c r="Q114" s="128"/>
-      <c r="R114" s="128"/>
-      <c r="S114" s="126"/>
-      <c r="T114" s="125">
+      <c r="M114" s="120"/>
+      <c r="N114" s="120"/>
+      <c r="O114" s="120"/>
+      <c r="P114" s="120"/>
+      <c r="Q114" s="120"/>
+      <c r="R114" s="120"/>
+      <c r="S114" s="121"/>
+      <c r="T114" s="119">
         <v>55</v>
       </c>
-      <c r="U114" s="128"/>
-      <c r="V114" s="128"/>
-      <c r="W114" s="128"/>
-      <c r="X114" s="128"/>
-      <c r="Y114" s="128"/>
-      <c r="Z114" s="128"/>
-      <c r="AA114" s="126"/>
-      <c r="AB114" s="125">
+      <c r="U114" s="120"/>
+      <c r="V114" s="120"/>
+      <c r="W114" s="120"/>
+      <c r="X114" s="120"/>
+      <c r="Y114" s="120"/>
+      <c r="Z114" s="120"/>
+      <c r="AA114" s="121"/>
+      <c r="AB114" s="119">
         <v>55</v>
       </c>
-      <c r="AC114" s="128"/>
-      <c r="AD114" s="128"/>
-      <c r="AE114" s="128"/>
-      <c r="AF114" s="128"/>
-      <c r="AG114" s="128"/>
-      <c r="AH114" s="128"/>
-      <c r="AI114" s="126"/>
-      <c r="AJ114" s="125">
+      <c r="AC114" s="120"/>
+      <c r="AD114" s="120"/>
+      <c r="AE114" s="120"/>
+      <c r="AF114" s="120"/>
+      <c r="AG114" s="120"/>
+      <c r="AH114" s="120"/>
+      <c r="AI114" s="121"/>
+      <c r="AJ114" s="119">
         <v>54</v>
       </c>
-      <c r="AK114" s="128"/>
-      <c r="AL114" s="128"/>
-      <c r="AM114" s="128"/>
-      <c r="AN114" s="128"/>
-      <c r="AO114" s="128"/>
-      <c r="AP114" s="128"/>
-      <c r="AQ114" s="126"/>
-      <c r="AR114" s="125" t="s">
+      <c r="AK114" s="120"/>
+      <c r="AL114" s="120"/>
+      <c r="AM114" s="120"/>
+      <c r="AN114" s="120"/>
+      <c r="AO114" s="120"/>
+      <c r="AP114" s="120"/>
+      <c r="AQ114" s="121"/>
+      <c r="AR114" s="119" t="s">
         <v>227</v>
       </c>
-      <c r="AS114" s="128"/>
-      <c r="AT114" s="128"/>
-      <c r="AU114" s="128"/>
-      <c r="AV114" s="128"/>
-      <c r="AW114" s="128"/>
-      <c r="AX114" s="128"/>
-      <c r="AY114" s="126"/>
+      <c r="AS114" s="120"/>
+      <c r="AT114" s="120"/>
+      <c r="AU114" s="120"/>
+      <c r="AV114" s="120"/>
+      <c r="AW114" s="120"/>
+      <c r="AX114" s="120"/>
+      <c r="AY114" s="121"/>
     </row>
     <row r="118" spans="2:75" x14ac:dyDescent="0.3">
       <c r="B118" s="36" t="s">
         <v>527</v>
       </c>
-      <c r="D118" s="132" t="s">
+      <c r="D118" s="117" t="s">
         <v>1006</v>
       </c>
-      <c r="E118" s="132"/>
-      <c r="F118" s="132"/>
-      <c r="G118" s="132"/>
-      <c r="H118" s="132"/>
-      <c r="I118" s="132"/>
-      <c r="J118" s="132"/>
-      <c r="K118" s="132"/>
-      <c r="L118" s="132" t="s">
+      <c r="E118" s="117"/>
+      <c r="F118" s="117"/>
+      <c r="G118" s="117"/>
+      <c r="H118" s="117"/>
+      <c r="I118" s="117"/>
+      <c r="J118" s="117"/>
+      <c r="K118" s="117"/>
+      <c r="L118" s="117" t="s">
         <v>1007</v>
       </c>
-      <c r="M118" s="132"/>
-      <c r="N118" s="132"/>
-      <c r="O118" s="132"/>
-      <c r="P118" s="132"/>
-      <c r="Q118" s="132"/>
-      <c r="R118" s="132"/>
-      <c r="S118" s="132"/>
-      <c r="T118" s="132" t="s">
+      <c r="M118" s="117"/>
+      <c r="N118" s="117"/>
+      <c r="O118" s="117"/>
+      <c r="P118" s="117"/>
+      <c r="Q118" s="117"/>
+      <c r="R118" s="117"/>
+      <c r="S118" s="117"/>
+      <c r="T118" s="117" t="s">
         <v>1008</v>
       </c>
-      <c r="U118" s="132"/>
-      <c r="V118" s="132"/>
-      <c r="W118" s="132"/>
-      <c r="X118" s="132"/>
-      <c r="Y118" s="132"/>
-      <c r="Z118" s="132"/>
-      <c r="AA118" s="132"/>
-      <c r="AB118" s="132" t="s">
+      <c r="U118" s="117"/>
+      <c r="V118" s="117"/>
+      <c r="W118" s="117"/>
+      <c r="X118" s="117"/>
+      <c r="Y118" s="117"/>
+      <c r="Z118" s="117"/>
+      <c r="AA118" s="117"/>
+      <c r="AB118" s="117" t="s">
         <v>649</v>
       </c>
-      <c r="AC118" s="132"/>
-      <c r="AD118" s="132"/>
-      <c r="AE118" s="132"/>
-      <c r="AF118" s="132"/>
-      <c r="AG118" s="132"/>
-      <c r="AH118" s="132"/>
-      <c r="AI118" s="132"/>
-      <c r="AJ118" s="132" t="s">
+      <c r="AC118" s="117"/>
+      <c r="AD118" s="117"/>
+      <c r="AE118" s="117"/>
+      <c r="AF118" s="117"/>
+      <c r="AG118" s="117"/>
+      <c r="AH118" s="117"/>
+      <c r="AI118" s="117"/>
+      <c r="AJ118" s="117" t="s">
         <v>650</v>
       </c>
-      <c r="AK118" s="132"/>
-      <c r="AL118" s="132"/>
-      <c r="AM118" s="132"/>
-      <c r="AN118" s="132"/>
-      <c r="AO118" s="132"/>
-      <c r="AP118" s="132"/>
-      <c r="AQ118" s="132"/>
-      <c r="AR118" s="132" t="s">
+      <c r="AK118" s="117"/>
+      <c r="AL118" s="117"/>
+      <c r="AM118" s="117"/>
+      <c r="AN118" s="117"/>
+      <c r="AO118" s="117"/>
+      <c r="AP118" s="117"/>
+      <c r="AQ118" s="117"/>
+      <c r="AR118" s="117" t="s">
         <v>420</v>
       </c>
-      <c r="AS118" s="132"/>
-      <c r="AT118" s="132"/>
-      <c r="AU118" s="132"/>
-      <c r="AV118" s="132"/>
-      <c r="AW118" s="132"/>
-      <c r="AX118" s="132"/>
-      <c r="AY118" s="132"/>
-      <c r="AZ118" s="132" t="s">
+      <c r="AS118" s="117"/>
+      <c r="AT118" s="117"/>
+      <c r="AU118" s="117"/>
+      <c r="AV118" s="117"/>
+      <c r="AW118" s="117"/>
+      <c r="AX118" s="117"/>
+      <c r="AY118" s="117"/>
+      <c r="AZ118" s="117" t="s">
         <v>419</v>
       </c>
-      <c r="BA118" s="132"/>
-      <c r="BB118" s="132"/>
-      <c r="BC118" s="132"/>
-      <c r="BD118" s="132"/>
-      <c r="BE118" s="132"/>
-      <c r="BF118" s="132"/>
-      <c r="BG118" s="132"/>
-      <c r="BH118" s="132" t="s">
+      <c r="BA118" s="117"/>
+      <c r="BB118" s="117"/>
+      <c r="BC118" s="117"/>
+      <c r="BD118" s="117"/>
+      <c r="BE118" s="117"/>
+      <c r="BF118" s="117"/>
+      <c r="BG118" s="117"/>
+      <c r="BH118" s="117" t="s">
         <v>418</v>
       </c>
-      <c r="BI118" s="132"/>
-      <c r="BJ118" s="132"/>
-      <c r="BK118" s="132"/>
-      <c r="BL118" s="132"/>
-      <c r="BM118" s="132"/>
-      <c r="BN118" s="132"/>
-      <c r="BO118" s="132"/>
-      <c r="BP118" s="132" t="s">
+      <c r="BI118" s="117"/>
+      <c r="BJ118" s="117"/>
+      <c r="BK118" s="117"/>
+      <c r="BL118" s="117"/>
+      <c r="BM118" s="117"/>
+      <c r="BN118" s="117"/>
+      <c r="BO118" s="117"/>
+      <c r="BP118" s="117" t="s">
         <v>417</v>
       </c>
-      <c r="BQ118" s="132"/>
-      <c r="BR118" s="132"/>
-      <c r="BS118" s="132"/>
-      <c r="BT118" s="132"/>
-      <c r="BU118" s="132"/>
-      <c r="BV118" s="132"/>
-      <c r="BW118" s="132"/>
+      <c r="BQ118" s="117"/>
+      <c r="BR118" s="117"/>
+      <c r="BS118" s="117"/>
+      <c r="BT118" s="117"/>
+      <c r="BU118" s="117"/>
+      <c r="BV118" s="117"/>
+      <c r="BW118" s="117"/>
     </row>
     <row r="119" spans="2:75" x14ac:dyDescent="0.3">
-      <c r="D119" s="133" t="s">
+      <c r="D119" s="118" t="s">
         <v>361</v>
       </c>
-      <c r="E119" s="133"/>
-      <c r="F119" s="133"/>
-      <c r="G119" s="133"/>
-      <c r="H119" s="133"/>
-      <c r="I119" s="133"/>
-      <c r="J119" s="133"/>
-      <c r="K119" s="133"/>
-      <c r="L119" s="133"/>
-      <c r="M119" s="133"/>
-      <c r="N119" s="133" t="s">
+      <c r="E119" s="118"/>
+      <c r="F119" s="118"/>
+      <c r="G119" s="118"/>
+      <c r="H119" s="118"/>
+      <c r="I119" s="118"/>
+      <c r="J119" s="118"/>
+      <c r="K119" s="118"/>
+      <c r="L119" s="118"/>
+      <c r="M119" s="118"/>
+      <c r="N119" s="118" t="s">
         <v>364</v>
       </c>
-      <c r="O119" s="133"/>
-      <c r="P119" s="133"/>
-      <c r="Q119" s="133"/>
-      <c r="R119" s="133"/>
-      <c r="S119" s="133"/>
-      <c r="T119" s="133"/>
-      <c r="U119" s="133"/>
-      <c r="V119" s="133" t="s">
+      <c r="O119" s="118"/>
+      <c r="P119" s="118"/>
+      <c r="Q119" s="118"/>
+      <c r="R119" s="118"/>
+      <c r="S119" s="118"/>
+      <c r="T119" s="118"/>
+      <c r="U119" s="118"/>
+      <c r="V119" s="118" t="s">
         <v>1009</v>
       </c>
-      <c r="W119" s="133"/>
-      <c r="X119" s="133"/>
-      <c r="Y119" s="133"/>
-      <c r="Z119" s="133"/>
-      <c r="AA119" s="133"/>
-      <c r="AB119" s="133"/>
-      <c r="AC119" s="133"/>
-      <c r="AD119" s="133"/>
-      <c r="AE119" s="133"/>
-      <c r="AF119" s="133"/>
-      <c r="AG119" s="133"/>
-      <c r="AH119" s="133"/>
-      <c r="AI119" s="133"/>
-      <c r="AJ119" s="133"/>
-      <c r="AK119" s="133"/>
-      <c r="AL119" s="133"/>
-      <c r="AM119" s="133" t="s">
+      <c r="W119" s="118"/>
+      <c r="X119" s="118"/>
+      <c r="Y119" s="118"/>
+      <c r="Z119" s="118"/>
+      <c r="AA119" s="118"/>
+      <c r="AB119" s="118"/>
+      <c r="AC119" s="118"/>
+      <c r="AD119" s="118"/>
+      <c r="AE119" s="118"/>
+      <c r="AF119" s="118"/>
+      <c r="AG119" s="118"/>
+      <c r="AH119" s="118"/>
+      <c r="AI119" s="118"/>
+      <c r="AJ119" s="118"/>
+      <c r="AK119" s="118"/>
+      <c r="AL119" s="118"/>
+      <c r="AM119" s="118" t="s">
         <v>1010</v>
       </c>
-      <c r="AN119" s="133"/>
-      <c r="AO119" s="133" t="s">
+      <c r="AN119" s="118"/>
+      <c r="AO119" s="118" t="s">
         <v>1011</v>
       </c>
-      <c r="AP119" s="133"/>
-      <c r="AQ119" s="133"/>
-      <c r="AR119" s="133"/>
-      <c r="AS119" s="133"/>
-      <c r="AT119" s="133"/>
-      <c r="AU119" s="133"/>
-      <c r="AV119" s="133"/>
-      <c r="AW119" s="133"/>
-      <c r="AX119" s="133"/>
-      <c r="AY119" s="133" t="s">
+      <c r="AP119" s="118"/>
+      <c r="AQ119" s="118"/>
+      <c r="AR119" s="118"/>
+      <c r="AS119" s="118"/>
+      <c r="AT119" s="118"/>
+      <c r="AU119" s="118"/>
+      <c r="AV119" s="118"/>
+      <c r="AW119" s="118"/>
+      <c r="AX119" s="118"/>
+      <c r="AY119" s="118" t="s">
         <v>1012</v>
       </c>
-      <c r="AZ119" s="133"/>
-      <c r="BA119" s="133"/>
-      <c r="BB119" s="133"/>
-      <c r="BC119" s="133"/>
-      <c r="BD119" s="133"/>
-      <c r="BE119" s="133"/>
-      <c r="BF119" s="133"/>
-      <c r="BG119" s="133"/>
-      <c r="BH119" s="133"/>
-      <c r="BI119" s="133" t="s">
+      <c r="AZ119" s="118"/>
+      <c r="BA119" s="118"/>
+      <c r="BB119" s="118"/>
+      <c r="BC119" s="118"/>
+      <c r="BD119" s="118"/>
+      <c r="BE119" s="118"/>
+      <c r="BF119" s="118"/>
+      <c r="BG119" s="118"/>
+      <c r="BH119" s="118"/>
+      <c r="BI119" s="118" t="s">
         <v>1013</v>
       </c>
-      <c r="BJ119" s="133"/>
-      <c r="BK119" s="133"/>
-      <c r="BL119" s="133"/>
-      <c r="BM119" s="133"/>
-      <c r="BN119" s="133"/>
-      <c r="BO119" s="133"/>
-      <c r="BP119" s="133"/>
-      <c r="BQ119" s="133"/>
-      <c r="BR119" s="133"/>
+      <c r="BJ119" s="118"/>
+      <c r="BK119" s="118"/>
+      <c r="BL119" s="118"/>
+      <c r="BM119" s="118"/>
+      <c r="BN119" s="118"/>
+      <c r="BO119" s="118"/>
+      <c r="BP119" s="118"/>
+      <c r="BQ119" s="118"/>
+      <c r="BR119" s="118"/>
       <c r="BS119" s="14" t="s">
         <v>1014</v>
       </c>
-      <c r="BT119" s="133" t="s">
+      <c r="BT119" s="118" t="s">
         <v>1015</v>
       </c>
-      <c r="BU119" s="133"/>
-      <c r="BV119" s="133"/>
-      <c r="BW119" s="133"/>
+      <c r="BU119" s="118"/>
+      <c r="BV119" s="118"/>
+      <c r="BW119" s="118"/>
     </row>
     <row r="120" spans="2:75" x14ac:dyDescent="0.3">
       <c r="D120" s="5">
@@ -23746,96 +23864,96 @@
       </c>
     </row>
     <row r="121" spans="2:75" x14ac:dyDescent="0.3">
-      <c r="D121" s="134">
+      <c r="D121" s="116">
         <v>96</v>
       </c>
-      <c r="E121" s="134"/>
-      <c r="F121" s="134"/>
-      <c r="G121" s="134"/>
-      <c r="H121" s="134"/>
-      <c r="I121" s="134"/>
-      <c r="J121" s="134"/>
-      <c r="K121" s="134"/>
-      <c r="L121" s="134" t="s">
+      <c r="E121" s="116"/>
+      <c r="F121" s="116"/>
+      <c r="G121" s="116"/>
+      <c r="H121" s="116"/>
+      <c r="I121" s="116"/>
+      <c r="J121" s="116"/>
+      <c r="K121" s="116"/>
+      <c r="L121" s="116" t="s">
         <v>1016</v>
       </c>
-      <c r="M121" s="134"/>
-      <c r="N121" s="134"/>
-      <c r="O121" s="134"/>
-      <c r="P121" s="134"/>
-      <c r="Q121" s="134"/>
-      <c r="R121" s="134"/>
-      <c r="S121" s="134"/>
-      <c r="T121" s="134">
+      <c r="M121" s="116"/>
+      <c r="N121" s="116"/>
+      <c r="O121" s="116"/>
+      <c r="P121" s="116"/>
+      <c r="Q121" s="116"/>
+      <c r="R121" s="116"/>
+      <c r="S121" s="116"/>
+      <c r="T121" s="116">
         <v>80</v>
       </c>
-      <c r="U121" s="134"/>
-      <c r="V121" s="134"/>
-      <c r="W121" s="134"/>
-      <c r="X121" s="134"/>
-      <c r="Y121" s="134"/>
-      <c r="Z121" s="134"/>
-      <c r="AA121" s="134"/>
-      <c r="AB121" s="134" t="s">
+      <c r="U121" s="116"/>
+      <c r="V121" s="116"/>
+      <c r="W121" s="116"/>
+      <c r="X121" s="116"/>
+      <c r="Y121" s="116"/>
+      <c r="Z121" s="116"/>
+      <c r="AA121" s="116"/>
+      <c r="AB121" s="116" t="s">
         <v>392</v>
       </c>
-      <c r="AC121" s="134"/>
-      <c r="AD121" s="134"/>
-      <c r="AE121" s="134"/>
-      <c r="AF121" s="134"/>
-      <c r="AG121" s="134"/>
-      <c r="AH121" s="134"/>
-      <c r="AI121" s="134"/>
-      <c r="AJ121" s="134">
+      <c r="AC121" s="116"/>
+      <c r="AD121" s="116"/>
+      <c r="AE121" s="116"/>
+      <c r="AF121" s="116"/>
+      <c r="AG121" s="116"/>
+      <c r="AH121" s="116"/>
+      <c r="AI121" s="116"/>
+      <c r="AJ121" s="116">
         <v>3</v>
       </c>
-      <c r="AK121" s="134"/>
-      <c r="AL121" s="134"/>
-      <c r="AM121" s="134"/>
-      <c r="AN121" s="134"/>
-      <c r="AO121" s="134"/>
-      <c r="AP121" s="134"/>
-      <c r="AQ121" s="134"/>
-      <c r="AR121" s="134" t="s">
+      <c r="AK121" s="116"/>
+      <c r="AL121" s="116"/>
+      <c r="AM121" s="116"/>
+      <c r="AN121" s="116"/>
+      <c r="AO121" s="116"/>
+      <c r="AP121" s="116"/>
+      <c r="AQ121" s="116"/>
+      <c r="AR121" s="116" t="s">
         <v>225</v>
       </c>
-      <c r="AS121" s="134"/>
-      <c r="AT121" s="134"/>
-      <c r="AU121" s="134"/>
-      <c r="AV121" s="134"/>
-      <c r="AW121" s="134"/>
-      <c r="AX121" s="134"/>
-      <c r="AY121" s="134"/>
-      <c r="AZ121" s="134" t="s">
+      <c r="AS121" s="116"/>
+      <c r="AT121" s="116"/>
+      <c r="AU121" s="116"/>
+      <c r="AV121" s="116"/>
+      <c r="AW121" s="116"/>
+      <c r="AX121" s="116"/>
+      <c r="AY121" s="116"/>
+      <c r="AZ121" s="116" t="s">
         <v>1017</v>
       </c>
-      <c r="BA121" s="134"/>
-      <c r="BB121" s="134"/>
-      <c r="BC121" s="134"/>
-      <c r="BD121" s="134"/>
-      <c r="BE121" s="134"/>
-      <c r="BF121" s="134"/>
-      <c r="BG121" s="134"/>
-      <c r="BH121" s="134">
+      <c r="BA121" s="116"/>
+      <c r="BB121" s="116"/>
+      <c r="BC121" s="116"/>
+      <c r="BD121" s="116"/>
+      <c r="BE121" s="116"/>
+      <c r="BF121" s="116"/>
+      <c r="BG121" s="116"/>
+      <c r="BH121" s="116">
         <v>57</v>
       </c>
-      <c r="BI121" s="134"/>
-      <c r="BJ121" s="134"/>
-      <c r="BK121" s="134"/>
-      <c r="BL121" s="134"/>
-      <c r="BM121" s="134"/>
-      <c r="BN121" s="134"/>
-      <c r="BO121" s="134"/>
-      <c r="BP121" s="134" t="s">
+      <c r="BI121" s="116"/>
+      <c r="BJ121" s="116"/>
+      <c r="BK121" s="116"/>
+      <c r="BL121" s="116"/>
+      <c r="BM121" s="116"/>
+      <c r="BN121" s="116"/>
+      <c r="BO121" s="116"/>
+      <c r="BP121" s="116" t="s">
         <v>392</v>
       </c>
-      <c r="BQ121" s="134"/>
-      <c r="BR121" s="134"/>
-      <c r="BS121" s="134"/>
-      <c r="BT121" s="134"/>
-      <c r="BU121" s="134"/>
-      <c r="BV121" s="134"/>
-      <c r="BW121" s="134"/>
+      <c r="BQ121" s="116"/>
+      <c r="BR121" s="116"/>
+      <c r="BS121" s="116"/>
+      <c r="BT121" s="116"/>
+      <c r="BU121" s="116"/>
+      <c r="BV121" s="116"/>
+      <c r="BW121" s="116"/>
     </row>
     <row r="122" spans="2:75" x14ac:dyDescent="0.3">
       <c r="D122" s="84"/>
@@ -23912,90 +24030,90 @@
       <c r="BW122" s="103"/>
     </row>
     <row r="123" spans="2:75" x14ac:dyDescent="0.3">
-      <c r="D123" s="134">
+      <c r="D123" s="116">
         <v>603</v>
       </c>
-      <c r="E123" s="134"/>
-      <c r="F123" s="134"/>
-      <c r="G123" s="134"/>
-      <c r="H123" s="134"/>
-      <c r="I123" s="134"/>
-      <c r="J123" s="134"/>
-      <c r="K123" s="134"/>
-      <c r="L123" s="134"/>
-      <c r="M123" s="134"/>
-      <c r="N123" s="134">
+      <c r="E123" s="116"/>
+      <c r="F123" s="116"/>
+      <c r="G123" s="116"/>
+      <c r="H123" s="116"/>
+      <c r="I123" s="116"/>
+      <c r="J123" s="116"/>
+      <c r="K123" s="116"/>
+      <c r="L123" s="116"/>
+      <c r="M123" s="116"/>
+      <c r="N123" s="116">
         <v>102</v>
       </c>
-      <c r="O123" s="134"/>
-      <c r="P123" s="134"/>
-      <c r="Q123" s="134"/>
-      <c r="R123" s="134"/>
-      <c r="S123" s="134"/>
-      <c r="T123" s="134"/>
-      <c r="U123" s="134"/>
-      <c r="V123" s="134">
+      <c r="O123" s="116"/>
+      <c r="P123" s="116"/>
+      <c r="Q123" s="116"/>
+      <c r="R123" s="116"/>
+      <c r="S123" s="116"/>
+      <c r="T123" s="116"/>
+      <c r="U123" s="116"/>
+      <c r="V123" s="116">
         <v>96</v>
       </c>
-      <c r="W123" s="134"/>
-      <c r="X123" s="134"/>
-      <c r="Y123" s="134"/>
-      <c r="Z123" s="134"/>
-      <c r="AA123" s="134"/>
-      <c r="AB123" s="134"/>
-      <c r="AC123" s="134"/>
-      <c r="AD123" s="134"/>
-      <c r="AE123" s="134"/>
-      <c r="AF123" s="134"/>
-      <c r="AG123" s="134"/>
-      <c r="AH123" s="134"/>
-      <c r="AI123" s="134"/>
-      <c r="AJ123" s="134"/>
-      <c r="AK123" s="134"/>
-      <c r="AL123" s="134"/>
-      <c r="AM123" s="134"/>
-      <c r="AN123" s="134"/>
-      <c r="AO123" s="134">
+      <c r="W123" s="116"/>
+      <c r="X123" s="116"/>
+      <c r="Y123" s="116"/>
+      <c r="Z123" s="116"/>
+      <c r="AA123" s="116"/>
+      <c r="AB123" s="116"/>
+      <c r="AC123" s="116"/>
+      <c r="AD123" s="116"/>
+      <c r="AE123" s="116"/>
+      <c r="AF123" s="116"/>
+      <c r="AG123" s="116"/>
+      <c r="AH123" s="116"/>
+      <c r="AI123" s="116"/>
+      <c r="AJ123" s="116"/>
+      <c r="AK123" s="116"/>
+      <c r="AL123" s="116"/>
+      <c r="AM123" s="116"/>
+      <c r="AN123" s="116"/>
+      <c r="AO123" s="116">
         <v>489</v>
       </c>
-      <c r="AP123" s="134"/>
-      <c r="AQ123" s="134"/>
-      <c r="AR123" s="134"/>
-      <c r="AS123" s="134"/>
-      <c r="AT123" s="134"/>
-      <c r="AU123" s="134"/>
-      <c r="AV123" s="134"/>
-      <c r="AW123" s="134"/>
-      <c r="AX123" s="134"/>
-      <c r="AY123" s="134">
+      <c r="AP123" s="116"/>
+      <c r="AQ123" s="116"/>
+      <c r="AR123" s="116"/>
+      <c r="AS123" s="116"/>
+      <c r="AT123" s="116"/>
+      <c r="AU123" s="116"/>
+      <c r="AV123" s="116"/>
+      <c r="AW123" s="116"/>
+      <c r="AX123" s="116"/>
+      <c r="AY123" s="116">
         <v>485</v>
       </c>
-      <c r="AZ123" s="134"/>
-      <c r="BA123" s="134"/>
-      <c r="BB123" s="134"/>
-      <c r="BC123" s="134"/>
-      <c r="BD123" s="134"/>
-      <c r="BE123" s="134"/>
-      <c r="BF123" s="134"/>
-      <c r="BG123" s="134"/>
-      <c r="BH123" s="134"/>
-      <c r="BI123" s="134">
+      <c r="AZ123" s="116"/>
+      <c r="BA123" s="116"/>
+      <c r="BB123" s="116"/>
+      <c r="BC123" s="116"/>
+      <c r="BD123" s="116"/>
+      <c r="BE123" s="116"/>
+      <c r="BF123" s="116"/>
+      <c r="BG123" s="116"/>
+      <c r="BH123" s="116"/>
+      <c r="BI123" s="116">
         <v>702</v>
       </c>
-      <c r="BJ123" s="134"/>
-      <c r="BK123" s="134"/>
-      <c r="BL123" s="134"/>
-      <c r="BM123" s="134"/>
-      <c r="BN123" s="134"/>
-      <c r="BO123" s="134"/>
-      <c r="BP123" s="134"/>
-      <c r="BQ123" s="134"/>
-      <c r="BR123" s="134"/>
+      <c r="BJ123" s="116"/>
+      <c r="BK123" s="116"/>
+      <c r="BL123" s="116"/>
+      <c r="BM123" s="116"/>
+      <c r="BN123" s="116"/>
+      <c r="BO123" s="116"/>
+      <c r="BP123" s="116"/>
+      <c r="BQ123" s="116"/>
+      <c r="BR123" s="116"/>
       <c r="BS123" s="5"/>
-      <c r="BT123" s="134"/>
-      <c r="BU123" s="134"/>
-      <c r="BV123" s="134"/>
-      <c r="BW123" s="134"/>
+      <c r="BT123" s="116"/>
+      <c r="BU123" s="116"/>
+      <c r="BV123" s="116"/>
+      <c r="BW123" s="116"/>
     </row>
     <row r="125" spans="2:75" x14ac:dyDescent="0.3">
       <c r="V125" s="106">
@@ -24052,123 +24170,39 @@
     </row>
   </sheetData>
   <mergeCells count="174">
-    <mergeCell ref="BT123:BW123"/>
-    <mergeCell ref="D123:M123"/>
-    <mergeCell ref="N123:U123"/>
-    <mergeCell ref="V123:AL123"/>
-    <mergeCell ref="AM123:AN123"/>
-    <mergeCell ref="AO123:AX123"/>
-    <mergeCell ref="AY123:BH123"/>
-    <mergeCell ref="BI123:BR123"/>
-    <mergeCell ref="D121:K121"/>
-    <mergeCell ref="L121:S121"/>
-    <mergeCell ref="T121:AA121"/>
-    <mergeCell ref="AB121:AI121"/>
-    <mergeCell ref="AJ121:AQ121"/>
-    <mergeCell ref="AR121:AY121"/>
-    <mergeCell ref="AZ121:BG121"/>
-    <mergeCell ref="BH121:BO121"/>
-    <mergeCell ref="BP121:BW121"/>
-    <mergeCell ref="BP118:BW118"/>
-    <mergeCell ref="D119:M119"/>
-    <mergeCell ref="N119:U119"/>
-    <mergeCell ref="V119:AL119"/>
-    <mergeCell ref="AM119:AN119"/>
-    <mergeCell ref="AO119:AX119"/>
-    <mergeCell ref="AY119:BH119"/>
-    <mergeCell ref="BI119:BR119"/>
-    <mergeCell ref="BT119:BW119"/>
-    <mergeCell ref="D118:K118"/>
-    <mergeCell ref="L118:S118"/>
-    <mergeCell ref="T118:AA118"/>
-    <mergeCell ref="AB118:AI118"/>
-    <mergeCell ref="AJ118:AQ118"/>
-    <mergeCell ref="AR118:AY118"/>
-    <mergeCell ref="AZ118:BG118"/>
-    <mergeCell ref="BH118:BO118"/>
-    <mergeCell ref="D94:K94"/>
-    <mergeCell ref="D109:K109"/>
-    <mergeCell ref="L109:S109"/>
-    <mergeCell ref="T109:AA109"/>
-    <mergeCell ref="D102:K102"/>
-    <mergeCell ref="L102:S102"/>
-    <mergeCell ref="U102:W102"/>
-    <mergeCell ref="D103:K103"/>
-    <mergeCell ref="Q89:AA89"/>
-    <mergeCell ref="D91:K91"/>
-    <mergeCell ref="L91:S91"/>
-    <mergeCell ref="T91:AA91"/>
-    <mergeCell ref="L94:S94"/>
-    <mergeCell ref="AB109:AI109"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="J97:P97"/>
-    <mergeCell ref="Q97:AA97"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="J98:P98"/>
-    <mergeCell ref="Q98:AA98"/>
-    <mergeCell ref="D100:K100"/>
-    <mergeCell ref="L100:S100"/>
-    <mergeCell ref="T100:AA100"/>
-    <mergeCell ref="AB100:AI100"/>
-    <mergeCell ref="D106:I106"/>
-    <mergeCell ref="J106:P106"/>
-    <mergeCell ref="Q106:AA106"/>
-    <mergeCell ref="D107:I107"/>
-    <mergeCell ref="J107:P107"/>
-    <mergeCell ref="Q107:AA107"/>
-    <mergeCell ref="L103:S103"/>
-    <mergeCell ref="AR114:AY114"/>
-    <mergeCell ref="D114:K114"/>
-    <mergeCell ref="L114:S114"/>
-    <mergeCell ref="T114:AA114"/>
-    <mergeCell ref="AB114:AI114"/>
-    <mergeCell ref="AJ114:AQ114"/>
-    <mergeCell ref="AR111:AY111"/>
-    <mergeCell ref="E112:H112"/>
-    <mergeCell ref="I112:P112"/>
-    <mergeCell ref="Q112:R112"/>
-    <mergeCell ref="S112:Z112"/>
-    <mergeCell ref="AA112:AH112"/>
-    <mergeCell ref="AI112:AP112"/>
-    <mergeCell ref="AQ112:AR112"/>
-    <mergeCell ref="AS112:AU112"/>
-    <mergeCell ref="D111:K111"/>
-    <mergeCell ref="L111:S111"/>
-    <mergeCell ref="T111:AA111"/>
-    <mergeCell ref="AB111:AI111"/>
-    <mergeCell ref="AJ111:AQ111"/>
-    <mergeCell ref="T36:AA36"/>
-    <mergeCell ref="D34:K34"/>
-    <mergeCell ref="R34:AA34"/>
-    <mergeCell ref="R35:AA35"/>
-    <mergeCell ref="T29:AA29"/>
-    <mergeCell ref="T30:AA30"/>
-    <mergeCell ref="T31:AA31"/>
-    <mergeCell ref="T21:AA21"/>
-    <mergeCell ref="AB21:AI21"/>
-    <mergeCell ref="L14:S14"/>
-    <mergeCell ref="T14:AA14"/>
-    <mergeCell ref="T9:AA9"/>
-    <mergeCell ref="AC9:AE9"/>
-    <mergeCell ref="L10:S10"/>
-    <mergeCell ref="D10:K10"/>
-    <mergeCell ref="T10:AA10"/>
-    <mergeCell ref="D20:K20"/>
-    <mergeCell ref="D26:K26"/>
-    <mergeCell ref="L26:S26"/>
-    <mergeCell ref="T26:AA26"/>
-    <mergeCell ref="AB26:AI26"/>
-    <mergeCell ref="L24:U24"/>
-    <mergeCell ref="T15:AA15"/>
-    <mergeCell ref="D16:K16"/>
-    <mergeCell ref="L16:S16"/>
-    <mergeCell ref="T16:AA16"/>
-    <mergeCell ref="AB20:AI20"/>
-    <mergeCell ref="AB16:AI16"/>
-    <mergeCell ref="D18:K18"/>
-    <mergeCell ref="L18:U18"/>
-    <mergeCell ref="D19:K19"/>
-    <mergeCell ref="L19:U19"/>
+    <mergeCell ref="AD93:AE93"/>
+    <mergeCell ref="AH93:AI93"/>
+    <mergeCell ref="V93:AA93"/>
+    <mergeCell ref="AG71:AH71"/>
+    <mergeCell ref="AG72:AH72"/>
+    <mergeCell ref="AG73:AH73"/>
+    <mergeCell ref="D75:K75"/>
+    <mergeCell ref="AG75:AH75"/>
+    <mergeCell ref="AG76:AH76"/>
+    <mergeCell ref="AG77:AH77"/>
+    <mergeCell ref="D84:K84"/>
+    <mergeCell ref="L84:S84"/>
+    <mergeCell ref="U84:W84"/>
+    <mergeCell ref="D80:K80"/>
+    <mergeCell ref="M80:S80"/>
+    <mergeCell ref="T80:AA80"/>
+    <mergeCell ref="AB91:AI91"/>
+    <mergeCell ref="D89:I89"/>
+    <mergeCell ref="J89:P89"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="Q88:AA88"/>
+    <mergeCell ref="J88:P88"/>
+    <mergeCell ref="D93:K93"/>
+    <mergeCell ref="L93:S93"/>
+    <mergeCell ref="D47:K47"/>
+    <mergeCell ref="D51:K51"/>
+    <mergeCell ref="L51:S51"/>
+    <mergeCell ref="D55:K55"/>
+    <mergeCell ref="D59:K59"/>
+    <mergeCell ref="L59:S59"/>
+    <mergeCell ref="D63:K63"/>
+    <mergeCell ref="D67:K67"/>
+    <mergeCell ref="D71:K71"/>
     <mergeCell ref="T1:AA1"/>
     <mergeCell ref="AB1:AI1"/>
     <mergeCell ref="D4:K4"/>
@@ -24193,39 +24227,123 @@
     <mergeCell ref="T11:AA11"/>
     <mergeCell ref="AB11:AI11"/>
     <mergeCell ref="D14:K14"/>
-    <mergeCell ref="D47:K47"/>
-    <mergeCell ref="D51:K51"/>
-    <mergeCell ref="L51:S51"/>
-    <mergeCell ref="D55:K55"/>
-    <mergeCell ref="D59:K59"/>
-    <mergeCell ref="L59:S59"/>
-    <mergeCell ref="D63:K63"/>
-    <mergeCell ref="D67:K67"/>
-    <mergeCell ref="D71:K71"/>
-    <mergeCell ref="AD93:AE93"/>
-    <mergeCell ref="AH93:AI93"/>
-    <mergeCell ref="V93:AA93"/>
-    <mergeCell ref="AG71:AH71"/>
-    <mergeCell ref="AG72:AH72"/>
-    <mergeCell ref="AG73:AH73"/>
-    <mergeCell ref="D75:K75"/>
-    <mergeCell ref="AG75:AH75"/>
-    <mergeCell ref="AG76:AH76"/>
-    <mergeCell ref="AG77:AH77"/>
-    <mergeCell ref="D84:K84"/>
-    <mergeCell ref="L84:S84"/>
-    <mergeCell ref="U84:W84"/>
-    <mergeCell ref="D80:K80"/>
-    <mergeCell ref="M80:S80"/>
-    <mergeCell ref="T80:AA80"/>
-    <mergeCell ref="AB91:AI91"/>
-    <mergeCell ref="D89:I89"/>
-    <mergeCell ref="J89:P89"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="Q88:AA88"/>
-    <mergeCell ref="J88:P88"/>
-    <mergeCell ref="D93:K93"/>
-    <mergeCell ref="L93:S93"/>
+    <mergeCell ref="L14:S14"/>
+    <mergeCell ref="T14:AA14"/>
+    <mergeCell ref="T9:AA9"/>
+    <mergeCell ref="AC9:AE9"/>
+    <mergeCell ref="L10:S10"/>
+    <mergeCell ref="D10:K10"/>
+    <mergeCell ref="T10:AA10"/>
+    <mergeCell ref="D20:K20"/>
+    <mergeCell ref="D26:K26"/>
+    <mergeCell ref="L26:S26"/>
+    <mergeCell ref="T26:AA26"/>
+    <mergeCell ref="AB26:AI26"/>
+    <mergeCell ref="L24:U24"/>
+    <mergeCell ref="T15:AA15"/>
+    <mergeCell ref="D16:K16"/>
+    <mergeCell ref="L16:S16"/>
+    <mergeCell ref="T16:AA16"/>
+    <mergeCell ref="AB20:AI20"/>
+    <mergeCell ref="AB16:AI16"/>
+    <mergeCell ref="D18:K18"/>
+    <mergeCell ref="L18:U18"/>
+    <mergeCell ref="D19:K19"/>
+    <mergeCell ref="L19:U19"/>
+    <mergeCell ref="T36:AA36"/>
+    <mergeCell ref="D34:K34"/>
+    <mergeCell ref="R34:AA34"/>
+    <mergeCell ref="R35:AA35"/>
+    <mergeCell ref="T29:AA29"/>
+    <mergeCell ref="T30:AA30"/>
+    <mergeCell ref="T31:AA31"/>
+    <mergeCell ref="T21:AA21"/>
+    <mergeCell ref="AB21:AI21"/>
+    <mergeCell ref="AR114:AY114"/>
+    <mergeCell ref="D114:K114"/>
+    <mergeCell ref="L114:S114"/>
+    <mergeCell ref="T114:AA114"/>
+    <mergeCell ref="AB114:AI114"/>
+    <mergeCell ref="AJ114:AQ114"/>
+    <mergeCell ref="AR111:AY111"/>
+    <mergeCell ref="E112:H112"/>
+    <mergeCell ref="I112:P112"/>
+    <mergeCell ref="Q112:R112"/>
+    <mergeCell ref="S112:Z112"/>
+    <mergeCell ref="AA112:AH112"/>
+    <mergeCell ref="AI112:AP112"/>
+    <mergeCell ref="AQ112:AR112"/>
+    <mergeCell ref="AS112:AU112"/>
+    <mergeCell ref="D111:K111"/>
+    <mergeCell ref="L111:S111"/>
+    <mergeCell ref="T111:AA111"/>
+    <mergeCell ref="AB111:AI111"/>
+    <mergeCell ref="AJ111:AQ111"/>
+    <mergeCell ref="AB109:AI109"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="J97:P97"/>
+    <mergeCell ref="Q97:AA97"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="J98:P98"/>
+    <mergeCell ref="Q98:AA98"/>
+    <mergeCell ref="D100:K100"/>
+    <mergeCell ref="L100:S100"/>
+    <mergeCell ref="T100:AA100"/>
+    <mergeCell ref="AB100:AI100"/>
+    <mergeCell ref="D106:I106"/>
+    <mergeCell ref="J106:P106"/>
+    <mergeCell ref="Q106:AA106"/>
+    <mergeCell ref="D107:I107"/>
+    <mergeCell ref="J107:P107"/>
+    <mergeCell ref="Q107:AA107"/>
+    <mergeCell ref="L103:S103"/>
+    <mergeCell ref="D94:K94"/>
+    <mergeCell ref="D109:K109"/>
+    <mergeCell ref="L109:S109"/>
+    <mergeCell ref="T109:AA109"/>
+    <mergeCell ref="D102:K102"/>
+    <mergeCell ref="L102:S102"/>
+    <mergeCell ref="U102:W102"/>
+    <mergeCell ref="D103:K103"/>
+    <mergeCell ref="Q89:AA89"/>
+    <mergeCell ref="D91:K91"/>
+    <mergeCell ref="L91:S91"/>
+    <mergeCell ref="T91:AA91"/>
+    <mergeCell ref="L94:S94"/>
+    <mergeCell ref="BP118:BW118"/>
+    <mergeCell ref="D119:M119"/>
+    <mergeCell ref="N119:U119"/>
+    <mergeCell ref="V119:AL119"/>
+    <mergeCell ref="AM119:AN119"/>
+    <mergeCell ref="AO119:AX119"/>
+    <mergeCell ref="AY119:BH119"/>
+    <mergeCell ref="BI119:BR119"/>
+    <mergeCell ref="BT119:BW119"/>
+    <mergeCell ref="D118:K118"/>
+    <mergeCell ref="L118:S118"/>
+    <mergeCell ref="T118:AA118"/>
+    <mergeCell ref="AB118:AI118"/>
+    <mergeCell ref="AJ118:AQ118"/>
+    <mergeCell ref="AR118:AY118"/>
+    <mergeCell ref="AZ118:BG118"/>
+    <mergeCell ref="BH118:BO118"/>
+    <mergeCell ref="BT123:BW123"/>
+    <mergeCell ref="D123:M123"/>
+    <mergeCell ref="N123:U123"/>
+    <mergeCell ref="V123:AL123"/>
+    <mergeCell ref="AM123:AN123"/>
+    <mergeCell ref="AO123:AX123"/>
+    <mergeCell ref="AY123:BH123"/>
+    <mergeCell ref="BI123:BR123"/>
+    <mergeCell ref="D121:K121"/>
+    <mergeCell ref="L121:S121"/>
+    <mergeCell ref="T121:AA121"/>
+    <mergeCell ref="AB121:AI121"/>
+    <mergeCell ref="AJ121:AQ121"/>
+    <mergeCell ref="AR121:AY121"/>
+    <mergeCell ref="AZ121:BG121"/>
+    <mergeCell ref="BH121:BO121"/>
+    <mergeCell ref="BP121:BW121"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -24920,24 +25038,24 @@
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="C45" s="134" t="s">
+      <c r="C45" s="116" t="s">
         <v>778</v>
       </c>
-      <c r="D45" s="134"/>
-      <c r="E45" s="134" t="s">
+      <c r="D45" s="116"/>
+      <c r="E45" s="116" t="s">
         <v>779</v>
       </c>
-      <c r="F45" s="134"/>
+      <c r="F45" s="116"/>
       <c r="G45" s="9" t="s">
         <v>781</v>
       </c>
       <c r="H45" s="9" t="s">
         <v>782</v>
       </c>
-      <c r="I45" s="134" t="s">
+      <c r="I45" s="116" t="s">
         <v>780</v>
       </c>
-      <c r="J45" s="134"/>
+      <c r="J45" s="116"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B47" s="60" t="s">
@@ -25097,20 +25215,20 @@
       </c>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C70" s="134" t="s">
+      <c r="C70" s="116" t="s">
         <v>807</v>
       </c>
-      <c r="D70" s="134"/>
-      <c r="E70" s="134"/>
-      <c r="F70" s="134" t="s">
+      <c r="D70" s="116"/>
+      <c r="E70" s="116"/>
+      <c r="F70" s="116" t="s">
         <v>808</v>
       </c>
-      <c r="G70" s="134"/>
-      <c r="H70" s="134" t="s">
+      <c r="G70" s="116"/>
+      <c r="H70" s="116" t="s">
         <v>809</v>
       </c>
-      <c r="I70" s="134"/>
-      <c r="J70" s="134"/>
+      <c r="I70" s="116"/>
+      <c r="J70" s="116"/>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C71" s="9">
@@ -25142,20 +25260,20 @@
       </c>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C72" s="134">
+      <c r="C72" s="116">
         <v>2</v>
       </c>
-      <c r="D72" s="134"/>
-      <c r="E72" s="134"/>
-      <c r="F72" s="134">
+      <c r="D72" s="116"/>
+      <c r="E72" s="116"/>
+      <c r="F72" s="116">
         <v>1</v>
       </c>
-      <c r="G72" s="134"/>
-      <c r="H72" s="134">
+      <c r="G72" s="116"/>
+      <c r="H72" s="116">
         <v>3</v>
       </c>
-      <c r="I72" s="134"/>
-      <c r="J72" s="134"/>
+      <c r="I72" s="116"/>
+      <c r="J72" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -25184,14 +25302,14 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="129" t="s">
         <v>709</v>
       </c>
-      <c r="C3" s="110"/>
-      <c r="E3" s="110" t="s">
+      <c r="C3" s="129"/>
+      <c r="E3" s="129" t="s">
         <v>709</v>
       </c>
-      <c r="F3" s="110"/>
+      <c r="F3" s="129"/>
       <c r="G3" s="15"/>
       <c r="L3" s="15"/>
     </row>
@@ -25200,7 +25318,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="71">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
         <v>710</v>
@@ -25211,23 +25329,23 @@
       <c r="F4" s="71">
         <v>255</v>
       </c>
-      <c r="J4" s="110" t="s">
+      <c r="J4" s="129" t="s">
         <v>888</v>
       </c>
-      <c r="K4" s="110"/>
+      <c r="K4" s="129"/>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="14">
         <v>0</v>
       </c>
       <c r="C5" s="14">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="E5" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F5" s="14">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="G5" t="s">
         <v>710</v>
@@ -25249,7 +25367,7 @@
       </c>
       <c r="C6" s="72">
         <f>C4+(0-B4)</f>
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
         <v>377</v>
@@ -25260,7 +25378,7 @@
       </c>
       <c r="F6" s="72">
         <f>F5+(0-E5)</f>
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
         <v>870</v>
@@ -25282,15 +25400,15 @@
       </c>
       <c r="C7" s="73">
         <f>C6/C5</f>
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E7" s="72">
         <f xml:space="preserve"> (0-E5)*(-1)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F7" s="73">
         <f>F4/F6</f>
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="G7" t="s">
         <v>871</v>
@@ -25312,15 +25430,15 @@
       </c>
       <c r="C8" s="72">
         <f>C4*C7</f>
-        <v>50</v>
+        <v>10.200000000000001</v>
       </c>
       <c r="E8" s="72">
         <f>E4/F7+E7</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F8" s="72">
         <f>F4/F7+E7</f>
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
         <v>872</v>
@@ -25353,14 +25471,14 @@
       </c>
       <c r="C10" s="77">
         <f>C7</f>
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E10" s="75" t="s">
         <v>873</v>
       </c>
       <c r="F10" s="77">
         <f>F7</f>
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>50</v>
@@ -25385,7 +25503,7 @@
       </c>
       <c r="F11" s="76">
         <f>E7</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>51</v>
@@ -25398,14 +25516,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="108" t="s">
+      <c r="B12" s="134" t="s">
         <v>876</v>
       </c>
-      <c r="C12" s="109"/>
-      <c r="E12" s="108" t="s">
+      <c r="C12" s="135"/>
+      <c r="E12" s="134" t="s">
         <v>876</v>
       </c>
-      <c r="F12" s="109"/>
+      <c r="F12" s="135"/>
       <c r="J12">
         <v>52</v>
       </c>
@@ -25445,14 +25563,14 @@
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C15" s="81">
         <f>C14*C10+C11</f>
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
         <v>710</v>
       </c>
       <c r="F15" s="81">
         <f>F14/F10+F11</f>
-        <v>67.058823529411768</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -25469,19 +25587,19 @@
       <c r="O17">
         <v>10</v>
       </c>
-      <c r="P17" s="107">
+      <c r="P17" s="133">
         <v>4</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C18" s="81">
         <f>(C17-C11)/C10</f>
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="O18">
         <v>20</v>
       </c>
-      <c r="P18" s="107"/>
+      <c r="P18" s="133"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="M19">
@@ -25491,13 +25609,13 @@
       <c r="O19">
         <v>30</v>
       </c>
-      <c r="P19" s="107"/>
+      <c r="P19" s="133"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="O20">
         <v>40</v>
       </c>
-      <c r="P20" s="107">
+      <c r="P20" s="133">
         <v>4</v>
       </c>
     </row>
@@ -25512,20 +25630,20 @@
       <c r="O21">
         <v>50</v>
       </c>
-      <c r="P21" s="107"/>
+      <c r="P21" s="133"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="M22" s="19"/>
       <c r="O22">
         <v>60</v>
       </c>
-      <c r="P22" s="107"/>
+      <c r="P22" s="133"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="O23">
         <v>70</v>
       </c>
-      <c r="P23" s="107">
+      <c r="P23" s="133">
         <v>4</v>
       </c>
     </row>
@@ -25533,13 +25651,13 @@
       <c r="O24">
         <v>80</v>
       </c>
-      <c r="P24" s="107"/>
+      <c r="P24" s="133"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="O25">
         <v>90</v>
       </c>
-      <c r="P25" s="107"/>
+      <c r="P25" s="133"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P26" s="20">
